--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,9 +17,9 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AG$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AG$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$7</f>
+              <f>'資金明細'!$R$2:$R$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-24 18:50（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-24 20:22（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -796,19 +796,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$4,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$7,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$4,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$7,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$4,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$7,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$4,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$7,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -816,35 +816,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$4,交易明細!$J$2:$J$4,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$7,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$4,交易明細!$J$2:$J$4,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$4,交易明細!$J$2:$J$4,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$4,交易明細!$J$2:$J$4,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$4,交易明細!$J$2:$J$4,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$J$2:$J$7,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$4,交易明細!$J$2:$J$4,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$J$2:$J$7,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$4,交易明細!$J$2:$J$4,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$J$2:$J$7,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$4,"&lt;&gt;未平倉",交易明細!$L$2:$L$4,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$7,"&lt;&gt;未平倉",交易明細!$L$2:$L$7,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$4,"做多",交易明細!$B$2:$B$4,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$7,"做多",交易明細!$B$2:$B$7,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -863,19 +863,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$4,"做多",交易明細!$J$2:$J$4,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$4,"做多",交易明細!$J$2:$J$4,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$4,"做多",交易明細!$J$2:$J$4,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$4,"做多",交易明細!$J$2:$J$4,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -883,35 +883,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$4,交易明細!$C$2:$C$4,"做多",交易明細!$J$2:$J$4,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$7,交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$4,交易明細!$C$2:$C$4,"做多",交易明細!$J$2:$J$4,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$4,交易明細!$C$2:$C$4,"做多",交易明細!$J$2:$J$4,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$4,交易明細!$C$2:$C$4,"做多",交易明細!$J$2:$J$4,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$4,交易明細!$C$2:$C$4,"做多",交易明細!$J$2:$J$4,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$4,交易明細!$C$2:$C$4,"做多",交易明細!$J$2:$J$4,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$4,交易明細!$C$2:$C$4,"做多",交易明細!$J$2:$J$4,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$4,"做多",交易明細!$J$2:$J$4,"&lt;&gt;未平倉",交易明細!$L$2:$L$4,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"&lt;&gt;未平倉",交易明細!$L$2:$L$7,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$4,"做空",交易明細!$B$2:$B$4,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$7,"做空",交易明細!$B$2:$B$7,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -930,19 +930,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$4,"做空",交易明細!$J$2:$J$4,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$4,"做空",交易明細!$J$2:$J$4,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$4,"做空",交易明細!$J$2:$J$4,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$4,"做空",交易明細!$J$2:$J$4,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -950,35 +950,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$4,交易明細!$C$2:$C$4,"做空",交易明細!$J$2:$J$4,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$7,交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$4,交易明細!$C$2:$C$4,"做空",交易明細!$J$2:$J$4,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$4,交易明細!$C$2:$C$4,"做空",交易明細!$J$2:$J$4,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$4,交易明細!$C$2:$C$4,"做空",交易明細!$J$2:$J$4,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$4,交易明細!$C$2:$C$4,"做空",交易明細!$J$2:$J$4,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$4,交易明細!$C$2:$C$4,"做空",交易明細!$J$2:$J$4,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$4,交易明細!$C$2:$C$4,"做空",交易明細!$J$2:$J$4,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$4,"做空",交易明細!$J$2:$J$4,"&lt;&gt;未平倉",交易明細!$L$2:$L$4,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"&lt;&gt;未平倉",交易明細!$L$2:$L$7,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
@@ -1098,44 +1098,44 @@
         <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
@@ -1150,15 +1150,15 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
@@ -1173,15 +1173,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
@@ -1196,15 +1196,15 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
@@ -1219,15 +1219,15 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
@@ -1242,15 +1242,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
@@ -1262,18 +1262,18 @@
         <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
@@ -1288,15 +1288,15 @@
         <v>2</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
@@ -1311,15 +1311,15 @@
         <v>2</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
@@ -1334,18 +1334,18 @@
         <v>2</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0</v>
@@ -1357,15 +1357,15 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>441</v>
@@ -1380,15 +1380,15 @@
         <v>2</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>441</v>
@@ -1403,15 +1403,15 @@
         <v>2</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>441</v>
@@ -1426,18 +1426,18 @@
         <v>2</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
@@ -1446,18 +1446,18 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>440</v>
@@ -1472,15 +1472,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>440</v>
@@ -1495,15 +1495,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>440</v>
@@ -1518,15 +1518,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>440</v>
@@ -1541,15 +1541,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>440</v>
@@ -1564,15 +1564,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>440</v>
@@ -1587,15 +1587,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>440</v>
@@ -1610,15 +1610,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>440</v>
@@ -1633,15 +1633,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>440</v>
@@ -1656,15 +1656,15 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>440</v>
@@ -1679,15 +1679,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>440</v>
@@ -1702,15 +1702,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>440</v>
@@ -1725,15 +1725,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>440</v>
@@ -1748,15 +1748,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>440</v>
@@ -1771,15 +1771,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>440</v>
@@ -1794,15 +1794,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,18 +2484,18 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>0</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>442</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>442</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>442</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>442</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>442</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>442</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>442</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>442</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>442</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>442</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>442</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>442</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>442</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>442</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>442</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2903,10 +2903,10 @@
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,6 +2944,29 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B83" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3009,7 +3032,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R7</f>
+        <f>資金明細!R11</f>
         <v/>
       </c>
     </row>
@@ -3047,7 +3070,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$7)</f>
+        <f>MAX(資金明細!$R$2:$R$11)</f>
         <v/>
       </c>
     </row>
@@ -3066,7 +3089,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$7)</f>
+        <f>MIN(資金明細!$R$2:$R$11)</f>
         <v/>
       </c>
     </row>
@@ -3086,7 +3109,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$7)</f>
+        <f>MIN(資金明細!$X$2:$X$11)</f>
         <v/>
       </c>
     </row>
@@ -3105,7 +3128,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$7,"進場",資金明細!$N$2:$N$7,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$11,"進場",資金明細!$N$2:$N$11,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3124,7 +3147,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$7,"進場",資金明細!$N$2:$N$7,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$11,"進場",資金明細!$N$2:$N$11,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3135,7 +3158,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$7,"出場",資金明細!$N$2:$N$7,"已下單",資金明細!$K$2:$K$7,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$11,"出場",資金明細!$N$2:$N$11,"已下單",資金明細!$K$2:$K$11,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3146,7 +3169,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$4),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$7),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3155,7 +3178,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$7,"出場",資金明細!$N$2:$N$7,"已下單",資金明細!$K$2:$K$7,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$11,"出場",資金明細!$N$2:$N$11,"已下單",資金明細!$K$2:$K$11,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3171,7 +3194,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$7,"出場",資金明細!$N$2:$N$7,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$11,"出場",資金明細!$N$2:$N$11,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3187,7 +3210,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$7)</f>
+        <f>MAX(資金明細!$U$2:$U$11)</f>
         <v/>
       </c>
     </row>
@@ -3203,7 +3226,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$7)</f>
+        <f>MAX(資金明細!$S$2:$S$11)</f>
         <v/>
       </c>
     </row>
@@ -3214,7 +3237,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V7</f>
+        <f>B5*資金明細!V11</f>
         <v/>
       </c>
     </row>
@@ -3225,7 +3248,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N3="已下單",資金明細!O3*交易明細!L2,0)</f>
+        <f>IF(資金明細!N3="已下單",資金明細!O3*交易明細!L2,0)+IF(資金明細!N10="已下單",資金明細!O10*交易明細!L6,0)+IF(資金明細!N11="已下單",資金明細!O11*交易明細!L7,0)</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3259,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$7)</f>
+        <f>MAX(資金明細!$Y$2:$Y$11)</f>
         <v/>
       </c>
     </row>
@@ -3258,7 +3281,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$7,MATCH(1,資金明細!$Z$2:$Z$7,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$11,MATCH(1,資金明細!$Z$2:$Z$11,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3269,7 +3292,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$7,"進場",資金明細!$N$2:$N$7,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$11,"進場",資金明細!$N$2:$N$11,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3334,7 +3357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4035,9 +4058,390 @@
         <v/>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>46289.80486111111</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>BROCCOLI_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>0.02962</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>0.0287314</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>0.031101</v>
+      </c>
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="16">
+        <f>資金模擬!$B$5*V7</f>
+        <v/>
+      </c>
+      <c r="N8" s="2">
+        <f>IF(Z7=1,"已停止",IF(T7&gt;=M8,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O8" s="16">
+        <f>IF(N8="已下單",M8*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="10">
+        <f>R7+Q8</f>
+        <v/>
+      </c>
+      <c r="S8" s="16">
+        <f>S7+IF(N8="已下單",M8,0)</f>
+        <v/>
+      </c>
+      <c r="T8" s="16">
+        <f>R8-S8</f>
+        <v/>
+      </c>
+      <c r="U8" s="2">
+        <f>U7+IF(N8="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V8" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R8,0),MAX(V7,FLOOR(MAX(R8,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W8" s="10">
+        <f>MAX(W7,R8)</f>
+        <v/>
+      </c>
+      <c r="X8" s="4">
+        <f>IF(W8&gt;0,R8/W8-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y8" s="16">
+        <f>IF(R8&gt;0,S8*資金模擬!$B$7/R8,0)</f>
+        <v/>
+      </c>
+      <c r="Z8" s="2">
+        <f>IF(OR(Z7=1,R8&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>46289.80902777778</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>BROCCOLI_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>0.02962</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>0.0287314</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>0.031101</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>0.0287314</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L9" s="5">
+        <f>交易明細!K5</f>
+        <v/>
+      </c>
+      <c r="M9" s="16">
+        <f>M8</f>
+        <v/>
+      </c>
+      <c r="N9" s="2">
+        <f>N8</f>
+        <v/>
+      </c>
+      <c r="O9" s="16">
+        <f>O8</f>
+        <v/>
+      </c>
+      <c r="P9" s="4">
+        <f>交易明細!L5</f>
+        <v/>
+      </c>
+      <c r="Q9" s="10">
+        <f>IF(N9="已下單",O9*P9,0)</f>
+        <v/>
+      </c>
+      <c r="R9" s="10">
+        <f>R8+Q9</f>
+        <v/>
+      </c>
+      <c r="S9" s="16">
+        <f>S8-IF(N9="已下單",M9,0)</f>
+        <v/>
+      </c>
+      <c r="T9" s="16">
+        <f>R9-S9</f>
+        <v/>
+      </c>
+      <c r="U9" s="2">
+        <f>U8-IF(N9="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V9" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R9,0),MAX(V8,FLOOR(MAX(R9,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W9" s="10">
+        <f>MAX(W8,R9)</f>
+        <v/>
+      </c>
+      <c r="X9" s="4">
+        <f>IF(W9&gt;0,R9/W9-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y9" s="16">
+        <f>IF(R9&gt;0,S9*資金模擬!$B$7/R9,0)</f>
+        <v/>
+      </c>
+      <c r="Z9" s="2">
+        <f>IF(OR(Z8=1,R9&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>46289.81041666667</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>AGT_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>0.019584</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0.01899648</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>0.0205632</v>
+      </c>
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="16">
+        <f>資金模擬!$B$5*V9</f>
+        <v/>
+      </c>
+      <c r="N10" s="2">
+        <f>IF(Z9=1,"已停止",IF(T9&gt;=M10,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O10" s="16">
+        <f>IF(N10="已下單",M10*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P10" s="4" t="n"/>
+      <c r="Q10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="10">
+        <f>R9+Q10</f>
+        <v/>
+      </c>
+      <c r="S10" s="16">
+        <f>S9+IF(N10="已下單",M10,0)</f>
+        <v/>
+      </c>
+      <c r="T10" s="16">
+        <f>R10-S10</f>
+        <v/>
+      </c>
+      <c r="U10" s="2">
+        <f>U9+IF(N10="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V10" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R10,0),MAX(V9,FLOOR(MAX(R10,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W10" s="10">
+        <f>MAX(W9,R10)</f>
+        <v/>
+      </c>
+      <c r="X10" s="4">
+        <f>IF(W10&gt;0,R10/W10-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y10" s="16">
+        <f>IF(R10&gt;0,S10*資金模擬!$B$7/R10,0)</f>
+        <v/>
+      </c>
+      <c r="Z10" s="2">
+        <f>IF(OR(Z9=1,R10&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>46289.83611111111</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>PHA_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>0.05169</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>0.0501393</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>0.0542745</v>
+      </c>
+      <c r="J11" s="17" t="n"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="16">
+        <f>資金模擬!$B$5*V10</f>
+        <v/>
+      </c>
+      <c r="N11" s="2">
+        <f>IF(Z10=1,"已停止",IF(T10&gt;=M11,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O11" s="16">
+        <f>IF(N11="已下單",M11*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P11" s="4" t="n"/>
+      <c r="Q11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="10">
+        <f>R10+Q11</f>
+        <v/>
+      </c>
+      <c r="S11" s="16">
+        <f>S10+IF(N11="已下單",M11,0)</f>
+        <v/>
+      </c>
+      <c r="T11" s="16">
+        <f>R11-S11</f>
+        <v/>
+      </c>
+      <c r="U11" s="2">
+        <f>U10+IF(N11="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V11" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R11,0),MAX(V10,FLOOR(MAX(R11,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W11" s="10">
+        <f>MAX(W10,R11)</f>
+        <v/>
+      </c>
+      <c r="X11" s="4">
+        <f>IF(W11&gt;0,R11/W11-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="16">
+        <f>IF(R11&gt;0,S11*資金模擬!$B$7/R11,0)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="2">
+        <f>IF(OR(Z10=1,R11&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z7"/>
-  <conditionalFormatting sqref="K2:K7">
+  <autoFilter ref="A1:Z11"/>
+  <conditionalFormatting sqref="K2:K11">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -4045,7 +4449,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N7">
+  <conditionalFormatting sqref="N2:N11">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -4053,7 +4457,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q7">
+  <conditionalFormatting sqref="Q2:Q11">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -4118,7 +4522,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-24 18:50（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-24 20:22（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -4326,7 +4730,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$4),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$7),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4352,7 +4756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG4"/>
+  <dimension ref="A1:AG7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4584,10 +4988,10 @@
         <v>69.88800000000001</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>46289.78472222222</v>
+        <v>46289.84861111111</v>
       </c>
       <c r="I2" s="17" t="n">
-        <v>66.89</v>
+        <v>65.88</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -4613,7 +5017,7 @@
       <c r="Q2" s="19" t="n"/>
       <c r="R2" s="19" t="n"/>
       <c r="S2" s="4" t="n">
-        <v>0.009314903846153966</v>
+        <v>0.01532451923076916</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0.04371995192307687</v>
@@ -4819,9 +5223,275 @@
         <v>20</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>BROCCOLI_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>46289.80486111111</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0.02962</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>0.0287314</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>0.031101</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>46289.80902777778</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>0.0287314</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K5" s="5">
+        <f>(H5-D5)*24</f>
+        <v/>
+      </c>
+      <c r="L5" s="4">
+        <f>IF(C5="做多",I5/E5-1,1-I5/E5)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="19" t="n"/>
+      <c r="R5" s="19" t="n"/>
+      <c r="S5" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>0.006752194463200523</v>
+      </c>
+      <c r="U5" s="16" t="n"/>
+      <c r="V5" s="16" t="n"/>
+      <c r="W5" s="4" t="n"/>
+      <c r="X5" s="4" t="n"/>
+      <c r="Y5" s="4" t="n"/>
+      <c r="Z5" s="4" t="n"/>
+      <c r="AA5" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC5" s="4">
+        <f>(AB5+2*參數!$B$7)/(AA5+AB5)</f>
+        <v/>
+      </c>
+      <c r="AD5" s="2" t="n">
+        <v>0.1207865168539326</v>
+      </c>
+      <c r="AE5" s="2" t="n">
+        <v>1.057180369253066</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>0.04075895994378076</v>
+      </c>
+      <c r="AG5" s="2" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>AGT_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>46289.81041666667</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0.019584</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>0.01899648</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>0.0205632</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>46289.84861111111</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>0.019687</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K6" s="5">
+        <f>(H6-D6)*24</f>
+        <v/>
+      </c>
+      <c r="L6" s="4">
+        <f>IF(C6="做多",I6/E6-1,1-I6/E6)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="19" t="n"/>
+      <c r="R6" s="19" t="n"/>
+      <c r="S6" s="4" t="n">
+        <v>0.006995506535947826</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>0.01710580065359468</v>
+      </c>
+      <c r="U6" s="16" t="n"/>
+      <c r="V6" s="16" t="n"/>
+      <c r="W6" s="4" t="n"/>
+      <c r="X6" s="4" t="n"/>
+      <c r="Y6" s="4" t="n"/>
+      <c r="Z6" s="4" t="n"/>
+      <c r="AA6" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB6" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC6" s="4">
+        <f>(AB6+2*參數!$B$7)/(AA6+AB6)</f>
+        <v/>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>0.06028797537920427</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>1.019097229886326</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>0.01329745951259897</v>
+      </c>
+      <c r="AG6" s="2" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>PHA_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>46289.83611111111</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.05169</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>0.0501393</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>0.0542745</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>46289.84861111111</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>0.05308</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K7" s="5">
+        <f>(H7-D7)*24</f>
+        <v/>
+      </c>
+      <c r="L7" s="4">
+        <f>IF(C7="做多",I7/E7-1,1-I7/E7)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="19" t="n"/>
+      <c r="R7" s="19" t="n"/>
+      <c r="S7" s="4" t="n">
+        <v>0.01663764751402597</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>0.03965950860901524</v>
+      </c>
+      <c r="U7" s="16" t="n"/>
+      <c r="V7" s="16" t="n"/>
+      <c r="W7" s="4" t="n"/>
+      <c r="X7" s="4" t="n"/>
+      <c r="Y7" s="4" t="n"/>
+      <c r="Z7" s="4" t="n"/>
+      <c r="AA7" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB7" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC7" s="4">
+        <f>(AB7+2*參數!$B$7)/(AA7+AB7)</f>
+        <v/>
+      </c>
+      <c r="AD7" s="2" t="n">
+        <v>0.06299706990372544</v>
+      </c>
+      <c r="AE7" s="2" t="n">
+        <v>1.029561024149413</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>0.01412595644496761</v>
+      </c>
+      <c r="AG7" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG4"/>
-  <conditionalFormatting sqref="J2:J4">
+  <autoFilter ref="A1:AG7"/>
+  <conditionalFormatting sqref="J2:J7">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -4842,7 +5512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4928,27 +5598,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A2,交易明細!$C$2:$C$4,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A2,交易明細!$C$2:$C$7,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A2,交易明細!$C$2:$C$4,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A2,交易明細!$C$2:$C$7,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$4,$A2,交易明細!$J$2:$J$4,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$7,$A2,交易明細!$J$2:$J$7,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A2,交易明細!$J$2:$J$4,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A2,交易明細!$J$2:$J$7,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A2,交易明細!$J$2:$J$4,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A2,交易明細!$J$2:$J$7,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -4956,19 +5626,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$4,交易明細!$B$2:$B$4,$A2,交易明細!$J$2:$J$4,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A2,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$4,交易明細!$B$2:$B$4,$A2,交易明細!$J$2:$J$4,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A2,交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$4,交易明細!$B$2:$B$4,$A2,交易明細!$J$2:$J$4,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$B$2:$B$7,$A2,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A2,交易明細!$J$2:$J$4,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A2,交易明細!$J$2:$J$7,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -4979,27 +5649,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A3,交易明細!$C$2:$C$4,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A3,交易明細!$C$2:$C$7,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A3,交易明細!$C$2:$C$4,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A3,交易明細!$C$2:$C$7,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$4,$A3,交易明細!$J$2:$J$4,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$7,$A3,交易明細!$J$2:$J$7,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A3,交易明細!$J$2:$J$4,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A3,交易明細!$J$2:$J$7,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A3,交易明細!$J$2:$J$4,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A3,交易明細!$J$2:$J$7,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -5007,19 +5677,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$4,交易明細!$B$2:$B$4,$A3,交易明細!$J$2:$J$4,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A3,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$4,交易明細!$B$2:$B$4,$A3,交易明細!$J$2:$J$4,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A3,交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$4,交易明細!$B$2:$B$4,$A3,交易明細!$J$2:$J$4,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$B$2:$B$7,$A3,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A3,交易明細!$J$2:$J$4,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A3,交易明細!$J$2:$J$7,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -5030,27 +5700,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A4,交易明細!$C$2:$C$4,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A4,交易明細!$C$2:$C$7,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A4,交易明細!$C$2:$C$4,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A4,交易明細!$C$2:$C$7,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$4,$A4,交易明細!$J$2:$J$4,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$7,$A4,交易明細!$J$2:$J$7,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A4,交易明細!$J$2:$J$4,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A4,交易明細!$J$2:$J$7,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A4,交易明細!$J$2:$J$4,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A4,交易明細!$J$2:$J$7,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -5058,24 +5728,177 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$4,交易明細!$B$2:$B$4,$A4,交易明細!$J$2:$J$4,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A4,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$4,交易明細!$B$2:$B$4,$A4,交易明細!$J$2:$J$4,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A4,交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$4,交易明細!$B$2:$B$4,$A4,交易明細!$J$2:$J$4,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$B$2:$B$7,$A4,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$4,$A4,交易明細!$J$2:$J$4,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A4,交易明細!$J$2:$J$7,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>BROCCOLI_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B5" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A5)</f>
+        <v/>
+      </c>
+      <c r="C5" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A5,交易明細!$C$2:$C$7,"做多")</f>
+        <v/>
+      </c>
+      <c r="D5" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A5,交易明細!$C$2:$C$7,"做空")</f>
+        <v/>
+      </c>
+      <c r="E5" s="2">
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$7,$A5,交易明細!$J$2:$J$7,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F5" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A5,交易明細!$J$2:$J$7,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G5" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A5,交易明細!$J$2:$J$7,"止損")</f>
+        <v/>
+      </c>
+      <c r="H5" s="4">
+        <f>IFERROR(F5/E5,0)</f>
+        <v/>
+      </c>
+      <c r="I5" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A5,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J5" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A5,交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K5" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$B$2:$B$7,$A5,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L5" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A5,交易明細!$J$2:$J$7,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>AGT_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A6)</f>
+        <v/>
+      </c>
+      <c r="C6" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A6,交易明細!$C$2:$C$7,"做多")</f>
+        <v/>
+      </c>
+      <c r="D6" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A6,交易明細!$C$2:$C$7,"做空")</f>
+        <v/>
+      </c>
+      <c r="E6" s="2">
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$7,$A6,交易明細!$J$2:$J$7,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F6" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A6,交易明細!$J$2:$J$7,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G6" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A6,交易明細!$J$2:$J$7,"止損")</f>
+        <v/>
+      </c>
+      <c r="H6" s="4">
+        <f>IFERROR(F6/E6,0)</f>
+        <v/>
+      </c>
+      <c r="I6" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A6,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J6" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A6,交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K6" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$B$2:$B$7,$A6,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L6" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A6,交易明細!$J$2:$J$7,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>PHA_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B7" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A7)</f>
+        <v/>
+      </c>
+      <c r="C7" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A7,交易明細!$C$2:$C$7,"做多")</f>
+        <v/>
+      </c>
+      <c r="D7" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A7,交易明細!$C$2:$C$7,"做空")</f>
+        <v/>
+      </c>
+      <c r="E7" s="2">
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$7,$A7,交易明細!$J$2:$J$7,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F7" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A7,交易明細!$J$2:$J$7,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G7" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A7,交易明細!$J$2:$J$7,"止損")</f>
+        <v/>
+      </c>
+      <c r="H7" s="4">
+        <f>IFERROR(F7/E7,0)</f>
+        <v/>
+      </c>
+      <c r="I7" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A7,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J7" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A7,交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K7" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$B$2:$B$7,$A7,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L7" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$7,$A7,交易明細!$J$2:$J$7,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5368,7 +6191,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="17" t="n"/>
       <c r="F14" s="17" t="n"/>
@@ -10214,7 +11041,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C283" s="2" t="inlineStr"/>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D283" s="2" t="n"/>
       <c r="E283" s="17" t="n"/>
       <c r="F283" s="17" t="n"/>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,9 +17,9 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AG$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$11</f>
+              <f>'資金明細'!$R$2:$R$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-24 20:22（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-24 22:12（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -796,19 +796,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$7,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$5,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$7,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$5,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$7,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$5,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$7,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$5,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -816,35 +816,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$7,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$5,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$5,交易明細!$J$2:$J$5,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$J$2:$J$7,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$J$2:$J$5,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$J$2:$J$7,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$J$2:$J$5,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$J$2:$J$7,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$J$2:$J$5,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$7,"&lt;&gt;未平倉",交易明細!$L$2:$L$7,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$5,"&lt;&gt;未平倉",交易明細!$L$2:$L$5,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$7,"做多",交易明細!$B$2:$B$7,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$5,"做多",交易明細!$B$2:$B$5,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -863,19 +863,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -883,35 +883,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$7,交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$5,交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$5,交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$7,"做多",交易明細!$J$2:$J$7,"&lt;&gt;未平倉",交易明細!$L$2:$L$7,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"&lt;&gt;未平倉",交易明細!$L$2:$L$5,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$7,"做空",交易明細!$B$2:$B$7,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$5,"做空",交易明細!$B$2:$B$5,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -930,19 +930,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -950,35 +950,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$7,交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$5,交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$5,交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$7,"做空",交易明細!$J$2:$J$7,"&lt;&gt;未平倉",交易明細!$L$2:$L$7,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"&lt;&gt;未平倉",交易明細!$L$2:$L$5,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,33 +1086,33 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
@@ -1121,44 +1121,44 @@
         <v>3</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
@@ -1173,15 +1173,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
@@ -1196,15 +1196,15 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
@@ -1219,15 +1219,15 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
@@ -1242,15 +1242,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
@@ -1265,15 +1265,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
@@ -1285,18 +1285,18 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
@@ -1311,15 +1311,15 @@
         <v>2</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
@@ -1334,15 +1334,15 @@
         <v>2</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
@@ -1357,18 +1357,18 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
@@ -1380,15 +1380,15 @@
         <v>2</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>441</v>
@@ -1403,15 +1403,15 @@
         <v>2</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>441</v>
@@ -1426,15 +1426,15 @@
         <v>2</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>441</v>
@@ -1449,18 +1449,18 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0</v>
@@ -1469,18 +1469,18 @@
         <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>440</v>
@@ -1495,15 +1495,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>440</v>
@@ -1518,15 +1518,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>440</v>
@@ -1541,15 +1541,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>440</v>
@@ -1564,15 +1564,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>440</v>
@@ -1587,15 +1587,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>440</v>
@@ -1610,15 +1610,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>440</v>
@@ -1633,15 +1633,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>440</v>
@@ -1656,15 +1656,15 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>440</v>
@@ -1679,15 +1679,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>440</v>
@@ -1702,15 +1702,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>440</v>
@@ -1725,15 +1725,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>440</v>
@@ -1748,15 +1748,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>440</v>
@@ -1771,15 +1771,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>440</v>
@@ -1794,15 +1794,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,18 +2507,18 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>0</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>442</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>442</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>442</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>442</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>442</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>442</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>442</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>442</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>442</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>442</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>442</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>442</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>442</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>442</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,6 +2967,29 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3032,7 +3055,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R11</f>
+        <f>資金明細!R9</f>
         <v/>
       </c>
     </row>
@@ -3070,7 +3093,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$11)</f>
+        <f>MAX(資金明細!$R$2:$R$9)</f>
         <v/>
       </c>
     </row>
@@ -3089,7 +3112,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$11)</f>
+        <f>MIN(資金明細!$R$2:$R$9)</f>
         <v/>
       </c>
     </row>
@@ -3109,7 +3132,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$11)</f>
+        <f>MIN(資金明細!$X$2:$X$9)</f>
         <v/>
       </c>
     </row>
@@ -3128,7 +3151,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$11,"進場",資金明細!$N$2:$N$11,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$9,"進場",資金明細!$N$2:$N$9,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3170,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$11,"進場",資金明細!$N$2:$N$11,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$9,"進場",資金明細!$N$2:$N$9,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3158,7 +3181,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$11,"出場",資金明細!$N$2:$N$11,"已下單",資金明細!$K$2:$K$11,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$9,"出場",資金明細!$N$2:$N$9,"已下單",資金明細!$K$2:$K$9,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3169,7 +3192,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$7),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$5),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3178,7 +3201,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$11,"出場",資金明細!$N$2:$N$11,"已下單",資金明細!$K$2:$K$11,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$9,"出場",資金明細!$N$2:$N$9,"已下單",資金明細!$K$2:$K$9,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3194,7 +3217,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$11,"出場",資金明細!$N$2:$N$11,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$9,"出場",資金明細!$N$2:$N$9,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3210,7 +3233,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$11)</f>
+        <f>MAX(資金明細!$U$2:$U$9)</f>
         <v/>
       </c>
     </row>
@@ -3226,7 +3249,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$11)</f>
+        <f>MAX(資金明細!$S$2:$S$9)</f>
         <v/>
       </c>
     </row>
@@ -3237,7 +3260,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V11</f>
+        <f>B5*資金明細!V9</f>
         <v/>
       </c>
     </row>
@@ -3248,7 +3271,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N3="已下單",資金明細!O3*交易明細!L2,0)+IF(資金明細!N10="已下單",資金明細!O10*交易明細!L6,0)+IF(資金明細!N11="已下單",資金明細!O11*交易明細!L7,0)</f>
+        <f>IF(資金明細!N6="已下單",資金明細!O6*交易明細!L4,0)</f>
         <v/>
       </c>
     </row>
@@ -3259,7 +3282,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$11)</f>
+        <f>MAX(資金明細!$Y$2:$Y$9)</f>
         <v/>
       </c>
     </row>
@@ -3281,7 +3304,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$11,MATCH(1,資金明細!$Z$2:$Z$11,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$9,MATCH(1,資金明細!$Z$2:$Z$9,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3292,7 +3315,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$11,"進場",資金明細!$N$2:$N$11,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$9,"進場",資金明細!$N$2:$N$9,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3357,7 +3380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3583,7 +3606,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46289.48125</v>
+        <v>46289.59513888889</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -3595,7 +3618,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>LTC_USDT_PERP</t>
+          <t>NOM_USDT_PERP</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -3604,20 +3627,16 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>66.56</v>
+        <v>0.002779</v>
       </c>
       <c r="H3" s="17" t="n">
-        <v>64.56319999999999</v>
+        <v>0.00269563</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>69.88800000000001</v>
+        <v>0.00291795</v>
       </c>
       <c r="J3" s="17" t="n"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K3" s="2" t="n"/>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="16">
         <f>資金模擬!$B$5*V2</f>
@@ -3677,19 +3696,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46289.56458333333</v>
+        <v>46289.6</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>進場</t>
+          <t>出場</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>NIL_USDT_PERP</t>
+          <t>NOM_USDT_PERP</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -3698,39 +3717,52 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.14786</v>
+        <v>0.002779</v>
       </c>
       <c r="H4" s="17" t="n">
-        <v>0.1434242</v>
+        <v>0.00269563</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.155253</v>
-      </c>
-      <c r="J4" s="17" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="5" t="n"/>
+        <v>0.00291795</v>
+      </c>
+      <c r="J4" s="17" t="n">
+        <v>0.00269563</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L4" s="5">
+        <f>交易明細!K2</f>
+        <v/>
+      </c>
       <c r="M4" s="16">
-        <f>資金模擬!$B$5*V3</f>
+        <f>M3</f>
         <v/>
       </c>
       <c r="N4" s="2">
-        <f>IF(Z3=1,"已停止",IF(T3&gt;=M4,"已下單","資金不足略過"))</f>
+        <f>N3</f>
         <v/>
       </c>
       <c r="O4" s="16">
-        <f>IF(N4="已下單",M4*資金模擬!$B$7,0)</f>
-        <v/>
-      </c>
-      <c r="P4" s="4" t="n"/>
-      <c r="Q4" s="10" t="n">
-        <v>0</v>
+        <f>O3</f>
+        <v/>
+      </c>
+      <c r="P4" s="4">
+        <f>交易明細!L2</f>
+        <v/>
+      </c>
+      <c r="Q4" s="10">
+        <f>IF(N4="已下單",O4*P4,0)</f>
+        <v/>
       </c>
       <c r="R4" s="10">
         <f>R3+Q4</f>
         <v/>
       </c>
       <c r="S4" s="16">
-        <f>S3+IF(N4="已下單",M4,0)</f>
+        <f>S3-IF(N4="已下單",M4,0)</f>
         <v/>
       </c>
       <c r="T4" s="16">
@@ -3738,7 +3770,7 @@
         <v/>
       </c>
       <c r="U4" s="2">
-        <f>U3+IF(N4="已下單",1,0)</f>
+        <f>U3-IF(N4="已下單",1,0)</f>
         <v/>
       </c>
       <c r="V4" s="16">
@@ -3767,11 +3799,11 @@
         <v>3</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46289.56666666667</v>
+        <v>46289.8</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>出場</t>
+          <t>進場</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -3779,7 +3811,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>NIL_USDT_PERP</t>
+          <t>BROCCOLI_USDT_PERP</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3788,52 +3820,39 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.14786</v>
+        <v>0.02867</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>0.1434242</v>
+        <v>0.0278099</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.155253</v>
-      </c>
-      <c r="J5" s="17" t="n">
-        <v>0.1434242</v>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>止盈</t>
-        </is>
-      </c>
-      <c r="L5" s="5">
-        <f>交易明細!K3</f>
-        <v/>
-      </c>
+        <v>0.0301035</v>
+      </c>
+      <c r="J5" s="17" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="5" t="n"/>
       <c r="M5" s="16">
-        <f>M4</f>
+        <f>資金模擬!$B$5*V4</f>
         <v/>
       </c>
       <c r="N5" s="2">
-        <f>N4</f>
+        <f>IF(Z4=1,"已停止",IF(T4&gt;=M5,"已下單","資金不足略過"))</f>
         <v/>
       </c>
       <c r="O5" s="16">
-        <f>O4</f>
-        <v/>
-      </c>
-      <c r="P5" s="4">
-        <f>交易明細!L3</f>
-        <v/>
-      </c>
-      <c r="Q5" s="10">
-        <f>IF(N5="已下單",O5*P5,0)</f>
-        <v/>
+        <f>IF(N5="已下單",M5*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="R5" s="10">
         <f>R4+Q5</f>
         <v/>
       </c>
       <c r="S5" s="16">
-        <f>S4-IF(N5="已下單",M5,0)</f>
+        <f>S4+IF(N5="已下單",M5,0)</f>
         <v/>
       </c>
       <c r="T5" s="16">
@@ -3841,7 +3860,7 @@
         <v/>
       </c>
       <c r="U5" s="2">
-        <f>U4-IF(N5="已下單",1,0)</f>
+        <f>U4+IF(N5="已下單",1,0)</f>
         <v/>
       </c>
       <c r="V5" s="16">
@@ -3870,7 +3889,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46289.59722222222</v>
+        <v>46289.81041666667</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -3882,7 +3901,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>NOM_USDT_PERP</t>
+          <t>AGT_USDT_PERP</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -3891,16 +3910,20 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.002764</v>
+        <v>0.019584</v>
       </c>
       <c r="H6" s="17" t="n">
-        <v>0.00268108</v>
+        <v>0.01899648</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>0.0029022</v>
+        <v>0.0205632</v>
       </c>
       <c r="J6" s="17" t="n"/>
-      <c r="K6" s="2" t="n"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="16">
         <f>資金模擬!$B$5*V5</f>
@@ -3960,19 +3983,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46289.61944444444</v>
+        <v>46289.83541666667</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>出場</t>
+          <t>進場</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>NOM_USDT_PERP</t>
+          <t>PHA_USDT_PERP</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3981,52 +4004,39 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>0.002764</v>
+        <v>0.05098</v>
       </c>
       <c r="H7" s="17" t="n">
-        <v>0.00268108</v>
+        <v>0.0494506</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>0.0029022</v>
-      </c>
-      <c r="J7" s="17" t="n">
-        <v>0.00268108</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>止盈</t>
-        </is>
-      </c>
-      <c r="L7" s="5">
-        <f>交易明細!K4</f>
-        <v/>
-      </c>
+        <v>0.053529</v>
+      </c>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="5" t="n"/>
       <c r="M7" s="16">
-        <f>M6</f>
+        <f>資金模擬!$B$5*V6</f>
         <v/>
       </c>
       <c r="N7" s="2">
-        <f>N6</f>
+        <f>IF(Z6=1,"已停止",IF(T6&gt;=M7,"已下單","資金不足略過"))</f>
         <v/>
       </c>
       <c r="O7" s="16">
-        <f>O6</f>
-        <v/>
-      </c>
-      <c r="P7" s="4">
-        <f>交易明細!L4</f>
-        <v/>
-      </c>
-      <c r="Q7" s="10">
-        <f>IF(N7="已下單",O7*P7,0)</f>
-        <v/>
+        <f>IF(N7="已下單",M7*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="R7" s="10">
         <f>R6+Q7</f>
         <v/>
       </c>
       <c r="S7" s="16">
-        <f>S6-IF(N7="已下單",M7,0)</f>
+        <f>S6+IF(N7="已下單",M7,0)</f>
         <v/>
       </c>
       <c r="T7" s="16">
@@ -4034,7 +4044,7 @@
         <v/>
       </c>
       <c r="U7" s="2">
-        <f>U6-IF(N7="已下單",1,0)</f>
+        <f>U6+IF(N7="已下單",1,0)</f>
         <v/>
       </c>
       <c r="V7" s="16">
@@ -4063,11 +4073,11 @@
         <v>6</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46289.80486111111</v>
+        <v>46289.84652777778</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>進場</t>
+          <t>出場</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -4075,7 +4085,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>BROCCOLI_USDT_PERP</t>
+          <t>PHA_USDT_PERP</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4084,39 +4094,52 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>0.02962</v>
+        <v>0.05098</v>
       </c>
       <c r="H8" s="17" t="n">
-        <v>0.0287314</v>
+        <v>0.0494506</v>
       </c>
       <c r="I8" s="17" t="n">
-        <v>0.031101</v>
-      </c>
-      <c r="J8" s="17" t="n"/>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="5" t="n"/>
+        <v>0.053529</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>0.053529</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L8" s="5">
+        <f>交易明細!K5</f>
+        <v/>
+      </c>
       <c r="M8" s="16">
-        <f>資金模擬!$B$5*V7</f>
+        <f>M7</f>
         <v/>
       </c>
       <c r="N8" s="2">
-        <f>IF(Z7=1,"已停止",IF(T7&gt;=M8,"已下單","資金不足略過"))</f>
+        <f>N7</f>
         <v/>
       </c>
       <c r="O8" s="16">
-        <f>IF(N8="已下單",M8*資金模擬!$B$7,0)</f>
-        <v/>
-      </c>
-      <c r="P8" s="4" t="n"/>
-      <c r="Q8" s="10" t="n">
-        <v>0</v>
+        <f>O7</f>
+        <v/>
+      </c>
+      <c r="P8" s="4">
+        <f>交易明細!L5</f>
+        <v/>
+      </c>
+      <c r="Q8" s="10">
+        <f>IF(N8="已下單",O8*P8,0)</f>
+        <v/>
       </c>
       <c r="R8" s="10">
         <f>R7+Q8</f>
         <v/>
       </c>
       <c r="S8" s="16">
-        <f>S7+IF(N8="已下單",M8,0)</f>
+        <f>S7-IF(N8="已下單",M8,0)</f>
         <v/>
       </c>
       <c r="T8" s="16">
@@ -4124,7 +4147,7 @@
         <v/>
       </c>
       <c r="U8" s="2">
-        <f>U7+IF(N8="已下單",1,0)</f>
+        <f>U7-IF(N8="已下單",1,0)</f>
         <v/>
       </c>
       <c r="V8" s="16">
@@ -4153,7 +4176,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46289.80902777778</v>
+        <v>46289.85347222222</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -4161,7 +4184,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -4174,40 +4197,40 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.02962</v>
+        <v>0.02867</v>
       </c>
       <c r="H9" s="17" t="n">
-        <v>0.0287314</v>
+        <v>0.0278099</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.031101</v>
+        <v>0.0301035</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>0.0287314</v>
+        <v>0.0301035</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>止盈</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="L9" s="5">
-        <f>交易明細!K5</f>
+        <f>交易明細!K3</f>
         <v/>
       </c>
       <c r="M9" s="16">
-        <f>M8</f>
+        <f>M5</f>
         <v/>
       </c>
       <c r="N9" s="2">
-        <f>N8</f>
+        <f>N5</f>
         <v/>
       </c>
       <c r="O9" s="16">
-        <f>O8</f>
+        <f>O5</f>
         <v/>
       </c>
       <c r="P9" s="4">
-        <f>交易明細!L5</f>
+        <f>交易明細!L3</f>
         <v/>
       </c>
       <c r="Q9" s="10">
@@ -4251,197 +4274,9 @@
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>46289.81041666667</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>進場</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>AGT_USDT_PERP</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>做空</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="n">
-        <v>0.019584</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>0.01899648</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>0.0205632</v>
-      </c>
-      <c r="J10" s="17" t="n"/>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="16">
-        <f>資金模擬!$B$5*V9</f>
-        <v/>
-      </c>
-      <c r="N10" s="2">
-        <f>IF(Z9=1,"已停止",IF(T9&gt;=M10,"已下單","資金不足略過"))</f>
-        <v/>
-      </c>
-      <c r="O10" s="16">
-        <f>IF(N10="已下單",M10*資金模擬!$B$7,0)</f>
-        <v/>
-      </c>
-      <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="10">
-        <f>R9+Q10</f>
-        <v/>
-      </c>
-      <c r="S10" s="16">
-        <f>S9+IF(N10="已下單",M10,0)</f>
-        <v/>
-      </c>
-      <c r="T10" s="16">
-        <f>R10-S10</f>
-        <v/>
-      </c>
-      <c r="U10" s="2">
-        <f>U9+IF(N10="已下單",1,0)</f>
-        <v/>
-      </c>
-      <c r="V10" s="16">
-        <f>IF(資金模擬!$B$9=2,MAX(R10,0),MAX(V9,FLOOR(MAX(R10,0),資金模擬!$B$6)))</f>
-        <v/>
-      </c>
-      <c r="W10" s="10">
-        <f>MAX(W9,R10)</f>
-        <v/>
-      </c>
-      <c r="X10" s="4">
-        <f>IF(W10&gt;0,R10/W10-1,-1)</f>
-        <v/>
-      </c>
-      <c r="Y10" s="16">
-        <f>IF(R10&gt;0,S10*資金模擬!$B$7/R10,0)</f>
-        <v/>
-      </c>
-      <c r="Z10" s="2">
-        <f>IF(OR(Z9=1,R10&lt;=資金模擬!$B$10),1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>46289.83611111111</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>進場</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>PHA_USDT_PERP</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>做空</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="n">
-        <v>0.05169</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>0.0501393</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>0.0542745</v>
-      </c>
-      <c r="J11" s="17" t="n"/>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="16">
-        <f>資金模擬!$B$5*V10</f>
-        <v/>
-      </c>
-      <c r="N11" s="2">
-        <f>IF(Z10=1,"已停止",IF(T10&gt;=M11,"已下單","資金不足略過"))</f>
-        <v/>
-      </c>
-      <c r="O11" s="16">
-        <f>IF(N11="已下單",M11*資金模擬!$B$7,0)</f>
-        <v/>
-      </c>
-      <c r="P11" s="4" t="n"/>
-      <c r="Q11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="10">
-        <f>R10+Q11</f>
-        <v/>
-      </c>
-      <c r="S11" s="16">
-        <f>S10+IF(N11="已下單",M11,0)</f>
-        <v/>
-      </c>
-      <c r="T11" s="16">
-        <f>R11-S11</f>
-        <v/>
-      </c>
-      <c r="U11" s="2">
-        <f>U10+IF(N11="已下單",1,0)</f>
-        <v/>
-      </c>
-      <c r="V11" s="16">
-        <f>IF(資金模擬!$B$9=2,MAX(R11,0),MAX(V10,FLOOR(MAX(R11,0),資金模擬!$B$6)))</f>
-        <v/>
-      </c>
-      <c r="W11" s="10">
-        <f>MAX(W10,R11)</f>
-        <v/>
-      </c>
-      <c r="X11" s="4">
-        <f>IF(W11&gt;0,R11/W11-1,-1)</f>
-        <v/>
-      </c>
-      <c r="Y11" s="16">
-        <f>IF(R11&gt;0,S11*資金模擬!$B$7/R11,0)</f>
-        <v/>
-      </c>
-      <c r="Z11" s="2">
-        <f>IF(OR(Z10=1,R11&lt;=資金模擬!$B$10),1,0)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Z11"/>
-  <conditionalFormatting sqref="K2:K11">
+  <autoFilter ref="A1:Z9"/>
+  <conditionalFormatting sqref="K2:K9">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -4449,7 +4284,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N11">
+  <conditionalFormatting sqref="N2:N9">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -4457,7 +4292,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q11">
+  <conditionalFormatting sqref="Q2:Q9">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -4522,7 +4357,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-24 20:22（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-24 22:12（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -4613,7 +4448,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>① 前根收盤比最低點漲</t>
+          <t>① 前根收盤比開盤漲</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -4621,71 +4456,73 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>前一根 1h K：收盤 ÷ 最低 − 1</t>
+          <t>前一根 1h K：收盤 ÷ 開盤 − 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>② 當根量 ÷ 前一根量</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>1</v>
+          <t>②A 當根量 ÷ 前一根量</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2 倍</t>
+        </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>本小時到目前為止的累計量；1.0 = 持平</t>
+          <t>本小時到目前為止的累計量，不限時；A 與限時分支符合任一即可</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>③ 現價 &gt; 前高 ×</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>1</v>
+          <t>② 限時分支</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>30 分內 ≥ 1 倍、15 分內 ≥ 0.5 倍</t>
+        </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>現價 = 那根 1 分K 收盤價</t>
+          <t>開盤 N 分內（1 分K 收盤 ≤ 第 N 分）累計量曾達門檻，成立後本小時都算（黏著）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>進場時機</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>三條件第一次同時成立</t>
-        </is>
+          <t>③ 現價 &gt; 前高 ×</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>以那根 1 分K 收盤價進場；同幣每小時最多一次</t>
+          <t>現價 = 那根 1 分K 收盤價</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>持倉中</t>
+          <t>進場時機</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>不重複進場</t>
+          <t>三條件第一次同時成立</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>與群組機器人一致</t>
+          <t>以那根 1 分K 收盤價進場；同幣每小時最多一次；持倉中不重複進場（與群組機器人一致）</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4567,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$7),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$5),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4756,7 +4593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG7"/>
+  <dimension ref="A1:AH5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4790,8 +4627,9 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4942,7 +4780,7 @@
       </c>
       <c r="AD1" s="3" t="inlineStr">
         <is>
-          <t>① 前根收盤比最低</t>
+          <t>① 前根收盤比開盤</t>
         </is>
       </c>
       <c r="AE1" s="3" t="inlineStr">
@@ -4952,10 +4790,15 @@
       </c>
       <c r="AF1" s="3" t="inlineStr">
         <is>
+          <t>② 爆量分支</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
           <t>③ 進場價vs前高</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>觸發於第幾分鐘</t>
         </is>
@@ -4967,7 +4810,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>LTC_USDT_PERP</t>
+          <t>NOM_USDT_PERP</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -4976,26 +4819,26 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>46289.48125</v>
+        <v>46289.59513888889</v>
       </c>
       <c r="E2" s="17" t="n">
-        <v>66.56</v>
+        <v>0.002779</v>
       </c>
       <c r="F2" s="17" t="n">
-        <v>64.56319999999999</v>
+        <v>0.00269563</v>
       </c>
       <c r="G2" s="17" t="n">
-        <v>69.88800000000001</v>
+        <v>0.00291795</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>46289.84861111111</v>
+        <v>46289.6</v>
       </c>
       <c r="I2" s="17" t="n">
-        <v>65.88</v>
+        <v>0.00269563</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K2" s="5">
@@ -5006,21 +4849,17 @@
         <f>IF(C2="做多",I2/E2-1,1-I2/E2)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="19" t="n"/>
       <c r="R2" s="19" t="n"/>
       <c r="S2" s="4" t="n">
-        <v>0.01532451923076916</v>
+        <v>0.03</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>0.04371995192307687</v>
+        <v>0.01187477509895651</v>
       </c>
       <c r="U2" s="16" t="n"/>
       <c r="V2" s="16" t="n"/>
@@ -5039,16 +4878,21 @@
         <v/>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>0.06561892417368753</v>
+        <v>0.1595698924731184</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>1.126257067506423</v>
-      </c>
-      <c r="AF2" s="2" t="n">
-        <v>0.007263922518159882</v>
+        <v>0.7901093245305789</v>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>15分0.5倍</t>
+        </is>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>33</v>
+        <v>0.00761421319796951</v>
+      </c>
+      <c r="AH2" s="2" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -5057,7 +4901,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>NIL_USDT_PERP</t>
+          <t>BROCCOLI_USDT_PERP</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5066,26 +4910,26 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>46289.56458333333</v>
+        <v>46289.8</v>
       </c>
       <c r="E3" s="17" t="n">
-        <v>0.14786</v>
+        <v>0.02867</v>
       </c>
       <c r="F3" s="17" t="n">
-        <v>0.1434242</v>
+        <v>0.0278099</v>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.155253</v>
+        <v>0.0301035</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>46289.56666666667</v>
+        <v>46289.85347222222</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>0.1434242</v>
+        <v>0.0301035</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>止盈</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="K3" s="5">
@@ -5103,10 +4947,10 @@
       <c r="Q3" s="19" t="n"/>
       <c r="R3" s="19" t="n"/>
       <c r="S3" s="4" t="n">
-        <v>0.03</v>
+        <v>0.02790373212417163</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>0.009130258352495702</v>
+        <v>0.05</v>
       </c>
       <c r="U3" s="16" t="n"/>
       <c r="V3" s="16" t="n"/>
@@ -5125,16 +4969,21 @@
         <v/>
       </c>
       <c r="AD3" s="2" t="n">
-        <v>0.06385775028991114</v>
+        <v>0.1203369434416366</v>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>1.018164810320387</v>
-      </c>
-      <c r="AF3" s="2" t="n">
-        <v>0.06642625315542738</v>
+        <v>0.6219296190108617</v>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>15分0.5倍</t>
+        </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>33</v>
+        <v>0.007378777231201727</v>
+      </c>
+      <c r="AH3" s="2" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -5143,7 +4992,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>NOM_USDT_PERP</t>
+          <t>AGT_USDT_PERP</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -5152,26 +5001,26 @@
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>46289.59722222222</v>
+        <v>46289.81041666667</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>0.002764</v>
+        <v>0.019584</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>0.00268108</v>
+        <v>0.01899648</v>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.0029022</v>
+        <v>0.0205632</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>46289.61944444444</v>
+        <v>46289.925</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.00268108</v>
+        <v>0.019568</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>止盈</t>
+          <t>未平倉</t>
         </is>
       </c>
       <c r="K4" s="5">
@@ -5182,17 +5031,21 @@
         <f>IF(C4="做多",I4/E4-1,1-I4/E4)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
       <c r="N4" s="4" t="n"/>
       <c r="O4" s="4" t="n"/>
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="19" t="n"/>
       <c r="R4" s="19" t="n"/>
       <c r="S4" s="4" t="n">
-        <v>0.03</v>
+        <v>0.02236519607843146</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>0.006874095513748069</v>
+        <v>0.01710580065359468</v>
       </c>
       <c r="U4" s="16" t="n"/>
       <c r="V4" s="16" t="n"/>
@@ -5211,16 +5064,21 @@
         <v/>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>0.1650821089023335</v>
+        <v>0.06028797537920427</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>1.032123561080855</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>0.002175489485134019</v>
+        <v>1.019097229886326</v>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>30分1倍</t>
+        </is>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>20</v>
+        <v>0.01329745951259897</v>
+      </c>
+      <c r="AH4" s="2" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -5229,7 +5087,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>BROCCOLI_USDT_PERP</t>
+          <t>PHA_USDT_PERP</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5238,26 +5096,26 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>46289.80486111111</v>
+        <v>46289.83541666667</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>0.02962</v>
+        <v>0.05098</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>0.0287314</v>
+        <v>0.0494506</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.031101</v>
+        <v>0.053529</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>46289.80902777778</v>
+        <v>46289.84652777778</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.0287314</v>
+        <v>0.053529</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>止盈</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="K5" s="5">
@@ -5275,10 +5133,10 @@
       <c r="Q5" s="19" t="n"/>
       <c r="R5" s="19" t="n"/>
       <c r="S5" s="4" t="n">
-        <v>0.03</v>
+        <v>0.002942330325617859</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>0.006752194463200523</v>
+        <v>0.05</v>
       </c>
       <c r="U5" s="16" t="n"/>
       <c r="V5" s="16" t="n"/>
@@ -5297,201 +5155,26 @@
         <v/>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>0.1207865168539326</v>
+        <v>0.06299706990372544</v>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>1.057180369253066</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>0.04075895994378076</v>
+        <v>0.7304297906540625</v>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>15分0.5倍</t>
+        </is>
       </c>
       <c r="AG5" s="2" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>AGT_USDT_PERP</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>做空</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>46289.81041666667</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>0.019584</v>
-      </c>
-      <c r="F6" s="17" t="n">
-        <v>0.01899648</v>
-      </c>
-      <c r="G6" s="17" t="n">
-        <v>0.0205632</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>46289.84861111111</v>
-      </c>
-      <c r="I6" s="17" t="n">
-        <v>0.019687</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
-      <c r="K6" s="5">
-        <f>(H6-D6)*24</f>
-        <v/>
-      </c>
-      <c r="L6" s="4">
-        <f>IF(C6="做多",I6/E6-1,1-I6/E6)-2*參數!$B$7</f>
-        <v/>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n"/>
-      <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="19" t="n"/>
-      <c r="R6" s="19" t="n"/>
-      <c r="S6" s="4" t="n">
-        <v>0.006995506535947826</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>0.01710580065359468</v>
-      </c>
-      <c r="U6" s="16" t="n"/>
-      <c r="V6" s="16" t="n"/>
-      <c r="W6" s="4" t="n"/>
-      <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="4" t="n"/>
-      <c r="Z6" s="4" t="n"/>
-      <c r="AA6" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AB6" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AC6" s="4">
-        <f>(AB6+2*參數!$B$7)/(AA6+AB6)</f>
-        <v/>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.06028797537920427</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>1.019097229886326</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>0.01329745951259897</v>
-      </c>
-      <c r="AG6" s="2" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>PHA_USDT_PERP</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>做空</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>46289.83611111111</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>0.05169</v>
-      </c>
-      <c r="F7" s="17" t="n">
-        <v>0.0501393</v>
-      </c>
-      <c r="G7" s="17" t="n">
-        <v>0.0542745</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>46289.84861111111</v>
-      </c>
-      <c r="I7" s="17" t="n">
-        <v>0.05308</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
-      <c r="K7" s="5">
-        <f>(H7-D7)*24</f>
-        <v/>
-      </c>
-      <c r="L7" s="4">
-        <f>IF(C7="做多",I7/E7-1,1-I7/E7)-2*參數!$B$7</f>
-        <v/>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
-      <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="19" t="n"/>
-      <c r="R7" s="19" t="n"/>
-      <c r="S7" s="4" t="n">
-        <v>0.01663764751402597</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>0.03965950860901524</v>
-      </c>
-      <c r="U7" s="16" t="n"/>
-      <c r="V7" s="16" t="n"/>
-      <c r="W7" s="4" t="n"/>
-      <c r="X7" s="4" t="n"/>
-      <c r="Y7" s="4" t="n"/>
-      <c r="Z7" s="4" t="n"/>
-      <c r="AA7" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AB7" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AC7" s="4">
-        <f>(AB7+2*參數!$B$7)/(AA7+AB7)</f>
-        <v/>
-      </c>
-      <c r="AD7" s="2" t="n">
-        <v>0.06299706990372544</v>
-      </c>
-      <c r="AE7" s="2" t="n">
-        <v>1.029561024149413</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>0.01412595644496761</v>
-      </c>
-      <c r="AG7" s="2" t="n">
-        <v>4</v>
+        <v>0.0001961938395134144</v>
+      </c>
+      <c r="AH5" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG7"/>
-  <conditionalFormatting sqref="J2:J7">
+  <autoFilter ref="A1:AH5"/>
+  <conditionalFormatting sqref="J2:J5">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -5512,7 +5195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5594,31 +5277,31 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LTC_USDT_PERP</t>
+          <t>NOM_USDT_PERP</t>
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A2,交易明細!$C$2:$C$7,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A2,交易明細!$C$2:$C$5,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A2,交易明細!$C$2:$C$7,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A2,交易明細!$C$2:$C$5,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$7,$A2,交易明細!$J$2:$J$7,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$5,$A2,交易明細!$J$2:$J$5,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A2,交易明細!$J$2:$J$7,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A2,交易明細!$J$2:$J$5,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A2,交易明細!$J$2:$J$7,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A2,交易明細!$J$2:$J$5,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -5626,50 +5309,50 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A2,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A2,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A2,交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A2,交易明細!$J$2:$J$5,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$B$2:$B$7,$A2,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$B$2:$B$5,$A2,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A2,交易明細!$J$2:$J$7,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A2,交易明細!$J$2:$J$5,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>NIL_USDT_PERP</t>
+          <t>BROCCOLI_USDT_PERP</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A3,交易明細!$C$2:$C$7,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A3,交易明細!$C$2:$C$5,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A3,交易明細!$C$2:$C$7,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A3,交易明細!$C$2:$C$5,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$7,$A3,交易明細!$J$2:$J$7,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$5,$A3,交易明細!$J$2:$J$5,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A3,交易明細!$J$2:$J$7,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A3,交易明細!$J$2:$J$5,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A3,交易明細!$J$2:$J$7,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A3,交易明細!$J$2:$J$5,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -5677,50 +5360,50 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A3,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A3,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A3,交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A3,交易明細!$J$2:$J$5,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$B$2:$B$7,$A3,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$B$2:$B$5,$A3,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A3,交易明細!$J$2:$J$7,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A3,交易明細!$J$2:$J$5,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NOM_USDT_PERP</t>
+          <t>AGT_USDT_PERP</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A4,交易明細!$C$2:$C$7,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A4,交易明細!$C$2:$C$5,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A4,交易明細!$C$2:$C$7,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A4,交易明細!$C$2:$C$5,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$7,$A4,交易明細!$J$2:$J$7,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$5,$A4,交易明細!$J$2:$J$5,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A4,交易明細!$J$2:$J$7,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A4,交易明細!$J$2:$J$5,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A4,交易明細!$J$2:$J$7,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A4,交易明細!$J$2:$J$5,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -5728,50 +5411,50 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A4,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A4,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A4,交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A4,交易明細!$J$2:$J$5,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$B$2:$B$7,$A4,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$B$2:$B$5,$A4,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A4,交易明細!$J$2:$J$7,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A4,交易明細!$J$2:$J$5,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BROCCOLI_USDT_PERP</t>
+          <t>PHA_USDT_PERP</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A5,交易明細!$C$2:$C$7,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A5,交易明細!$C$2:$C$5,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A5,交易明細!$C$2:$C$7,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A5,交易明細!$C$2:$C$5,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$7,$A5,交易明細!$J$2:$J$7,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$5,$A5,交易明細!$J$2:$J$5,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A5,交易明細!$J$2:$J$7,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A5,交易明細!$J$2:$J$5,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A5,交易明細!$J$2:$J$7,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A5,交易明細!$J$2:$J$5,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -5779,126 +5462,24 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A5,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A5,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A5,交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A5,交易明細!$J$2:$J$5,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$B$2:$B$7,$A5,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$B$2:$B$5,$A5,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A5,交易明細!$J$2:$J$7,"未平倉")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>AGT_USDT_PERP</t>
-        </is>
-      </c>
-      <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A6)</f>
-        <v/>
-      </c>
-      <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A6,交易明細!$C$2:$C$7,"做多")</f>
-        <v/>
-      </c>
-      <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A6,交易明細!$C$2:$C$7,"做空")</f>
-        <v/>
-      </c>
-      <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$7,$A6,交易明細!$J$2:$J$7,"時間出場")</f>
-        <v/>
-      </c>
-      <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A6,交易明細!$J$2:$J$7,"止盈")</f>
-        <v/>
-      </c>
-      <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A6,交易明細!$J$2:$J$7,"止損")</f>
-        <v/>
-      </c>
-      <c r="H6" s="4">
-        <f>IFERROR(F6/E6,0)</f>
-        <v/>
-      </c>
-      <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A6,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
-        <v/>
-      </c>
-      <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A6,交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
-        <v/>
-      </c>
-      <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$B$2:$B$7,$A6,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
-        <v/>
-      </c>
-      <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A6,交易明細!$J$2:$J$7,"未平倉")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>PHA_USDT_PERP</t>
-        </is>
-      </c>
-      <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A7)</f>
-        <v/>
-      </c>
-      <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A7,交易明細!$C$2:$C$7,"做多")</f>
-        <v/>
-      </c>
-      <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A7,交易明細!$C$2:$C$7,"做空")</f>
-        <v/>
-      </c>
-      <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$7,$A7,交易明細!$J$2:$J$7,"時間出場")</f>
-        <v/>
-      </c>
-      <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A7,交易明細!$J$2:$J$7,"止盈")</f>
-        <v/>
-      </c>
-      <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A7,交易明細!$J$2:$J$7,"止損")</f>
-        <v/>
-      </c>
-      <c r="H7" s="4">
-        <f>IFERROR(F7/E7,0)</f>
-        <v/>
-      </c>
-      <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A7,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
-        <v/>
-      </c>
-      <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$7,交易明細!$B$2:$B$7,$A7,交易明細!$J$2:$J$7,"&lt;&gt;未平倉")</f>
-        <v/>
-      </c>
-      <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$7,交易明細!$B$2:$B$7,$A7,交易明細!$J$2:$J$7,"&lt;&gt;未平倉"),0)</f>
-        <v/>
-      </c>
-      <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$7,$A7,交易明細!$J$2:$J$7,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$5,$A5,交易明細!$J$2:$J$5,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L7"/>
+  <autoFilter ref="A1:L5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9867,11 +9448,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C218" s="2" t="inlineStr"/>
       <c r="D218" s="2" t="n"/>
       <c r="E218" s="17" t="n"/>
       <c r="F218" s="17" t="n"/>
@@ -11041,11 +10618,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C283" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C283" s="2" t="inlineStr"/>
       <c r="D283" s="2" t="n"/>
       <c r="E283" s="17" t="n"/>
       <c r="F283" s="17" t="n"/>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-24 22:12（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-24 22:35（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,56 +1086,56 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
@@ -1144,44 +1144,44 @@
         <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
@@ -1196,15 +1196,15 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
@@ -1219,15 +1219,15 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
@@ -1242,15 +1242,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
@@ -1265,15 +1265,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
@@ -1288,15 +1288,15 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
@@ -1308,18 +1308,18 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
@@ -1334,15 +1334,15 @@
         <v>2</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
@@ -1357,15 +1357,15 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
@@ -1380,18 +1380,18 @@
         <v>2</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0</v>
@@ -1403,15 +1403,15 @@
         <v>2</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>441</v>
@@ -1426,15 +1426,15 @@
         <v>2</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>441</v>
@@ -1449,15 +1449,15 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>441</v>
@@ -1472,18 +1472,18 @@
         <v>2</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0</v>
@@ -1492,18 +1492,18 @@
         <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>440</v>
@@ -1518,15 +1518,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>440</v>
@@ -1541,15 +1541,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>440</v>
@@ -1564,15 +1564,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>440</v>
@@ -1587,15 +1587,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>440</v>
@@ -1610,15 +1610,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>440</v>
@@ -1633,15 +1633,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>440</v>
@@ -1656,15 +1656,15 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>440</v>
@@ -1679,15 +1679,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>440</v>
@@ -1702,15 +1702,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>440</v>
@@ -1725,15 +1725,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>440</v>
@@ -1748,15 +1748,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>440</v>
@@ -1771,15 +1771,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>440</v>
@@ -1794,15 +1794,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,18 +2530,18 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>0</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>442</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>442</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>442</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>442</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>442</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>442</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>442</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>442</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>442</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>442</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>442</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>442</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>442</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2949,10 +2949,10 @@
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,6 +2990,29 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B85" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -4357,7 +4380,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-24 22:12（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-24 22:35（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5013,10 +5036,10 @@
         <v>0.0205632</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>46289.925</v>
+        <v>46289.94097222222</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.019568</v>
+        <v>0.019522</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,9 +17,9 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$9</f>
+              <f>'資金明細'!$R$2:$R$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-24 22:35（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-24 22:48（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -796,19 +796,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$5,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$6,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$5,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$6,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$5,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$6,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$5,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$6,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -816,35 +816,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$5,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$6,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$5,交易明細!$J$2:$J$5,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$J$2:$J$5,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$J$2:$J$6,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$J$2:$J$5,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$J$2:$J$6,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$J$2:$J$5,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$J$2:$J$6,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$5,"&lt;&gt;未平倉",交易明細!$L$2:$L$5,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$6,"&lt;&gt;未平倉",交易明細!$L$2:$L$6,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$5,"做多",交易明細!$B$2:$B$5,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$6,"做多",交易明細!$B$2:$B$6,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -863,19 +863,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -883,35 +883,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$5,交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$6,交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$5,交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$5,"做多",交易明細!$J$2:$J$5,"&lt;&gt;未平倉",交易明細!$L$2:$L$5,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"&lt;&gt;未平倉",交易明細!$L$2:$L$6,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$5,"做空",交易明細!$B$2:$B$5,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$6,"做空",交易明細!$B$2:$B$6,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -930,19 +930,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -950,35 +950,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$5,交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$6,交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$5,交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$5,"做空",交易明細!$J$2:$J$5,"&lt;&gt;未平倉",交易明細!$L$2:$L$5,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"&lt;&gt;未平倉",交易明細!$L$2:$L$6,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,16 +1086,16 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -1104,61 +1104,61 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
@@ -1167,44 +1167,44 @@
         <v>3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
@@ -1219,15 +1219,15 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
@@ -1242,15 +1242,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
@@ -1265,15 +1265,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
@@ -1288,15 +1288,15 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
@@ -1311,15 +1311,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
@@ -1331,18 +1331,18 @@
         <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
@@ -1357,15 +1357,15 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
@@ -1380,15 +1380,15 @@
         <v>2</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
@@ -1403,18 +1403,18 @@
         <v>2</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
@@ -1426,15 +1426,15 @@
         <v>2</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>441</v>
@@ -1449,15 +1449,15 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>441</v>
@@ -1472,15 +1472,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>441</v>
@@ -1495,18 +1495,18 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
@@ -1515,18 +1515,18 @@
         <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>440</v>
@@ -1541,15 +1541,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>440</v>
@@ -1564,15 +1564,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>440</v>
@@ -1587,15 +1587,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>440</v>
@@ -1610,15 +1610,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>440</v>
@@ -1633,15 +1633,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>440</v>
@@ -1656,15 +1656,15 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>440</v>
@@ -1679,15 +1679,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>440</v>
@@ -1702,15 +1702,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>440</v>
@@ -1725,15 +1725,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>440</v>
@@ -1748,15 +1748,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>440</v>
@@ -1771,15 +1771,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>440</v>
@@ -1794,15 +1794,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,18 +2553,18 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>0</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>442</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>442</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>442</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>442</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>442</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>442</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>442</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>442</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>442</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>442</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>442</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>442</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,6 +3013,29 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3078,7 +3101,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R9</f>
+        <f>資金明細!R10</f>
         <v/>
       </c>
     </row>
@@ -3116,7 +3139,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$9)</f>
+        <f>MAX(資金明細!$R$2:$R$10)</f>
         <v/>
       </c>
     </row>
@@ -3135,7 +3158,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$9)</f>
+        <f>MIN(資金明細!$R$2:$R$10)</f>
         <v/>
       </c>
     </row>
@@ -3155,7 +3178,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$9)</f>
+        <f>MIN(資金明細!$X$2:$X$10)</f>
         <v/>
       </c>
     </row>
@@ -3174,7 +3197,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$9,"進場",資金明細!$N$2:$N$9,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$10,"進場",資金明細!$N$2:$N$10,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3193,7 +3216,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$9,"進場",資金明細!$N$2:$N$9,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$10,"進場",資金明細!$N$2:$N$10,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3204,7 +3227,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$9,"出場",資金明細!$N$2:$N$9,"已下單",資金明細!$K$2:$K$9,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$10,"出場",資金明細!$N$2:$N$10,"已下單",資金明細!$K$2:$K$10,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3215,7 +3238,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$5),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$6),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3224,7 +3247,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$9,"出場",資金明細!$N$2:$N$9,"已下單",資金明細!$K$2:$K$9,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$10,"出場",資金明細!$N$2:$N$10,"已下單",資金明細!$K$2:$K$10,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3240,7 +3263,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$9,"出場",資金明細!$N$2:$N$9,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$10,"出場",資金明細!$N$2:$N$10,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3256,7 +3279,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$9)</f>
+        <f>MAX(資金明細!$U$2:$U$10)</f>
         <v/>
       </c>
     </row>
@@ -3272,7 +3295,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$9)</f>
+        <f>MAX(資金明細!$S$2:$S$10)</f>
         <v/>
       </c>
     </row>
@@ -3283,7 +3306,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V9</f>
+        <f>B5*資金明細!V10</f>
         <v/>
       </c>
     </row>
@@ -3294,7 +3317,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N6="已下單",資金明細!O6*交易明細!L4,0)</f>
+        <f>IF(資金明細!N6="已下單",資金明細!O6*交易明細!L4,0)+IF(資金明細!N10="已下單",資金明細!O10*交易明細!L6,0)</f>
         <v/>
       </c>
     </row>
@@ -3305,7 +3328,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$9)</f>
+        <f>MAX(資金明細!$Y$2:$Y$10)</f>
         <v/>
       </c>
     </row>
@@ -3327,7 +3350,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$9,MATCH(1,資金明細!$Z$2:$Z$9,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$10,MATCH(1,資金明細!$Z$2:$Z$10,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3338,7 +3361,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$9,"進場",資金明細!$N$2:$N$9,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$10,"進場",資金明細!$N$2:$N$10,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3403,7 +3426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4297,9 +4320,103 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>46289.94236111111</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>BB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>0.01095</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0.0106215</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>0.0114975</v>
+      </c>
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="16">
+        <f>資金模擬!$B$5*V9</f>
+        <v/>
+      </c>
+      <c r="N10" s="2">
+        <f>IF(Z9=1,"已停止",IF(T9&gt;=M10,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O10" s="16">
+        <f>IF(N10="已下單",M10*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P10" s="4" t="n"/>
+      <c r="Q10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="10">
+        <f>R9+Q10</f>
+        <v/>
+      </c>
+      <c r="S10" s="16">
+        <f>S9+IF(N10="已下單",M10,0)</f>
+        <v/>
+      </c>
+      <c r="T10" s="16">
+        <f>R10-S10</f>
+        <v/>
+      </c>
+      <c r="U10" s="2">
+        <f>U9+IF(N10="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V10" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R10,0),MAX(V9,FLOOR(MAX(R10,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W10" s="10">
+        <f>MAX(W9,R10)</f>
+        <v/>
+      </c>
+      <c r="X10" s="4">
+        <f>IF(W10&gt;0,R10/W10-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y10" s="16">
+        <f>IF(R10&gt;0,S10*資金模擬!$B$7/R10,0)</f>
+        <v/>
+      </c>
+      <c r="Z10" s="2">
+        <f>IF(OR(Z9=1,R10&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z9"/>
-  <conditionalFormatting sqref="K2:K9">
+  <autoFilter ref="A1:Z10"/>
+  <conditionalFormatting sqref="K2:K10">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -4307,7 +4424,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N9">
+  <conditionalFormatting sqref="N2:N10">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -4315,7 +4432,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q9">
+  <conditionalFormatting sqref="Q2:Q10">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -4380,7 +4497,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-24 22:35（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-24 22:48（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -4590,7 +4707,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$5),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$6),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4616,7 +4733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5036,10 +5153,10 @@
         <v>0.0205632</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>46289.94097222222</v>
+        <v>46289.95</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.019522</v>
+        <v>0.019507</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -5195,9 +5312,104 @@
         <v>3</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>BB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>46289.94236111111</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0.01095</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>0.0106215</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>0.0114975</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>46289.95</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K6" s="5">
+        <f>(H6-D6)*24</f>
+        <v/>
+      </c>
+      <c r="L6" s="4">
+        <f>IF(C6="做多",I6/E6-1,1-I6/E6)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="19" t="n"/>
+      <c r="R6" s="19" t="n"/>
+      <c r="S6" s="4" t="n">
+        <v>0.0091324200913242</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>0.02922374429223762</v>
+      </c>
+      <c r="U6" s="16" t="n"/>
+      <c r="V6" s="16" t="n"/>
+      <c r="W6" s="4" t="n"/>
+      <c r="X6" s="4" t="n"/>
+      <c r="Y6" s="4" t="n"/>
+      <c r="Z6" s="4" t="n"/>
+      <c r="AA6" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB6" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC6" s="4">
+        <f>(AB6+2*參數!$B$7)/(AA6+AB6)</f>
+        <v/>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>0.07157057654075549</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>2.437114019164603</v>
+      </c>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>2倍</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="n">
+        <v>0.01388888888888884</v>
+      </c>
+      <c r="AH6" s="2" t="n">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AH5"/>
-  <conditionalFormatting sqref="J2:J5">
+  <autoFilter ref="A1:AH6"/>
+  <conditionalFormatting sqref="J2:J6">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -5218,7 +5430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5304,27 +5516,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A2,交易明細!$C$2:$C$5,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A2,交易明細!$C$2:$C$6,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A2,交易明細!$C$2:$C$5,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A2,交易明細!$C$2:$C$6,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$5,$A2,交易明細!$J$2:$J$5,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$6,$A2,交易明細!$J$2:$J$6,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A2,交易明細!$J$2:$J$5,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A2,交易明細!$J$2:$J$6,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A2,交易明細!$J$2:$J$5,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A2,交易明細!$J$2:$J$6,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -5332,19 +5544,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A2,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A2,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A2,交易明細!$J$2:$J$5,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A2,交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$B$2:$B$5,$A2,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$B$2:$B$6,$A2,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A2,交易明細!$J$2:$J$5,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A2,交易明細!$J$2:$J$6,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -5355,27 +5567,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A3,交易明細!$C$2:$C$5,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A3,交易明細!$C$2:$C$6,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A3,交易明細!$C$2:$C$5,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A3,交易明細!$C$2:$C$6,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$5,$A3,交易明細!$J$2:$J$5,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$6,$A3,交易明細!$J$2:$J$6,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A3,交易明細!$J$2:$J$5,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A3,交易明細!$J$2:$J$6,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A3,交易明細!$J$2:$J$5,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A3,交易明細!$J$2:$J$6,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -5383,19 +5595,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A3,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A3,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A3,交易明細!$J$2:$J$5,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A3,交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$B$2:$B$5,$A3,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$B$2:$B$6,$A3,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A3,交易明細!$J$2:$J$5,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A3,交易明細!$J$2:$J$6,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -5406,27 +5618,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A4,交易明細!$C$2:$C$5,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A4,交易明細!$C$2:$C$6,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A4,交易明細!$C$2:$C$5,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A4,交易明細!$C$2:$C$6,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$5,$A4,交易明細!$J$2:$J$5,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$6,$A4,交易明細!$J$2:$J$6,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A4,交易明細!$J$2:$J$5,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A4,交易明細!$J$2:$J$6,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A4,交易明細!$J$2:$J$5,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A4,交易明細!$J$2:$J$6,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -5434,19 +5646,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A4,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A4,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A4,交易明細!$J$2:$J$5,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A4,交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$B$2:$B$5,$A4,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$B$2:$B$6,$A4,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A4,交易明細!$J$2:$J$5,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A4,交易明細!$J$2:$J$6,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -5457,27 +5669,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A5,交易明細!$C$2:$C$5,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A5,交易明細!$C$2:$C$6,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A5,交易明細!$C$2:$C$5,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A5,交易明細!$C$2:$C$6,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$5,$A5,交易明細!$J$2:$J$5,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$6,$A5,交易明細!$J$2:$J$6,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A5,交易明細!$J$2:$J$5,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A5,交易明細!$J$2:$J$6,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A5,交易明細!$J$2:$J$5,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A5,交易明細!$J$2:$J$6,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -5485,24 +5697,75 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A5,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A5,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$5,交易明細!$B$2:$B$5,$A5,交易明細!$J$2:$J$5,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A5,交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$5,交易明細!$B$2:$B$5,$A5,交易明細!$J$2:$J$5,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$B$2:$B$6,$A5,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$5,$A5,交易明細!$J$2:$J$5,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A5,交易明細!$J$2:$J$6,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>BB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A6)</f>
+        <v/>
+      </c>
+      <c r="C6" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A6,交易明細!$C$2:$C$6,"做多")</f>
+        <v/>
+      </c>
+      <c r="D6" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A6,交易明細!$C$2:$C$6,"做空")</f>
+        <v/>
+      </c>
+      <c r="E6" s="2">
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$6,$A6,交易明細!$J$2:$J$6,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F6" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A6,交易明細!$J$2:$J$6,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G6" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A6,交易明細!$J$2:$J$6,"止損")</f>
+        <v/>
+      </c>
+      <c r="H6" s="4">
+        <f>IFERROR(F6/E6,0)</f>
+        <v/>
+      </c>
+      <c r="I6" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A6,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J6" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A6,交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K6" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$B$2:$B$6,$A6,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L6" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$6,$A6,交易明細!$J$2:$J$6,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L5"/>
+  <autoFilter ref="A1:L6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6663,7 +6926,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="17" t="n"/>
       <c r="F62" s="17" t="n"/>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-24 22:48（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-24 23:12（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,16 +1086,16 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -1104,21 +1104,21 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -1127,61 +1127,61 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
@@ -1190,44 +1190,44 @@
         <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
@@ -1242,15 +1242,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
@@ -1265,15 +1265,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
@@ -1288,15 +1288,15 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
@@ -1311,15 +1311,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
@@ -1334,15 +1334,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
@@ -1354,18 +1354,18 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
@@ -1380,15 +1380,15 @@
         <v>2</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
@@ -1403,15 +1403,15 @@
         <v>2</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
@@ -1426,18 +1426,18 @@
         <v>2</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
@@ -1449,15 +1449,15 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>441</v>
@@ -1472,15 +1472,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>441</v>
@@ -1495,15 +1495,15 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>441</v>
@@ -1518,18 +1518,18 @@
         <v>2</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0</v>
@@ -1538,18 +1538,18 @@
         <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>440</v>
@@ -1564,15 +1564,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>440</v>
@@ -1587,15 +1587,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>440</v>
@@ -1610,15 +1610,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>440</v>
@@ -1633,15 +1633,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>440</v>
@@ -1656,15 +1656,15 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>440</v>
@@ -1679,15 +1679,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>440</v>
@@ -1702,15 +1702,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>440</v>
@@ -1725,15 +1725,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>440</v>
@@ -1748,15 +1748,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>440</v>
@@ -1771,15 +1771,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>440</v>
@@ -1794,15 +1794,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,18 +2576,18 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>0</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>442</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>442</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>442</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>442</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>442</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>442</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>442</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>442</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>442</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>442</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>442</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,6 +3036,29 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B87" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -4497,7 +4520,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-24 22:48（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-24 23:12（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5153,10 +5176,10 @@
         <v>0.0205632</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>46289.95</v>
+        <v>46289.96666666667</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.019507</v>
+        <v>0.019527</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -5339,10 +5362,10 @@
         <v>0.0114975</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>46289.95</v>
+        <v>46289.96666666667</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>0.01125</v>
+        <v>0.01123</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -5368,10 +5391,10 @@
       <c r="Q6" s="19" t="n"/>
       <c r="R6" s="19" t="n"/>
       <c r="S6" s="4" t="n">
-        <v>0.0091324200913242</v>
+        <v>0.01917808219178085</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.02922374429223762</v>
+        <v>0.0310502283105023</v>
       </c>
       <c r="U6" s="16" t="n"/>
       <c r="V6" s="16" t="n"/>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,9 +17,9 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$10</f>
+              <f>'資金明細'!$R$2:$R$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-24 23:12（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 00:41（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -796,19 +796,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$6,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$8,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$6,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$8,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$6,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$8,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$6,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$8,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -816,35 +816,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$6,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$8,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$J$2:$J$6,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$J$2:$J$8,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$J$2:$J$6,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$J$2:$J$8,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$J$2:$J$6,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$J$2:$J$8,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$6,"&lt;&gt;未平倉",交易明細!$L$2:$L$6,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$8,"&lt;&gt;未平倉",交易明細!$L$2:$L$8,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$6,"做多",交易明細!$B$2:$B$6,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$8,"做多",交易明細!$B$2:$B$8,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -863,19 +863,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -883,35 +883,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$6,交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$8,交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$6,"做多",交易明細!$J$2:$J$6,"&lt;&gt;未平倉",交易明細!$L$2:$L$6,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"&lt;&gt;未平倉",交易明細!$L$2:$L$8,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$6,"做空",交易明細!$B$2:$B$6,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$8,"做空",交易明細!$B$2:$B$8,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -930,19 +930,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -950,35 +950,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$6,交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$8,交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$6,"做空",交易明細!$J$2:$J$6,"&lt;&gt;未平倉",交易明細!$L$2:$L$6,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"&lt;&gt;未平倉",交易明細!$L$2:$L$8,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,39 +1086,39 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -1127,21 +1127,21 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -1150,61 +1150,61 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
@@ -1213,44 +1213,44 @@
         <v>3</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
@@ -1265,15 +1265,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
@@ -1288,15 +1288,15 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
@@ -1311,15 +1311,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
@@ -1334,15 +1334,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
@@ -1357,15 +1357,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
@@ -1377,18 +1377,18 @@
         <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
@@ -1403,15 +1403,15 @@
         <v>2</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
@@ -1426,15 +1426,15 @@
         <v>2</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
@@ -1449,18 +1449,18 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0</v>
@@ -1472,15 +1472,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>441</v>
@@ -1495,15 +1495,15 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>441</v>
@@ -1518,15 +1518,15 @@
         <v>2</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>441</v>
@@ -1541,18 +1541,18 @@
         <v>2</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
@@ -1561,18 +1561,18 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>440</v>
@@ -1587,15 +1587,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>440</v>
@@ -1610,15 +1610,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>440</v>
@@ -1633,15 +1633,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>440</v>
@@ -1656,15 +1656,15 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>440</v>
@@ -1679,15 +1679,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>440</v>
@@ -1702,15 +1702,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>440</v>
@@ -1725,15 +1725,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>440</v>
@@ -1748,15 +1748,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>440</v>
@@ -1771,15 +1771,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>440</v>
@@ -1794,15 +1794,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,18 +2599,18 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>0</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>442</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>442</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>442</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>442</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>442</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>442</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>442</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>442</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>442</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>442</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3018,10 +3018,10 @@
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,6 +3059,29 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B88" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3124,7 +3147,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R10</f>
+        <f>資金明細!R14</f>
         <v/>
       </c>
     </row>
@@ -3162,7 +3185,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$10)</f>
+        <f>MAX(資金明細!$R$2:$R$14)</f>
         <v/>
       </c>
     </row>
@@ -3181,7 +3204,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$10)</f>
+        <f>MIN(資金明細!$R$2:$R$14)</f>
         <v/>
       </c>
     </row>
@@ -3201,7 +3224,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$10)</f>
+        <f>MIN(資金明細!$X$2:$X$14)</f>
         <v/>
       </c>
     </row>
@@ -3220,7 +3243,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$10,"進場",資金明細!$N$2:$N$10,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$14,"進場",資金明細!$N$2:$N$14,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3239,7 +3262,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$10,"進場",資金明細!$N$2:$N$10,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$14,"進場",資金明細!$N$2:$N$14,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3250,7 +3273,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$10,"出場",資金明細!$N$2:$N$10,"已下單",資金明細!$K$2:$K$10,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$14,"出場",資金明細!$N$2:$N$14,"已下單",資金明細!$K$2:$K$14,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3261,7 +3284,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$6),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$8),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3270,7 +3293,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$10,"出場",資金明細!$N$2:$N$10,"已下單",資金明細!$K$2:$K$10,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$14,"出場",資金明細!$N$2:$N$14,"已下單",資金明細!$K$2:$K$14,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3286,7 +3309,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$10,"出場",資金明細!$N$2:$N$10,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$14,"出場",資金明細!$N$2:$N$14,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3302,7 +3325,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$10)</f>
+        <f>MAX(資金明細!$U$2:$U$14)</f>
         <v/>
       </c>
     </row>
@@ -3318,7 +3341,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$10)</f>
+        <f>MAX(資金明細!$S$2:$S$14)</f>
         <v/>
       </c>
     </row>
@@ -3329,7 +3352,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V10</f>
+        <f>B5*資金明細!V14</f>
         <v/>
       </c>
     </row>
@@ -3340,7 +3363,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N6="已下單",資金明細!O6*交易明細!L4,0)+IF(資金明細!N10="已下單",資金明細!O10*交易明細!L6,0)</f>
+        <f>IF(資金明細!N13="已下單",資金明細!O13*交易明細!L7,0)+IF(資金明細!N14="已下單",資金明細!O14*交易明細!L8,0)</f>
         <v/>
       </c>
     </row>
@@ -3351,7 +3374,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$10)</f>
+        <f>MAX(資金明細!$Y$2:$Y$14)</f>
         <v/>
       </c>
     </row>
@@ -3373,7 +3396,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$10,MATCH(1,資金明細!$Z$2:$Z$10,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$14,MATCH(1,資金明細!$Z$2:$Z$14,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3384,7 +3407,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$10,"進場",資金明細!$N$2:$N$10,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$14,"進場",資金明細!$N$2:$N$14,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3449,7 +3472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3988,11 +4011,7 @@
         <v>0.0205632</v>
       </c>
       <c r="J6" s="17" t="n"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K6" s="2" t="n"/>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="16">
         <f>資金模擬!$B$5*V5</f>
@@ -4378,11 +4397,7 @@
         <v>0.0114975</v>
       </c>
       <c r="J10" s="17" t="n"/>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="16">
         <f>資金模擬!$B$5*V9</f>
@@ -4437,9 +4452,403 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>46289.97430555556</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>AGT_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>0.019584</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>0.01899648</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>0.0205632</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>0.01899648</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L11" s="5">
+        <f>交易明細!K4</f>
+        <v/>
+      </c>
+      <c r="M11" s="16">
+        <f>M6</f>
+        <v/>
+      </c>
+      <c r="N11" s="2">
+        <f>N6</f>
+        <v/>
+      </c>
+      <c r="O11" s="16">
+        <f>O6</f>
+        <v/>
+      </c>
+      <c r="P11" s="4">
+        <f>交易明細!L4</f>
+        <v/>
+      </c>
+      <c r="Q11" s="10">
+        <f>IF(N11="已下單",O11*P11,0)</f>
+        <v/>
+      </c>
+      <c r="R11" s="10">
+        <f>R10+Q11</f>
+        <v/>
+      </c>
+      <c r="S11" s="16">
+        <f>S10-IF(N11="已下單",M11,0)</f>
+        <v/>
+      </c>
+      <c r="T11" s="16">
+        <f>R11-S11</f>
+        <v/>
+      </c>
+      <c r="U11" s="2">
+        <f>U10-IF(N11="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V11" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R11,0),MAX(V10,FLOOR(MAX(R11,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W11" s="10">
+        <f>MAX(W10,R11)</f>
+        <v/>
+      </c>
+      <c r="X11" s="4">
+        <f>IF(W11&gt;0,R11/W11-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="16">
+        <f>IF(R11&gt;0,S11*資金模擬!$B$7/R11,0)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="2">
+        <f>IF(OR(Z10=1,R11&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>46289.99236111111</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>BB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>0.01095</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>0.0106215</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>0.0114975</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>0.0106215</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L12" s="5">
+        <f>交易明細!K6</f>
+        <v/>
+      </c>
+      <c r="M12" s="16">
+        <f>M10</f>
+        <v/>
+      </c>
+      <c r="N12" s="2">
+        <f>N10</f>
+        <v/>
+      </c>
+      <c r="O12" s="16">
+        <f>O10</f>
+        <v/>
+      </c>
+      <c r="P12" s="4">
+        <f>交易明細!L6</f>
+        <v/>
+      </c>
+      <c r="Q12" s="10">
+        <f>IF(N12="已下單",O12*P12,0)</f>
+        <v/>
+      </c>
+      <c r="R12" s="10">
+        <f>R11+Q12</f>
+        <v/>
+      </c>
+      <c r="S12" s="16">
+        <f>S11-IF(N12="已下單",M12,0)</f>
+        <v/>
+      </c>
+      <c r="T12" s="16">
+        <f>R12-S12</f>
+        <v/>
+      </c>
+      <c r="U12" s="2">
+        <f>U11-IF(N12="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V12" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R12,0),MAX(V11,FLOOR(MAX(R12,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W12" s="10">
+        <f>MAX(W11,R12)</f>
+        <v/>
+      </c>
+      <c r="X12" s="4">
+        <f>IF(W12&gt;0,R12/W12-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y12" s="16">
+        <f>IF(R12&gt;0,S12*資金模擬!$B$7/R12,0)</f>
+        <v/>
+      </c>
+      <c r="Z12" s="2">
+        <f>IF(OR(Z11=1,R12&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>46290.01111111111</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>1.278</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>1.23966</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>1.3419</v>
+      </c>
+      <c r="J13" s="17" t="n"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="16">
+        <f>資金模擬!$B$5*V12</f>
+        <v/>
+      </c>
+      <c r="N13" s="2">
+        <f>IF(Z12=1,"已停止",IF(T12&gt;=M13,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O13" s="16">
+        <f>IF(N13="已下單",M13*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P13" s="4" t="n"/>
+      <c r="Q13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="10">
+        <f>R12+Q13</f>
+        <v/>
+      </c>
+      <c r="S13" s="16">
+        <f>S12+IF(N13="已下單",M13,0)</f>
+        <v/>
+      </c>
+      <c r="T13" s="16">
+        <f>R13-S13</f>
+        <v/>
+      </c>
+      <c r="U13" s="2">
+        <f>U12+IF(N13="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V13" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R13,0),MAX(V12,FLOOR(MAX(R13,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W13" s="10">
+        <f>MAX(W12,R13)</f>
+        <v/>
+      </c>
+      <c r="X13" s="4">
+        <f>IF(W13&gt;0,R13/W13-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y13" s="16">
+        <f>IF(R13&gt;0,S13*資金模擬!$B$7/R13,0)</f>
+        <v/>
+      </c>
+      <c r="Z13" s="2">
+        <f>IF(OR(Z12=1,R13&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>46290.01458333333</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>0.06094</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>0.0591118</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>0.063987</v>
+      </c>
+      <c r="J14" s="17" t="n"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="16">
+        <f>資金模擬!$B$5*V13</f>
+        <v/>
+      </c>
+      <c r="N14" s="2">
+        <f>IF(Z13=1,"已停止",IF(T13&gt;=M14,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O14" s="16">
+        <f>IF(N14="已下單",M14*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P14" s="4" t="n"/>
+      <c r="Q14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="10">
+        <f>R13+Q14</f>
+        <v/>
+      </c>
+      <c r="S14" s="16">
+        <f>S13+IF(N14="已下單",M14,0)</f>
+        <v/>
+      </c>
+      <c r="T14" s="16">
+        <f>R14-S14</f>
+        <v/>
+      </c>
+      <c r="U14" s="2">
+        <f>U13+IF(N14="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V14" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R14,0),MAX(V13,FLOOR(MAX(R14,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W14" s="10">
+        <f>MAX(W13,R14)</f>
+        <v/>
+      </c>
+      <c r="X14" s="4">
+        <f>IF(W14&gt;0,R14/W14-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="16">
+        <f>IF(R14&gt;0,S14*資金模擬!$B$7/R14,0)</f>
+        <v/>
+      </c>
+      <c r="Z14" s="2">
+        <f>IF(OR(Z13=1,R14&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z10"/>
-  <conditionalFormatting sqref="K2:K10">
+  <autoFilter ref="A1:Z14"/>
+  <conditionalFormatting sqref="K2:K14">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -4447,7 +4856,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N10">
+  <conditionalFormatting sqref="N2:N14">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -4455,7 +4864,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q10">
+  <conditionalFormatting sqref="Q2:Q14">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -4520,7 +4929,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-24 23:12（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-25 00:41（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -4730,7 +5139,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$6),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$8),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4756,7 +5165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH6"/>
+  <dimension ref="A1:AH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5176,14 +5585,14 @@
         <v>0.0205632</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>46289.96666666667</v>
+        <v>46289.97430555556</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.019527</v>
+        <v>0.01899648</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K4" s="5">
@@ -5194,18 +5603,14 @@
         <f>IF(C4="做多",I4/E4-1,1-I4/E4)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="4" t="n"/>
       <c r="O4" s="4" t="n"/>
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="19" t="n"/>
       <c r="R4" s="19" t="n"/>
       <c r="S4" s="4" t="n">
-        <v>0.02236519607843146</v>
+        <v>0.03</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0.01710580065359468</v>
@@ -5362,14 +5767,14 @@
         <v>0.0114975</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>46289.96666666667</v>
+        <v>46289.99236111111</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>0.01123</v>
+        <v>0.0106215</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K6" s="5">
@@ -5380,21 +5785,17 @@
         <f>IF(C6="做多",I6/E6-1,1-I6/E6)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="19" t="n"/>
       <c r="R6" s="19" t="n"/>
       <c r="S6" s="4" t="n">
-        <v>0.01917808219178085</v>
+        <v>0.03</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.0310502283105023</v>
+        <v>0.03926940639269394</v>
       </c>
       <c r="U6" s="16" t="n"/>
       <c r="V6" s="16" t="n"/>
@@ -5430,9 +5831,199 @@
         <v>37</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>46290.01111111111</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>1.278</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>1.23966</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>1.3419</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>46290.02847222222</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K7" s="5">
+        <f>(H7-D7)*24</f>
+        <v/>
+      </c>
+      <c r="L7" s="4">
+        <f>IF(C7="做多",I7/E7-1,1-I7/E7)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="19" t="n"/>
+      <c r="R7" s="19" t="n"/>
+      <c r="S7" s="4" t="n">
+        <v>0.007824726134585291</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>0.01956181533646317</v>
+      </c>
+      <c r="U7" s="16" t="n"/>
+      <c r="V7" s="16" t="n"/>
+      <c r="W7" s="4" t="n"/>
+      <c r="X7" s="4" t="n"/>
+      <c r="Y7" s="4" t="n"/>
+      <c r="Z7" s="4" t="n"/>
+      <c r="AA7" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB7" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC7" s="4">
+        <f>(AB7+2*參數!$B$7)/(AA7+AB7)</f>
+        <v/>
+      </c>
+      <c r="AD7" s="2" t="n">
+        <v>0.06688963210702337</v>
+      </c>
+      <c r="AE7" s="2" t="n">
+        <v>1.912629795915797</v>
+      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>30分1倍+15分0.5倍</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="n">
+        <v>0.00156739811912221</v>
+      </c>
+      <c r="AH7" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>46290.01458333333</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0.06094</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>0.0591118</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>0.063987</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>46290.02847222222</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>0.06207</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K8" s="5">
+        <f>(H8-D8)*24</f>
+        <v/>
+      </c>
+      <c r="L8" s="4">
+        <f>IF(C8="做多",I8/E8-1,1-I8/E8)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="19" t="n"/>
+      <c r="R8" s="19" t="n"/>
+      <c r="S8" s="4" t="n">
+        <v>0.006892024942566466</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>0.02494256645881188</v>
+      </c>
+      <c r="U8" s="16" t="n"/>
+      <c r="V8" s="16" t="n"/>
+      <c r="W8" s="4" t="n"/>
+      <c r="X8" s="4" t="n"/>
+      <c r="Y8" s="4" t="n"/>
+      <c r="Z8" s="4" t="n"/>
+      <c r="AA8" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB8" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC8" s="4">
+        <f>(AB8+2*參數!$B$7)/(AA8+AB8)</f>
+        <v/>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>0.06563976894801327</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>0.6644694678375066</v>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>15分0.5倍</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="n">
+        <v>0.0003282994090609836</v>
+      </c>
+      <c r="AH8" s="2" t="n">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AH6"/>
-  <conditionalFormatting sqref="J2:J6">
+  <autoFilter ref="A1:AH8"/>
+  <conditionalFormatting sqref="J2:J8">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -5453,7 +6044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5539,27 +6130,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A2,交易明細!$C$2:$C$6,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A2,交易明細!$C$2:$C$8,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A2,交易明細!$C$2:$C$6,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A2,交易明細!$C$2:$C$8,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$6,$A2,交易明細!$J$2:$J$6,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$8,$A2,交易明細!$J$2:$J$8,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A2,交易明細!$J$2:$J$6,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A2,交易明細!$J$2:$J$8,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A2,交易明細!$J$2:$J$6,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A2,交易明細!$J$2:$J$8,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -5567,19 +6158,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A2,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A2,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A2,交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A2,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$B$2:$B$6,$A2,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$B$2:$B$8,$A2,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A2,交易明細!$J$2:$J$6,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A2,交易明細!$J$2:$J$8,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -5590,27 +6181,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A3,交易明細!$C$2:$C$6,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A3,交易明細!$C$2:$C$8,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A3,交易明細!$C$2:$C$6,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A3,交易明細!$C$2:$C$8,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$6,$A3,交易明細!$J$2:$J$6,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$8,$A3,交易明細!$J$2:$J$8,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A3,交易明細!$J$2:$J$6,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A3,交易明細!$J$2:$J$8,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A3,交易明細!$J$2:$J$6,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A3,交易明細!$J$2:$J$8,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -5618,19 +6209,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A3,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A3,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A3,交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A3,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$B$2:$B$6,$A3,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$B$2:$B$8,$A3,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A3,交易明細!$J$2:$J$6,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A3,交易明細!$J$2:$J$8,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -5641,27 +6232,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A4,交易明細!$C$2:$C$6,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A4,交易明細!$C$2:$C$8,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A4,交易明細!$C$2:$C$6,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A4,交易明細!$C$2:$C$8,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$6,$A4,交易明細!$J$2:$J$6,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$8,$A4,交易明細!$J$2:$J$8,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A4,交易明細!$J$2:$J$6,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A4,交易明細!$J$2:$J$8,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A4,交易明細!$J$2:$J$6,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A4,交易明細!$J$2:$J$8,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -5669,19 +6260,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A4,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A4,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A4,交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A4,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$B$2:$B$6,$A4,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$B$2:$B$8,$A4,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A4,交易明細!$J$2:$J$6,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A4,交易明細!$J$2:$J$8,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -5692,27 +6283,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A5,交易明細!$C$2:$C$6,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A5,交易明細!$C$2:$C$8,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A5,交易明細!$C$2:$C$6,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A5,交易明細!$C$2:$C$8,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$6,$A5,交易明細!$J$2:$J$6,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$8,$A5,交易明細!$J$2:$J$8,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A5,交易明細!$J$2:$J$6,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A5,交易明細!$J$2:$J$8,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A5,交易明細!$J$2:$J$6,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A5,交易明細!$J$2:$J$8,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -5720,19 +6311,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A5,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A5,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A5,交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A5,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$B$2:$B$6,$A5,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$B$2:$B$8,$A5,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A5,交易明細!$J$2:$J$6,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A5,交易明細!$J$2:$J$8,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -5743,27 +6334,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A6,交易明細!$C$2:$C$6,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A6,交易明細!$C$2:$C$8,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A6,交易明細!$C$2:$C$6,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A6,交易明細!$C$2:$C$8,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$6,$A6,交易明細!$J$2:$J$6,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$8,$A6,交易明細!$J$2:$J$8,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A6,交易明細!$J$2:$J$6,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A6,交易明細!$J$2:$J$8,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A6,交易明細!$J$2:$J$6,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A6,交易明細!$J$2:$J$8,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -5771,24 +6362,126 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A6,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A6,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$6,交易明細!$B$2:$B$6,$A6,交易明細!$J$2:$J$6,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A6,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$6,交易明細!$B$2:$B$6,$A6,交易明細!$J$2:$J$6,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$B$2:$B$8,$A6,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$6,$A6,交易明細!$J$2:$J$6,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A6,交易明細!$J$2:$J$8,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B7" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A7)</f>
+        <v/>
+      </c>
+      <c r="C7" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A7,交易明細!$C$2:$C$8,"做多")</f>
+        <v/>
+      </c>
+      <c r="D7" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A7,交易明細!$C$2:$C$8,"做空")</f>
+        <v/>
+      </c>
+      <c r="E7" s="2">
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$8,$A7,交易明細!$J$2:$J$8,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F7" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A7,交易明細!$J$2:$J$8,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G7" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A7,交易明細!$J$2:$J$8,"止損")</f>
+        <v/>
+      </c>
+      <c r="H7" s="4">
+        <f>IFERROR(F7/E7,0)</f>
+        <v/>
+      </c>
+      <c r="I7" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A7,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J7" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A7,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K7" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$B$2:$B$8,$A7,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L7" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A7,交易明細!$J$2:$J$8,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A8,交易明細!$C$2:$C$8,"做多")</f>
+        <v/>
+      </c>
+      <c r="D8" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A8,交易明細!$C$2:$C$8,"做空")</f>
+        <v/>
+      </c>
+      <c r="E8" s="2">
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$8,$A8,交易明細!$J$2:$J$8,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F8" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A8,交易明細!$J$2:$J$8,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G8" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A8,交易明細!$J$2:$J$8,"止損")</f>
+        <v/>
+      </c>
+      <c r="H8" s="4">
+        <f>IFERROR(F8/E8,0)</f>
+        <v/>
+      </c>
+      <c r="I8" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A8,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J8" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A8,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K8" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$B$2:$B$8,$A8,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L8" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$8,$A8,交易明細!$J$2:$J$8,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L6"/>
+  <autoFilter ref="A1:L8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6081,11 +6774,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="17" t="n"/>
       <c r="F14" s="17" t="n"/>
@@ -6949,11 +7638,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="17" t="n"/>
       <c r="F62" s="17" t="n"/>
@@ -9545,7 +10230,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr"/>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D206" s="2" t="n"/>
       <c r="E206" s="17" t="n"/>
       <c r="F206" s="17" t="n"/>
@@ -11525,7 +12214,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C316" s="2" t="inlineStr"/>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D316" s="2" t="n"/>
       <c r="E316" s="17" t="n"/>
       <c r="F316" s="17" t="n"/>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 00:41（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 03:15（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,62 +1086,62 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -1150,21 +1150,21 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -1173,61 +1173,61 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
@@ -1236,44 +1236,44 @@
         <v>3</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
@@ -1288,15 +1288,15 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
@@ -1311,15 +1311,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
@@ -1334,15 +1334,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
@@ -1357,15 +1357,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
@@ -1380,15 +1380,15 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
@@ -1400,18 +1400,18 @@
         <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
@@ -1426,15 +1426,15 @@
         <v>2</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
@@ -1449,15 +1449,15 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
@@ -1472,18 +1472,18 @@
         <v>2</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0</v>
@@ -1495,15 +1495,15 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>441</v>
@@ -1518,15 +1518,15 @@
         <v>2</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>441</v>
@@ -1541,15 +1541,15 @@
         <v>2</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>441</v>
@@ -1564,18 +1564,18 @@
         <v>2</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0</v>
@@ -1584,18 +1584,18 @@
         <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>440</v>
@@ -1610,15 +1610,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>440</v>
@@ -1633,15 +1633,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>440</v>
@@ -1656,15 +1656,15 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>440</v>
@@ -1679,15 +1679,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>440</v>
@@ -1702,15 +1702,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>440</v>
@@ -1725,15 +1725,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>440</v>
@@ -1748,15 +1748,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>440</v>
@@ -1771,15 +1771,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>440</v>
@@ -1794,15 +1794,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,18 +2622,18 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>0</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>442</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>442</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>442</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>442</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>442</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>442</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>442</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>442</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>442</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,6 +3082,29 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B89" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -4929,7 +4952,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-25 00:41（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-25 03:15（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5858,10 +5881,10 @@
         <v>1.3419</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>46290.02847222222</v>
+        <v>46290.13541666666</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>1.275</v>
+        <v>1.299</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -5887,10 +5910,10 @@
       <c r="Q7" s="19" t="n"/>
       <c r="R7" s="19" t="n"/>
       <c r="S7" s="4" t="n">
-        <v>0.007824726134585291</v>
+        <v>0.02347417840375587</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.01956181533646317</v>
+        <v>0.02973395931142409</v>
       </c>
       <c r="U7" s="16" t="n"/>
       <c r="V7" s="16" t="n"/>
@@ -5953,10 +5976,10 @@
         <v>0.063987</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>46290.02847222222</v>
+        <v>46290.13541666666</v>
       </c>
       <c r="I8" s="17" t="n">
-        <v>0.06207</v>
+        <v>0.06011</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -5982,10 +6005,10 @@
       <c r="Q8" s="19" t="n"/>
       <c r="R8" s="19" t="n"/>
       <c r="S8" s="4" t="n">
-        <v>0.006892024942566466</v>
+        <v>0.02543485395470957</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.02494256645881188</v>
+        <v>0.03807023301608137</v>
       </c>
       <c r="U8" s="16" t="n"/>
       <c r="V8" s="16" t="n"/>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,7 +17,7 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$14</f>
+              <f>'資金明細'!$R$2:$R$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 03:15（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 06:31（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
@@ -1098,73 +1098,73 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -1173,21 +1173,21 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -1196,61 +1196,61 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
@@ -1259,44 +1259,44 @@
         <v>3</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
@@ -1311,15 +1311,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
@@ -1334,15 +1334,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
@@ -1357,15 +1357,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
@@ -1380,15 +1380,15 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
@@ -1403,15 +1403,15 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
@@ -1423,18 +1423,18 @@
         <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
@@ -1449,15 +1449,15 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
@@ -1472,15 +1472,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
@@ -1495,18 +1495,18 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
@@ -1518,15 +1518,15 @@
         <v>2</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>441</v>
@@ -1541,15 +1541,15 @@
         <v>2</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>441</v>
@@ -1564,15 +1564,15 @@
         <v>2</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>441</v>
@@ -1587,18 +1587,18 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
@@ -1607,18 +1607,18 @@
         <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>440</v>
@@ -1633,15 +1633,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>440</v>
@@ -1656,15 +1656,15 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>440</v>
@@ -1679,15 +1679,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>440</v>
@@ -1702,15 +1702,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>440</v>
@@ -1725,15 +1725,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>440</v>
@@ -1748,15 +1748,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>440</v>
@@ -1771,15 +1771,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>440</v>
@@ -1794,15 +1794,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,18 +2645,18 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>0</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>442</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>442</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>442</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>442</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>442</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>442</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>442</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>442</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3064,10 +3064,10 @@
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,6 +3105,29 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B90" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3170,7 +3193,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R14</f>
+        <f>資金明細!R15</f>
         <v/>
       </c>
     </row>
@@ -3208,7 +3231,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$14)</f>
+        <f>MAX(資金明細!$R$2:$R$15)</f>
         <v/>
       </c>
     </row>
@@ -3227,7 +3250,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$14)</f>
+        <f>MIN(資金明細!$R$2:$R$15)</f>
         <v/>
       </c>
     </row>
@@ -3247,7 +3270,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$14)</f>
+        <f>MIN(資金明細!$X$2:$X$15)</f>
         <v/>
       </c>
     </row>
@@ -3266,7 +3289,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$14,"進場",資金明細!$N$2:$N$14,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$15,"進場",資金明細!$N$2:$N$15,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3285,7 +3308,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$14,"進場",資金明細!$N$2:$N$14,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$15,"進場",資金明細!$N$2:$N$15,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3296,7 +3319,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$14,"出場",資金明細!$N$2:$N$14,"已下單",資金明細!$K$2:$K$14,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$15,"出場",資金明細!$N$2:$N$15,"已下單",資金明細!$K$2:$K$15,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3316,7 +3339,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$14,"出場",資金明細!$N$2:$N$14,"已下單",資金明細!$K$2:$K$14,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$15,"出場",資金明細!$N$2:$N$15,"已下單",資金明細!$K$2:$K$15,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3332,7 +3355,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$14,"出場",資金明細!$N$2:$N$14,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$15,"出場",資金明細!$N$2:$N$15,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3348,7 +3371,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$14)</f>
+        <f>MAX(資金明細!$U$2:$U$15)</f>
         <v/>
       </c>
     </row>
@@ -3364,7 +3387,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$14)</f>
+        <f>MAX(資金明細!$S$2:$S$15)</f>
         <v/>
       </c>
     </row>
@@ -3375,7 +3398,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V14</f>
+        <f>B5*資金明細!V15</f>
         <v/>
       </c>
     </row>
@@ -3386,7 +3409,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N13="已下單",資金明細!O13*交易明細!L7,0)+IF(資金明細!N14="已下單",資金明細!O14*交易明細!L8,0)</f>
+        <f>IF(資金明細!N13="已下單",資金明細!O13*交易明細!L7,0)</f>
         <v/>
       </c>
     </row>
@@ -3397,7 +3420,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$14)</f>
+        <f>MAX(資金明細!$Y$2:$Y$15)</f>
         <v/>
       </c>
     </row>
@@ -3419,7 +3442,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$14,MATCH(1,資金明細!$Z$2:$Z$14,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$15,MATCH(1,資金明細!$Z$2:$Z$15,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3430,7 +3453,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$14,"進場",資金明細!$N$2:$N$14,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$15,"進場",資金明細!$N$2:$N$15,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3495,7 +3518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4810,11 +4833,7 @@
         <v>0.063987</v>
       </c>
       <c r="J14" s="17" t="n"/>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K14" s="2" t="n"/>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="16">
         <f>資金模擬!$B$5*V13</f>
@@ -4869,9 +4888,112 @@
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>46290.26388888889</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>LAB_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>0.06094</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>0.0591118</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>0.063987</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>0.0591118</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L15" s="5">
+        <f>交易明細!K8</f>
+        <v/>
+      </c>
+      <c r="M15" s="16">
+        <f>M14</f>
+        <v/>
+      </c>
+      <c r="N15" s="2">
+        <f>N14</f>
+        <v/>
+      </c>
+      <c r="O15" s="16">
+        <f>O14</f>
+        <v/>
+      </c>
+      <c r="P15" s="4">
+        <f>交易明細!L8</f>
+        <v/>
+      </c>
+      <c r="Q15" s="10">
+        <f>IF(N15="已下單",O15*P15,0)</f>
+        <v/>
+      </c>
+      <c r="R15" s="10">
+        <f>R14+Q15</f>
+        <v/>
+      </c>
+      <c r="S15" s="16">
+        <f>S14-IF(N15="已下單",M15,0)</f>
+        <v/>
+      </c>
+      <c r="T15" s="16">
+        <f>R15-S15</f>
+        <v/>
+      </c>
+      <c r="U15" s="2">
+        <f>U14-IF(N15="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V15" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R15,0),MAX(V14,FLOOR(MAX(R15,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W15" s="10">
+        <f>MAX(W14,R15)</f>
+        <v/>
+      </c>
+      <c r="X15" s="4">
+        <f>IF(W15&gt;0,R15/W15-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y15" s="16">
+        <f>IF(R15&gt;0,S15*資金模擬!$B$7/R15,0)</f>
+        <v/>
+      </c>
+      <c r="Z15" s="2">
+        <f>IF(OR(Z14=1,R15&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z14"/>
-  <conditionalFormatting sqref="K2:K14">
+  <autoFilter ref="A1:Z15"/>
+  <conditionalFormatting sqref="K2:K15">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -4879,7 +5001,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N14">
+  <conditionalFormatting sqref="N2:N15">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -4887,7 +5009,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q14">
+  <conditionalFormatting sqref="Q2:Q15">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -4952,7 +5074,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-25 03:15（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-25 06:31（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5881,10 +6003,10 @@
         <v>1.3419</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>46290.13541666666</v>
+        <v>46290.27152777778</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>1.299</v>
+        <v>1.266</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -5913,7 +6035,7 @@
         <v>0.02347417840375587</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.02973395931142409</v>
+        <v>0.04460093896713602</v>
       </c>
       <c r="U7" s="16" t="n"/>
       <c r="V7" s="16" t="n"/>
@@ -5976,14 +6098,14 @@
         <v>0.063987</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>46290.13541666666</v>
+        <v>46290.26388888889</v>
       </c>
       <c r="I8" s="17" t="n">
-        <v>0.06011</v>
+        <v>0.0591118</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K8" s="5">
@@ -5994,18 +6116,14 @@
         <f>IF(C8="做多",I8/E8-1,1-I8/E8)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="19" t="n"/>
       <c r="R8" s="19" t="n"/>
       <c r="S8" s="4" t="n">
-        <v>0.02543485395470957</v>
+        <v>0.03</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>0.03807023301608137</v>
@@ -10253,11 +10371,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C206" s="2" t="inlineStr"/>
       <c r="D206" s="2" t="n"/>
       <c r="E206" s="17" t="n"/>
       <c r="F206" s="17" t="n"/>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,9 +17,9 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$15</f>
+              <f>'資金明細'!$R$2:$R$17</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 06:31（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 08:21（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -796,19 +796,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$8,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$9,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$8,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$9,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$8,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$9,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$8,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$9,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -816,35 +816,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$8,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$9,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$J$2:$J$8,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$J$2:$J$9,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$J$2:$J$8,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$J$2:$J$9,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$J$2:$J$8,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$J$2:$J$9,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$8,"&lt;&gt;未平倉",交易明細!$L$2:$L$8,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$9,"&lt;&gt;未平倉",交易明細!$L$2:$L$9,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$8,"做多",交易明細!$B$2:$B$8,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$9,"做多",交易明細!$B$2:$B$9,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -863,19 +863,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -883,35 +883,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$8,交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$9,交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$8,"做多",交易明細!$J$2:$J$8,"&lt;&gt;未平倉",交易明細!$L$2:$L$8,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"&lt;&gt;未平倉",交易明細!$L$2:$L$9,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$8,"做空",交易明細!$B$2:$B$8,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$9,"做空",交易明細!$B$2:$B$9,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -930,19 +930,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -950,35 +950,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$8,交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$9,交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$8,"做空",交易明細!$J$2:$J$8,"&lt;&gt;未平倉",交易明細!$L$2:$L$8,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"&lt;&gt;未平倉",交易明細!$L$2:$L$9,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,33 +1086,33 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
@@ -1121,73 +1121,73 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -1196,21 +1196,21 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
@@ -1219,61 +1219,61 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
@@ -1282,44 +1282,44 @@
         <v>3</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
@@ -1334,15 +1334,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
@@ -1357,15 +1357,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
@@ -1380,15 +1380,15 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
@@ -1403,15 +1403,15 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
@@ -1426,15 +1426,15 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
@@ -1446,18 +1446,18 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
@@ -1472,15 +1472,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
@@ -1495,15 +1495,15 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
@@ -1518,18 +1518,18 @@
         <v>2</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0</v>
@@ -1541,15 +1541,15 @@
         <v>2</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>441</v>
@@ -1564,15 +1564,15 @@
         <v>2</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>441</v>
@@ -1587,15 +1587,15 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>441</v>
@@ -1610,18 +1610,18 @@
         <v>2</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0</v>
@@ -1630,18 +1630,18 @@
         <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>440</v>
@@ -1656,15 +1656,15 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>440</v>
@@ -1679,15 +1679,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>440</v>
@@ -1702,15 +1702,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>440</v>
@@ -1725,15 +1725,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>440</v>
@@ -1748,15 +1748,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>440</v>
@@ -1771,15 +1771,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>440</v>
@@ -1794,15 +1794,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,18 +2668,18 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>0</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>442</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>442</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>442</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>442</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>442</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>442</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>442</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3087,10 +3087,10 @@
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,6 +3128,29 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B91" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3193,7 +3216,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R15</f>
+        <f>資金明細!R17</f>
         <v/>
       </c>
     </row>
@@ -3231,7 +3254,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$15)</f>
+        <f>MAX(資金明細!$R$2:$R$17)</f>
         <v/>
       </c>
     </row>
@@ -3250,7 +3273,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$15)</f>
+        <f>MIN(資金明細!$R$2:$R$17)</f>
         <v/>
       </c>
     </row>
@@ -3270,7 +3293,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$15)</f>
+        <f>MIN(資金明細!$X$2:$X$17)</f>
         <v/>
       </c>
     </row>
@@ -3289,7 +3312,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$15,"進場",資金明細!$N$2:$N$15,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$17,"進場",資金明細!$N$2:$N$17,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3308,7 +3331,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$15,"進場",資金明細!$N$2:$N$15,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$17,"進場",資金明細!$N$2:$N$17,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3319,7 +3342,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$15,"出場",資金明細!$N$2:$N$15,"已下單",資金明細!$K$2:$K$15,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$17,"出場",資金明細!$N$2:$N$17,"已下單",資金明細!$K$2:$K$17,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3330,7 +3353,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$8),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$9),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3339,7 +3362,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$15,"出場",資金明細!$N$2:$N$15,"已下單",資金明細!$K$2:$K$15,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$17,"出場",資金明細!$N$2:$N$17,"已下單",資金明細!$K$2:$K$17,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3355,7 +3378,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$15,"出場",資金明細!$N$2:$N$15,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$17,"出場",資金明細!$N$2:$N$17,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3371,7 +3394,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$15)</f>
+        <f>MAX(資金明細!$U$2:$U$17)</f>
         <v/>
       </c>
     </row>
@@ -3387,7 +3410,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$15)</f>
+        <f>MAX(資金明細!$S$2:$S$17)</f>
         <v/>
       </c>
     </row>
@@ -3398,7 +3421,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V15</f>
+        <f>B5*資金明細!V17</f>
         <v/>
       </c>
     </row>
@@ -3420,7 +3443,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$15)</f>
+        <f>MAX(資金明細!$Y$2:$Y$17)</f>
         <v/>
       </c>
     </row>
@@ -3442,7 +3465,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$15,MATCH(1,資金明細!$Z$2:$Z$15,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$17,MATCH(1,資金明細!$Z$2:$Z$17,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3453,7 +3476,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$15,"進場",資金明細!$N$2:$N$15,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$17,"進場",資金明細!$N$2:$N$17,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3518,7 +3541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4991,9 +5014,202 @@
         <v/>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>46290.3375</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>SAGA_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>0.07862</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>0.07626139999999999</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>0.082551</v>
+      </c>
+      <c r="J16" s="17" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="16">
+        <f>資金模擬!$B$5*V15</f>
+        <v/>
+      </c>
+      <c r="N16" s="2">
+        <f>IF(Z15=1,"已停止",IF(T15&gt;=M16,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O16" s="16">
+        <f>IF(N16="已下單",M16*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P16" s="4" t="n"/>
+      <c r="Q16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="10">
+        <f>R15+Q16</f>
+        <v/>
+      </c>
+      <c r="S16" s="16">
+        <f>S15+IF(N16="已下單",M16,0)</f>
+        <v/>
+      </c>
+      <c r="T16" s="16">
+        <f>R16-S16</f>
+        <v/>
+      </c>
+      <c r="U16" s="2">
+        <f>U15+IF(N16="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V16" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R16,0),MAX(V15,FLOOR(MAX(R16,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W16" s="10">
+        <f>MAX(W15,R16)</f>
+        <v/>
+      </c>
+      <c r="X16" s="4">
+        <f>IF(W16&gt;0,R16/W16-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y16" s="16">
+        <f>IF(R16&gt;0,S16*資金模擬!$B$7/R16,0)</f>
+        <v/>
+      </c>
+      <c r="Z16" s="2">
+        <f>IF(OR(Z15=1,R16&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>46290.33819444444</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>SAGA_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>0.07862</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>0.07626139999999999</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>0.082551</v>
+      </c>
+      <c r="J17" s="17" t="n">
+        <v>0.07626139999999999</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L17" s="5">
+        <f>交易明細!K9</f>
+        <v/>
+      </c>
+      <c r="M17" s="16">
+        <f>M16</f>
+        <v/>
+      </c>
+      <c r="N17" s="2">
+        <f>N16</f>
+        <v/>
+      </c>
+      <c r="O17" s="16">
+        <f>O16</f>
+        <v/>
+      </c>
+      <c r="P17" s="4">
+        <f>交易明細!L9</f>
+        <v/>
+      </c>
+      <c r="Q17" s="10">
+        <f>IF(N17="已下單",O17*P17,0)</f>
+        <v/>
+      </c>
+      <c r="R17" s="10">
+        <f>R16+Q17</f>
+        <v/>
+      </c>
+      <c r="S17" s="16">
+        <f>S16-IF(N17="已下單",M17,0)</f>
+        <v/>
+      </c>
+      <c r="T17" s="16">
+        <f>R17-S17</f>
+        <v/>
+      </c>
+      <c r="U17" s="2">
+        <f>U16-IF(N17="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V17" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R17,0),MAX(V16,FLOOR(MAX(R17,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W17" s="10">
+        <f>MAX(W16,R17)</f>
+        <v/>
+      </c>
+      <c r="X17" s="4">
+        <f>IF(W17&gt;0,R17/W17-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y17" s="16">
+        <f>IF(R17&gt;0,S17*資金模擬!$B$7/R17,0)</f>
+        <v/>
+      </c>
+      <c r="Z17" s="2">
+        <f>IF(OR(Z16=1,R17&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z15"/>
-  <conditionalFormatting sqref="K2:K15">
+  <autoFilter ref="A1:Z17"/>
+  <conditionalFormatting sqref="K2:K17">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -5001,7 +5217,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N15">
+  <conditionalFormatting sqref="N2:N17">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -5009,7 +5225,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q15">
+  <conditionalFormatting sqref="Q2:Q17">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -5074,7 +5290,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-25 06:31（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-25 08:21（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5284,7 +5500,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$8),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$9),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5310,7 +5526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH8"/>
+  <dimension ref="A1:AH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6003,10 +6219,10 @@
         <v>1.3419</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>46290.27152777778</v>
+        <v>46290.34791666667</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>1.266</v>
+        <v>1.26</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -6162,9 +6378,100 @@
         <v>21</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SAGA_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>46290.3375</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.07862</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>0.07626139999999999</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>0.082551</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>46290.33819444444</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>0.07626139999999999</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K9" s="5">
+        <f>(H9-D9)*24</f>
+        <v/>
+      </c>
+      <c r="L9" s="4">
+        <f>IF(C9="做多",I9/E9-1,1-I9/E9)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
+      <c r="Q9" s="19" t="n"/>
+      <c r="R9" s="19" t="n"/>
+      <c r="S9" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="16" t="n"/>
+      <c r="V9" s="16" t="n"/>
+      <c r="W9" s="4" t="n"/>
+      <c r="X9" s="4" t="n"/>
+      <c r="Y9" s="4" t="n"/>
+      <c r="Z9" s="4" t="n"/>
+      <c r="AA9" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB9" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC9" s="4">
+        <f>(AB9+2*參數!$B$7)/(AA9+AB9)</f>
+        <v/>
+      </c>
+      <c r="AD9" s="2" t="n">
+        <v>0.07787302048525357</v>
+      </c>
+      <c r="AE9" s="2" t="n">
+        <v>0.5542907342236053</v>
+      </c>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>15分0.5倍</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="n">
+        <v>0.03270721134900811</v>
+      </c>
+      <c r="AH9" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AH8"/>
-  <conditionalFormatting sqref="J2:J8">
+  <autoFilter ref="A1:AH9"/>
+  <conditionalFormatting sqref="J2:J9">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -6185,7 +6492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6271,27 +6578,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A2,交易明細!$C$2:$C$8,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A2,交易明細!$C$2:$C$9,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A2,交易明細!$C$2:$C$8,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A2,交易明細!$C$2:$C$9,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$8,$A2,交易明細!$J$2:$J$8,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$9,$A2,交易明細!$J$2:$J$9,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A2,交易明細!$J$2:$J$8,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A2,交易明細!$J$2:$J$9,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A2,交易明細!$J$2:$J$8,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A2,交易明細!$J$2:$J$9,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -6299,19 +6606,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A2,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A2,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A2,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A2,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$B$2:$B$8,$A2,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A2,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A2,交易明細!$J$2:$J$8,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A2,交易明細!$J$2:$J$9,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -6322,27 +6629,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A3,交易明細!$C$2:$C$8,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A3,交易明細!$C$2:$C$9,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A3,交易明細!$C$2:$C$8,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A3,交易明細!$C$2:$C$9,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$8,$A3,交易明細!$J$2:$J$8,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$9,$A3,交易明細!$J$2:$J$9,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A3,交易明細!$J$2:$J$8,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A3,交易明細!$J$2:$J$9,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A3,交易明細!$J$2:$J$8,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A3,交易明細!$J$2:$J$9,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -6350,19 +6657,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A3,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A3,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A3,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A3,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$B$2:$B$8,$A3,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A3,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A3,交易明細!$J$2:$J$8,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A3,交易明細!$J$2:$J$9,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -6373,27 +6680,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A4,交易明細!$C$2:$C$8,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A4,交易明細!$C$2:$C$9,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A4,交易明細!$C$2:$C$8,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A4,交易明細!$C$2:$C$9,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$8,$A4,交易明細!$J$2:$J$8,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$9,$A4,交易明細!$J$2:$J$9,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A4,交易明細!$J$2:$J$8,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A4,交易明細!$J$2:$J$9,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A4,交易明細!$J$2:$J$8,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A4,交易明細!$J$2:$J$9,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -6401,19 +6708,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A4,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A4,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A4,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A4,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$B$2:$B$8,$A4,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A4,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A4,交易明細!$J$2:$J$8,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A4,交易明細!$J$2:$J$9,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -6424,27 +6731,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A5,交易明細!$C$2:$C$8,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A5,交易明細!$C$2:$C$9,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A5,交易明細!$C$2:$C$8,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A5,交易明細!$C$2:$C$9,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$8,$A5,交易明細!$J$2:$J$8,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$9,$A5,交易明細!$J$2:$J$9,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A5,交易明細!$J$2:$J$8,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A5,交易明細!$J$2:$J$9,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A5,交易明細!$J$2:$J$8,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A5,交易明細!$J$2:$J$9,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -6452,19 +6759,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A5,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A5,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A5,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A5,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$B$2:$B$8,$A5,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A5,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A5,交易明細!$J$2:$J$8,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A5,交易明細!$J$2:$J$9,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -6475,27 +6782,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A6,交易明細!$C$2:$C$8,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A6,交易明細!$C$2:$C$9,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A6,交易明細!$C$2:$C$8,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A6,交易明細!$C$2:$C$9,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$8,$A6,交易明細!$J$2:$J$8,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$9,$A6,交易明細!$J$2:$J$9,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A6,交易明細!$J$2:$J$8,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A6,交易明細!$J$2:$J$9,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A6,交易明細!$J$2:$J$8,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A6,交易明細!$J$2:$J$9,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -6503,19 +6810,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A6,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A6,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A6,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A6,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$B$2:$B$8,$A6,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A6,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A6,交易明細!$J$2:$J$8,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A6,交易明細!$J$2:$J$9,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -6526,27 +6833,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A7,交易明細!$C$2:$C$8,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A7,交易明細!$C$2:$C$9,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A7,交易明細!$C$2:$C$8,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A7,交易明細!$C$2:$C$9,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$8,$A7,交易明細!$J$2:$J$8,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$9,$A7,交易明細!$J$2:$J$9,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A7,交易明細!$J$2:$J$8,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A7,交易明細!$J$2:$J$9,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A7,交易明細!$J$2:$J$8,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A7,交易明細!$J$2:$J$9,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -6554,19 +6861,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A7,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A7,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A7,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A7,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$B$2:$B$8,$A7,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A7,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A7,交易明細!$J$2:$J$8,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A7,交易明細!$J$2:$J$9,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -6577,27 +6884,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A8,交易明細!$C$2:$C$8,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A8,交易明細!$C$2:$C$9,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A8,交易明細!$C$2:$C$8,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A8,交易明細!$C$2:$C$9,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$8,$A8,交易明細!$J$2:$J$8,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$9,$A8,交易明細!$J$2:$J$9,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A8,交易明細!$J$2:$J$8,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A8,交易明細!$J$2:$J$9,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A8,交易明細!$J$2:$J$8,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A8,交易明細!$J$2:$J$9,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -6605,24 +6912,75 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A8,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A8,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$8,交易明細!$B$2:$B$8,$A8,交易明細!$J$2:$J$8,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A8,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$8,交易明細!$B$2:$B$8,$A8,交易明細!$J$2:$J$8,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A8,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$8,$A8,交易明細!$J$2:$J$8,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A8,交易明細!$J$2:$J$9,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SAGA_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A9)</f>
+        <v/>
+      </c>
+      <c r="C9" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A9,交易明細!$C$2:$C$9,"做多")</f>
+        <v/>
+      </c>
+      <c r="D9" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A9,交易明細!$C$2:$C$9,"做空")</f>
+        <v/>
+      </c>
+      <c r="E9" s="2">
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$9,$A9,交易明細!$J$2:$J$9,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F9" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A9,交易明細!$J$2:$J$9,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G9" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A9,交易明細!$J$2:$J$9,"止損")</f>
+        <v/>
+      </c>
+      <c r="H9" s="4">
+        <f>IFERROR(F9/E9,0)</f>
+        <v/>
+      </c>
+      <c r="I9" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A9,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J9" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A9,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K9" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A9,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L9" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$9,$A9,交易明細!$J$2:$J$9,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L8"/>
+  <autoFilter ref="A1:L9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 08:21（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 09:35（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,56 +1086,56 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
@@ -1144,73 +1144,73 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
@@ -1219,21 +1219,21 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
@@ -1242,61 +1242,61 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
@@ -1305,44 +1305,44 @@
         <v>3</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
@@ -1357,15 +1357,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
@@ -1380,15 +1380,15 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
@@ -1403,15 +1403,15 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
@@ -1426,15 +1426,15 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
@@ -1449,15 +1449,15 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
@@ -1469,18 +1469,18 @@
         <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
@@ -1495,15 +1495,15 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
@@ -1518,15 +1518,15 @@
         <v>2</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
@@ -1541,18 +1541,18 @@
         <v>2</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
@@ -1564,15 +1564,15 @@
         <v>2</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>441</v>
@@ -1587,15 +1587,15 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>441</v>
@@ -1610,15 +1610,15 @@
         <v>2</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>441</v>
@@ -1633,18 +1633,18 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0</v>
@@ -1653,18 +1653,18 @@
         <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>440</v>
@@ -1679,15 +1679,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>440</v>
@@ -1702,15 +1702,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>440</v>
@@ -1725,15 +1725,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>440</v>
@@ -1748,15 +1748,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>440</v>
@@ -1771,15 +1771,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>440</v>
@@ -1794,15 +1794,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,18 +2691,18 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>0</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>442</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>442</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>442</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>442</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>442</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>442</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3110,10 +3110,10 @@
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,6 +3151,29 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B92" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -5290,7 +5313,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-25 08:21（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-25 09:35（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -6219,10 +6242,10 @@
         <v>1.3419</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>46290.34791666667</v>
+        <v>46290.39930555555</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>1.26</v>
+        <v>1.248</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -6248,7 +6271,7 @@
       <c r="Q7" s="19" t="n"/>
       <c r="R7" s="19" t="n"/>
       <c r="S7" s="4" t="n">
-        <v>0.02347417840375587</v>
+        <v>0.02503912363067295</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.04460093896713602</v>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,9 +17,9 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$17</f>
+              <f>'資金明細'!$R$2:$R$20</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 09:35（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 12:05（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -796,19 +796,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$9,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$10,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$9,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$10,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$9,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$10,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$9,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$10,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -816,35 +816,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$9,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$10,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$J$2:$J$9,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$J$2:$J$10,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$J$2:$J$9,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$J$2:$J$10,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$J$2:$J$9,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$J$2:$J$10,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$9,"&lt;&gt;未平倉",交易明細!$L$2:$L$9,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$10,"&lt;&gt;未平倉",交易明細!$L$2:$L$10,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$9,"做多",交易明細!$B$2:$B$9,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$10,"做多",交易明細!$B$2:$B$10,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -863,19 +863,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -883,35 +883,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$9,交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$10,交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$9,"做多",交易明細!$J$2:$J$9,"&lt;&gt;未平倉",交易明細!$L$2:$L$9,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"&lt;&gt;未平倉",交易明細!$L$2:$L$10,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$9,"做空",交易明細!$B$2:$B$9,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$10,"做空",交易明細!$B$2:$B$10,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -930,19 +930,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -950,35 +950,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$9,交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$10,交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$9,"做空",交易明細!$J$2:$J$9,"&lt;&gt;未平倉",交易明細!$L$2:$L$9,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"&lt;&gt;未平倉",交易明細!$L$2:$L$10,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,79 +1086,79 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
@@ -1167,73 +1167,73 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
@@ -1242,21 +1242,21 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1265,61 +1265,61 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
@@ -1328,44 +1328,44 @@
         <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
@@ -1380,15 +1380,15 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
@@ -1403,15 +1403,15 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
@@ -1426,15 +1426,15 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
@@ -1449,15 +1449,15 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
@@ -1472,15 +1472,15 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
@@ -1492,18 +1492,18 @@
         <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
@@ -1518,15 +1518,15 @@
         <v>2</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
@@ -1541,15 +1541,15 @@
         <v>2</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
@@ -1564,18 +1564,18 @@
         <v>2</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0</v>
@@ -1587,15 +1587,15 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>441</v>
@@ -1610,15 +1610,15 @@
         <v>2</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>441</v>
@@ -1633,15 +1633,15 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>441</v>
@@ -1656,18 +1656,18 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0</v>
@@ -1676,18 +1676,18 @@
         <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>440</v>
@@ -1702,15 +1702,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>440</v>
@@ -1725,15 +1725,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>440</v>
@@ -1748,15 +1748,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>440</v>
@@ -1771,15 +1771,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>440</v>
@@ -1794,15 +1794,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,18 +2714,18 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>0</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>442</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>442</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>442</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>442</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>442</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,6 +3174,29 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B93" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3239,7 +3262,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R17</f>
+        <f>資金明細!R20</f>
         <v/>
       </c>
     </row>
@@ -3277,7 +3300,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$17)</f>
+        <f>MAX(資金明細!$R$2:$R$20)</f>
         <v/>
       </c>
     </row>
@@ -3296,7 +3319,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$17)</f>
+        <f>MIN(資金明細!$R$2:$R$20)</f>
         <v/>
       </c>
     </row>
@@ -3316,7 +3339,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$17)</f>
+        <f>MIN(資金明細!$X$2:$X$20)</f>
         <v/>
       </c>
     </row>
@@ -3335,7 +3358,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$17,"進場",資金明細!$N$2:$N$17,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$20,"進場",資金明細!$N$2:$N$20,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3354,7 +3377,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$17,"進場",資金明細!$N$2:$N$17,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$20,"進場",資金明細!$N$2:$N$20,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3365,7 +3388,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$17,"出場",資金明細!$N$2:$N$17,"已下單",資金明細!$K$2:$K$17,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$20,"出場",資金明細!$N$2:$N$20,"已下單",資金明細!$K$2:$K$20,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3376,7 +3399,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$9),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$10),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3385,7 +3408,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$17,"出場",資金明細!$N$2:$N$17,"已下單",資金明細!$K$2:$K$17,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$20,"出場",資金明細!$N$2:$N$20,"已下單",資金明細!$K$2:$K$20,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3401,7 +3424,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$17,"出場",資金明細!$N$2:$N$17,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$20,"出場",資金明細!$N$2:$N$20,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3417,7 +3440,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$17)</f>
+        <f>MAX(資金明細!$U$2:$U$20)</f>
         <v/>
       </c>
     </row>
@@ -3433,7 +3456,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$17)</f>
+        <f>MAX(資金明細!$S$2:$S$20)</f>
         <v/>
       </c>
     </row>
@@ -3444,7 +3467,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V17</f>
+        <f>B5*資金明細!V20</f>
         <v/>
       </c>
     </row>
@@ -3455,7 +3478,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N13="已下單",資金明細!O13*交易明細!L7,0)</f>
+        <f>0</f>
         <v/>
       </c>
     </row>
@@ -3466,7 +3489,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$17)</f>
+        <f>MAX(資金明細!$Y$2:$Y$20)</f>
         <v/>
       </c>
     </row>
@@ -3488,7 +3511,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$17,MATCH(1,資金明細!$Z$2:$Z$17,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$20,MATCH(1,資金明細!$Z$2:$Z$20,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3499,7 +3522,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$17,"進場",資金明細!$N$2:$N$17,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$20,"進場",資金明細!$N$2:$N$20,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3564,7 +3587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4785,11 +4808,7 @@
         <v>1.3419</v>
       </c>
       <c r="J13" s="17" t="n"/>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K13" s="2" t="n"/>
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="16">
         <f>資金模擬!$B$5*V12</f>
@@ -5230,9 +5249,305 @@
         <v/>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>46290.44930555556</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>RIVER_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>1.278</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>1.23966</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>1.3419</v>
+      </c>
+      <c r="J18" s="17" t="n">
+        <v>1.23966</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L18" s="5">
+        <f>交易明細!K7</f>
+        <v/>
+      </c>
+      <c r="M18" s="16">
+        <f>M13</f>
+        <v/>
+      </c>
+      <c r="N18" s="2">
+        <f>N13</f>
+        <v/>
+      </c>
+      <c r="O18" s="16">
+        <f>O13</f>
+        <v/>
+      </c>
+      <c r="P18" s="4">
+        <f>交易明細!L7</f>
+        <v/>
+      </c>
+      <c r="Q18" s="10">
+        <f>IF(N18="已下單",O18*P18,0)</f>
+        <v/>
+      </c>
+      <c r="R18" s="10">
+        <f>R17+Q18</f>
+        <v/>
+      </c>
+      <c r="S18" s="16">
+        <f>S17-IF(N18="已下單",M18,0)</f>
+        <v/>
+      </c>
+      <c r="T18" s="16">
+        <f>R18-S18</f>
+        <v/>
+      </c>
+      <c r="U18" s="2">
+        <f>U17-IF(N18="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V18" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R18,0),MAX(V17,FLOOR(MAX(R18,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W18" s="10">
+        <f>MAX(W17,R18)</f>
+        <v/>
+      </c>
+      <c r="X18" s="4">
+        <f>IF(W18&gt;0,R18/W18-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y18" s="16">
+        <f>IF(R18&gt;0,S18*資金模擬!$B$7/R18,0)</f>
+        <v/>
+      </c>
+      <c r="Z18" s="2">
+        <f>IF(OR(Z17=1,R18&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>46290.45555555556</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>PLAY_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>0.04057</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>0.0393529</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>0.0425985</v>
+      </c>
+      <c r="J19" s="17" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="16">
+        <f>資金模擬!$B$5*V18</f>
+        <v/>
+      </c>
+      <c r="N19" s="2">
+        <f>IF(Z18=1,"已停止",IF(T18&gt;=M19,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O19" s="16">
+        <f>IF(N19="已下單",M19*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="10">
+        <f>R18+Q19</f>
+        <v/>
+      </c>
+      <c r="S19" s="16">
+        <f>S18+IF(N19="已下單",M19,0)</f>
+        <v/>
+      </c>
+      <c r="T19" s="16">
+        <f>R19-S19</f>
+        <v/>
+      </c>
+      <c r="U19" s="2">
+        <f>U18+IF(N19="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V19" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R19,0),MAX(V18,FLOOR(MAX(R19,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W19" s="10">
+        <f>MAX(W18,R19)</f>
+        <v/>
+      </c>
+      <c r="X19" s="4">
+        <f>IF(W19&gt;0,R19/W19-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y19" s="16">
+        <f>IF(R19&gt;0,S19*資金模擬!$B$7/R19,0)</f>
+        <v/>
+      </c>
+      <c r="Z19" s="2">
+        <f>IF(OR(Z18=1,R19&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>46290.48263888889</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>PLAY_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>0.04057</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>0.0393529</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>0.0425985</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>0.0393529</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L20" s="5">
+        <f>交易明細!K10</f>
+        <v/>
+      </c>
+      <c r="M20" s="16">
+        <f>M19</f>
+        <v/>
+      </c>
+      <c r="N20" s="2">
+        <f>N19</f>
+        <v/>
+      </c>
+      <c r="O20" s="16">
+        <f>O19</f>
+        <v/>
+      </c>
+      <c r="P20" s="4">
+        <f>交易明細!L10</f>
+        <v/>
+      </c>
+      <c r="Q20" s="10">
+        <f>IF(N20="已下單",O20*P20,0)</f>
+        <v/>
+      </c>
+      <c r="R20" s="10">
+        <f>R19+Q20</f>
+        <v/>
+      </c>
+      <c r="S20" s="16">
+        <f>S19-IF(N20="已下單",M20,0)</f>
+        <v/>
+      </c>
+      <c r="T20" s="16">
+        <f>R20-S20</f>
+        <v/>
+      </c>
+      <c r="U20" s="2">
+        <f>U19-IF(N20="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V20" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R20,0),MAX(V19,FLOOR(MAX(R20,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W20" s="10">
+        <f>MAX(W19,R20)</f>
+        <v/>
+      </c>
+      <c r="X20" s="4">
+        <f>IF(W20&gt;0,R20/W20-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y20" s="16">
+        <f>IF(R20&gt;0,S20*資金模擬!$B$7/R20,0)</f>
+        <v/>
+      </c>
+      <c r="Z20" s="2">
+        <f>IF(OR(Z19=1,R20&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z17"/>
-  <conditionalFormatting sqref="K2:K17">
+  <autoFilter ref="A1:Z20"/>
+  <conditionalFormatting sqref="K2:K20">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -5240,7 +5555,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N17">
+  <conditionalFormatting sqref="N2:N20">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -5248,7 +5563,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q17">
+  <conditionalFormatting sqref="Q2:Q20">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -5313,7 +5628,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-25 09:35（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-25 12:05（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5523,7 +5838,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$9),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$10),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5549,7 +5864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH9"/>
+  <dimension ref="A1:AH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6242,14 +6557,14 @@
         <v>1.3419</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>46290.39930555555</v>
+        <v>46290.44930555556</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>1.248</v>
+        <v>1.23966</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K7" s="5">
@@ -6260,18 +6575,14 @@
         <f>IF(C7="做多",I7/E7-1,1-I7/E7)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="4" t="n"/>
       <c r="O7" s="4" t="n"/>
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="19" t="n"/>
       <c r="R7" s="19" t="n"/>
       <c r="S7" s="4" t="n">
-        <v>0.02503912363067295</v>
+        <v>0.03</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0.04460093896713602</v>
@@ -6492,9 +6803,100 @@
         <v>6</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>PLAY_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>46290.45555555556</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0.04057</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>0.0393529</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>0.0425985</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>46290.48263888889</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>0.0393529</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K10" s="5">
+        <f>(H10-D10)*24</f>
+        <v/>
+      </c>
+      <c r="L10" s="4">
+        <f>IF(C10="做多",I10/E10-1,1-I10/E10)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
+      <c r="Q10" s="19" t="n"/>
+      <c r="R10" s="19" t="n"/>
+      <c r="S10" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>0.01947251663790972</v>
+      </c>
+      <c r="U10" s="16" t="n"/>
+      <c r="V10" s="16" t="n"/>
+      <c r="W10" s="4" t="n"/>
+      <c r="X10" s="4" t="n"/>
+      <c r="Y10" s="4" t="n"/>
+      <c r="Z10" s="4" t="n"/>
+      <c r="AA10" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB10" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC10" s="4">
+        <f>(AB10+2*參數!$B$7)/(AA10+AB10)</f>
+        <v/>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>0.06444740346205058</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>2.46672496232488</v>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>2倍</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="n">
+        <v>0.0002465483234714849</v>
+      </c>
+      <c r="AH10" s="2" t="n">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AH9"/>
-  <conditionalFormatting sqref="J2:J9">
+  <autoFilter ref="A1:AH10"/>
+  <conditionalFormatting sqref="J2:J10">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -6515,7 +6917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6601,27 +7003,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A2,交易明細!$C$2:$C$9,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A2,交易明細!$C$2:$C$10,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A2,交易明細!$C$2:$C$9,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A2,交易明細!$C$2:$C$10,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$9,$A2,交易明細!$J$2:$J$9,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$10,$A2,交易明細!$J$2:$J$10,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A2,交易明細!$J$2:$J$9,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A2,交易明細!$J$2:$J$10,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A2,交易明細!$J$2:$J$9,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A2,交易明細!$J$2:$J$10,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -6629,19 +7031,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A2,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A2,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A2,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A2,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A2,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A2,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A2,交易明細!$J$2:$J$9,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A2,交易明細!$J$2:$J$10,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -6652,27 +7054,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A3,交易明細!$C$2:$C$9,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A3,交易明細!$C$2:$C$10,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A3,交易明細!$C$2:$C$9,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A3,交易明細!$C$2:$C$10,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$9,$A3,交易明細!$J$2:$J$9,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$10,$A3,交易明細!$J$2:$J$10,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A3,交易明細!$J$2:$J$9,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A3,交易明細!$J$2:$J$10,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A3,交易明細!$J$2:$J$9,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A3,交易明細!$J$2:$J$10,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -6680,19 +7082,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A3,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A3,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A3,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A3,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A3,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A3,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A3,交易明細!$J$2:$J$9,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A3,交易明細!$J$2:$J$10,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -6703,27 +7105,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A4,交易明細!$C$2:$C$9,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A4,交易明細!$C$2:$C$10,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A4,交易明細!$C$2:$C$9,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A4,交易明細!$C$2:$C$10,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$9,$A4,交易明細!$J$2:$J$9,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$10,$A4,交易明細!$J$2:$J$10,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A4,交易明細!$J$2:$J$9,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A4,交易明細!$J$2:$J$10,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A4,交易明細!$J$2:$J$9,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A4,交易明細!$J$2:$J$10,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -6731,19 +7133,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A4,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A4,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A4,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A4,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A4,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A4,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A4,交易明細!$J$2:$J$9,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A4,交易明細!$J$2:$J$10,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -6754,27 +7156,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A5,交易明細!$C$2:$C$9,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A5,交易明細!$C$2:$C$10,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A5,交易明細!$C$2:$C$9,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A5,交易明細!$C$2:$C$10,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$9,$A5,交易明細!$J$2:$J$9,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$10,$A5,交易明細!$J$2:$J$10,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A5,交易明細!$J$2:$J$9,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A5,交易明細!$J$2:$J$10,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A5,交易明細!$J$2:$J$9,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A5,交易明細!$J$2:$J$10,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -6782,19 +7184,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A5,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A5,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A5,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A5,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A5,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A5,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A5,交易明細!$J$2:$J$9,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A5,交易明細!$J$2:$J$10,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -6805,27 +7207,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A6,交易明細!$C$2:$C$9,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A6,交易明細!$C$2:$C$10,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A6,交易明細!$C$2:$C$9,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A6,交易明細!$C$2:$C$10,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$9,$A6,交易明細!$J$2:$J$9,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$10,$A6,交易明細!$J$2:$J$10,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A6,交易明細!$J$2:$J$9,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A6,交易明細!$J$2:$J$10,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A6,交易明細!$J$2:$J$9,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A6,交易明細!$J$2:$J$10,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -6833,19 +7235,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A6,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A6,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A6,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A6,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A6,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A6,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A6,交易明細!$J$2:$J$9,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A6,交易明細!$J$2:$J$10,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -6856,27 +7258,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A7,交易明細!$C$2:$C$9,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A7,交易明細!$C$2:$C$10,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A7,交易明細!$C$2:$C$9,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A7,交易明細!$C$2:$C$10,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$9,$A7,交易明細!$J$2:$J$9,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$10,$A7,交易明細!$J$2:$J$10,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A7,交易明細!$J$2:$J$9,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A7,交易明細!$J$2:$J$10,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A7,交易明細!$J$2:$J$9,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A7,交易明細!$J$2:$J$10,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -6884,19 +7286,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A7,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A7,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A7,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A7,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A7,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A7,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A7,交易明細!$J$2:$J$9,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A7,交易明細!$J$2:$J$10,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -6907,27 +7309,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A8,交易明細!$C$2:$C$9,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A8,交易明細!$C$2:$C$10,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A8,交易明細!$C$2:$C$9,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A8,交易明細!$C$2:$C$10,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$9,$A8,交易明細!$J$2:$J$9,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$10,$A8,交易明細!$J$2:$J$10,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A8,交易明細!$J$2:$J$9,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A8,交易明細!$J$2:$J$10,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A8,交易明細!$J$2:$J$9,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A8,交易明細!$J$2:$J$10,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -6935,19 +7337,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A8,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A8,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A8,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A8,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A8,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A8,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A8,交易明細!$J$2:$J$9,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A8,交易明細!$J$2:$J$10,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -6958,27 +7360,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A9,交易明細!$C$2:$C$9,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A9,交易明細!$C$2:$C$10,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A9,交易明細!$C$2:$C$9,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A9,交易明細!$C$2:$C$10,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$9,$A9,交易明細!$J$2:$J$9,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$10,$A9,交易明細!$J$2:$J$10,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A9,交易明細!$J$2:$J$9,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A9,交易明細!$J$2:$J$10,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A9,交易明細!$J$2:$J$9,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A9,交易明細!$J$2:$J$10,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -6986,24 +7388,75 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A9,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A9,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$9,交易明細!$B$2:$B$9,$A9,交易明細!$J$2:$J$9,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A9,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$9,交易明細!$B$2:$B$9,$A9,交易明細!$J$2:$J$9,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A9,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$9,$A9,交易明細!$J$2:$J$9,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A9,交易明細!$J$2:$J$10,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>PLAY_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A10,交易明細!$C$2:$C$10,"做多")</f>
+        <v/>
+      </c>
+      <c r="D10" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A10,交易明細!$C$2:$C$10,"做空")</f>
+        <v/>
+      </c>
+      <c r="E10" s="2">
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$10,$A10,交易明細!$J$2:$J$10,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F10" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A10,交易明細!$J$2:$J$10,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G10" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A10,交易明細!$J$2:$J$10,"止損")</f>
+        <v/>
+      </c>
+      <c r="H10" s="4">
+        <f>IFERROR(F10/E10,0)</f>
+        <v/>
+      </c>
+      <c r="I10" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A10,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J10" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A10,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K10" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A10,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$10,$A10,交易明細!$J$2:$J$10,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L9"/>
+  <autoFilter ref="A1:L10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12732,11 +13185,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C316" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C316" s="2" t="inlineStr"/>
       <c r="D316" s="2" t="n"/>
       <c r="E316" s="17" t="n"/>
       <c r="F316" s="17" t="n"/>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,9 +17,9 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$20</f>
+              <f>'資金明細'!$R$2:$R$21</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 12:05（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 13:21（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -796,19 +796,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$10,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$11,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$10,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$11,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$10,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$11,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$10,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$11,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -816,35 +816,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$10,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$11,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$J$2:$J$10,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$J$2:$J$11,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$J$2:$J$10,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$J$2:$J$11,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$J$2:$J$10,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$J$2:$J$11,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$10,"&lt;&gt;未平倉",交易明細!$L$2:$L$10,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$11,"&lt;&gt;未平倉",交易明細!$L$2:$L$11,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$10,"做多",交易明細!$B$2:$B$10,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$11,"做多",交易明細!$B$2:$B$11,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -863,19 +863,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -883,35 +883,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$10,交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$11,交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$10,"做多",交易明細!$J$2:$J$10,"&lt;&gt;未平倉",交易明細!$L$2:$L$10,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"&lt;&gt;未平倉",交易明細!$L$2:$L$11,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$10,"做空",交易明細!$B$2:$B$10,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$11,"做空",交易明細!$B$2:$B$11,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -930,19 +930,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -950,35 +950,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$10,交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$11,交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$10,"做空",交易明細!$J$2:$J$10,"&lt;&gt;未平倉",交易明細!$L$2:$L$10,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"&lt;&gt;未平倉",交易明細!$L$2:$L$11,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
@@ -1098,90 +1098,90 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
@@ -1190,73 +1190,73 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1265,21 +1265,21 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
@@ -1288,61 +1288,61 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
@@ -1351,44 +1351,44 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
@@ -1403,15 +1403,15 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
@@ -1426,15 +1426,15 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
@@ -1449,15 +1449,15 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
@@ -1472,15 +1472,15 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
@@ -1495,15 +1495,15 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
@@ -1515,18 +1515,18 @@
         <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
@@ -1541,15 +1541,15 @@
         <v>2</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
@@ -1564,15 +1564,15 @@
         <v>2</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
@@ -1587,18 +1587,18 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
@@ -1610,15 +1610,15 @@
         <v>2</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>441</v>
@@ -1633,15 +1633,15 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>441</v>
@@ -1656,15 +1656,15 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>441</v>
@@ -1679,18 +1679,18 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0</v>
@@ -1699,18 +1699,18 @@
         <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>440</v>
@@ -1725,15 +1725,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>440</v>
@@ -1748,15 +1748,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>440</v>
@@ -1771,15 +1771,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>440</v>
@@ -1794,15 +1794,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,18 +2737,18 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>0</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>442</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>442</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>442</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>442</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3156,10 +3156,10 @@
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,6 +3197,29 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B94" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3262,7 +3285,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R20</f>
+        <f>資金明細!R21</f>
         <v/>
       </c>
     </row>
@@ -3300,7 +3323,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$20)</f>
+        <f>MAX(資金明細!$R$2:$R$21)</f>
         <v/>
       </c>
     </row>
@@ -3319,7 +3342,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$20)</f>
+        <f>MIN(資金明細!$R$2:$R$21)</f>
         <v/>
       </c>
     </row>
@@ -3339,7 +3362,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$20)</f>
+        <f>MIN(資金明細!$X$2:$X$21)</f>
         <v/>
       </c>
     </row>
@@ -3358,7 +3381,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$20,"進場",資金明細!$N$2:$N$20,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$21,"進場",資金明細!$N$2:$N$21,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3377,7 +3400,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$20,"進場",資金明細!$N$2:$N$20,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$21,"進場",資金明細!$N$2:$N$21,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3388,7 +3411,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$20,"出場",資金明細!$N$2:$N$20,"已下單",資金明細!$K$2:$K$20,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$21,"出場",資金明細!$N$2:$N$21,"已下單",資金明細!$K$2:$K$21,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3399,7 +3422,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$10),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$11),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3408,7 +3431,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$20,"出場",資金明細!$N$2:$N$20,"已下單",資金明細!$K$2:$K$20,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$21,"出場",資金明細!$N$2:$N$21,"已下單",資金明細!$K$2:$K$21,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3424,7 +3447,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$20,"出場",資金明細!$N$2:$N$20,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$21,"出場",資金明細!$N$2:$N$21,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3440,7 +3463,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$20)</f>
+        <f>MAX(資金明細!$U$2:$U$21)</f>
         <v/>
       </c>
     </row>
@@ -3456,7 +3479,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$20)</f>
+        <f>MAX(資金明細!$S$2:$S$21)</f>
         <v/>
       </c>
     </row>
@@ -3467,7 +3490,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V20</f>
+        <f>B5*資金明細!V21</f>
         <v/>
       </c>
     </row>
@@ -3478,7 +3501,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>0</f>
+        <f>IF(資金明細!N21="已下單",資金明細!O21*交易明細!L11,0)</f>
         <v/>
       </c>
     </row>
@@ -3489,7 +3512,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$20)</f>
+        <f>MAX(資金明細!$Y$2:$Y$21)</f>
         <v/>
       </c>
     </row>
@@ -3511,7 +3534,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$20,MATCH(1,資金明細!$Z$2:$Z$20,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$21,MATCH(1,資金明細!$Z$2:$Z$21,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3522,7 +3545,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$20,"進場",資金明細!$N$2:$N$20,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$21,"進場",資金明細!$N$2:$N$21,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3587,7 +3610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5545,9 +5568,103 @@
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>46290.54375</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>MOVR_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>0.94478</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>1.0227</v>
+      </c>
+      <c r="J21" s="17" t="n"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="16">
+        <f>資金模擬!$B$5*V20</f>
+        <v/>
+      </c>
+      <c r="N21" s="2">
+        <f>IF(Z20=1,"已停止",IF(T20&gt;=M21,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O21" s="16">
+        <f>IF(N21="已下單",M21*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P21" s="4" t="n"/>
+      <c r="Q21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="10">
+        <f>R20+Q21</f>
+        <v/>
+      </c>
+      <c r="S21" s="16">
+        <f>S20+IF(N21="已下單",M21,0)</f>
+        <v/>
+      </c>
+      <c r="T21" s="16">
+        <f>R21-S21</f>
+        <v/>
+      </c>
+      <c r="U21" s="2">
+        <f>U20+IF(N21="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V21" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R21,0),MAX(V20,FLOOR(MAX(R21,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W21" s="10">
+        <f>MAX(W20,R21)</f>
+        <v/>
+      </c>
+      <c r="X21" s="4">
+        <f>IF(W21&gt;0,R21/W21-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y21" s="16">
+        <f>IF(R21&gt;0,S21*資金模擬!$B$7/R21,0)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="2">
+        <f>IF(OR(Z20=1,R21&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z20"/>
-  <conditionalFormatting sqref="K2:K20">
+  <autoFilter ref="A1:Z21"/>
+  <conditionalFormatting sqref="K2:K21">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -5555,7 +5672,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N20">
+  <conditionalFormatting sqref="N2:N21">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -5563,7 +5680,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q20">
+  <conditionalFormatting sqref="Q2:Q21">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -5628,7 +5745,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-25 12:05（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-25 13:21（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5838,7 +5955,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$10),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$11),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5864,7 +5981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH10"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6894,9 +7011,104 @@
         <v>56</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>MOVR_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>46290.54375</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>0.94478</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>1.0227</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>46290.55625</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K11" s="5">
+        <f>(H11-D11)*24</f>
+        <v/>
+      </c>
+      <c r="L11" s="4">
+        <f>IF(C11="做多",I11/E11-1,1-I11/E11)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
+      <c r="Q11" s="19" t="n"/>
+      <c r="R11" s="19" t="n"/>
+      <c r="S11" s="4" t="n">
+        <v>0.01745379876796715</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>0.01540041067761799</v>
+      </c>
+      <c r="U11" s="16" t="n"/>
+      <c r="V11" s="16" t="n"/>
+      <c r="W11" s="4" t="n"/>
+      <c r="X11" s="4" t="n"/>
+      <c r="Y11" s="4" t="n"/>
+      <c r="Z11" s="4" t="n"/>
+      <c r="AA11" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB11" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC11" s="4">
+        <f>(AB11+2*參數!$B$7)/(AA11+AB11)</f>
+        <v/>
+      </c>
+      <c r="AD11" s="2" t="n">
+        <v>0.0723025583982202</v>
+      </c>
+      <c r="AE11" s="2" t="n">
+        <v>0.697488740609033</v>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>15分0.5倍</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="n">
+        <v>0.007238883143743546</v>
+      </c>
+      <c r="AH11" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AH10"/>
-  <conditionalFormatting sqref="J2:J10">
+  <autoFilter ref="A1:AH11"/>
+  <conditionalFormatting sqref="J2:J11">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -6917,7 +7129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7003,27 +7215,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A2,交易明細!$C$2:$C$10,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A2,交易明細!$C$2:$C$11,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A2,交易明細!$C$2:$C$10,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A2,交易明細!$C$2:$C$11,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$10,$A2,交易明細!$J$2:$J$10,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$11,$A2,交易明細!$J$2:$J$11,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A2,交易明細!$J$2:$J$10,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A2,交易明細!$J$2:$J$11,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A2,交易明細!$J$2:$J$10,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A2,交易明細!$J$2:$J$11,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -7031,19 +7243,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A2,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A2,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A2,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A2,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A2,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A2,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A2,交易明細!$J$2:$J$10,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A2,交易明細!$J$2:$J$11,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7054,27 +7266,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A3,交易明細!$C$2:$C$10,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A3,交易明細!$C$2:$C$11,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A3,交易明細!$C$2:$C$10,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A3,交易明細!$C$2:$C$11,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$10,$A3,交易明細!$J$2:$J$10,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$11,$A3,交易明細!$J$2:$J$11,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A3,交易明細!$J$2:$J$10,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A3,交易明細!$J$2:$J$11,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A3,交易明細!$J$2:$J$10,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A3,交易明細!$J$2:$J$11,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -7082,19 +7294,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A3,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A3,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A3,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A3,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A3,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A3,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A3,交易明細!$J$2:$J$10,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A3,交易明細!$J$2:$J$11,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7105,27 +7317,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A4,交易明細!$C$2:$C$10,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A4,交易明細!$C$2:$C$11,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A4,交易明細!$C$2:$C$10,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A4,交易明細!$C$2:$C$11,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$10,$A4,交易明細!$J$2:$J$10,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$11,$A4,交易明細!$J$2:$J$11,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A4,交易明細!$J$2:$J$10,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A4,交易明細!$J$2:$J$11,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A4,交易明細!$J$2:$J$10,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A4,交易明細!$J$2:$J$11,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -7133,19 +7345,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A4,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A4,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A4,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A4,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A4,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A4,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A4,交易明細!$J$2:$J$10,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A4,交易明細!$J$2:$J$11,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7156,27 +7368,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A5,交易明細!$C$2:$C$10,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A5,交易明細!$C$2:$C$11,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A5,交易明細!$C$2:$C$10,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A5,交易明細!$C$2:$C$11,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$10,$A5,交易明細!$J$2:$J$10,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$11,$A5,交易明細!$J$2:$J$11,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A5,交易明細!$J$2:$J$10,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A5,交易明細!$J$2:$J$11,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A5,交易明細!$J$2:$J$10,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A5,交易明細!$J$2:$J$11,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -7184,19 +7396,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A5,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A5,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A5,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A5,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A5,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A5,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A5,交易明細!$J$2:$J$10,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A5,交易明細!$J$2:$J$11,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7207,27 +7419,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A6,交易明細!$C$2:$C$10,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A6,交易明細!$C$2:$C$11,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A6,交易明細!$C$2:$C$10,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A6,交易明細!$C$2:$C$11,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$10,$A6,交易明細!$J$2:$J$10,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$11,$A6,交易明細!$J$2:$J$11,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A6,交易明細!$J$2:$J$10,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A6,交易明細!$J$2:$J$11,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A6,交易明細!$J$2:$J$10,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A6,交易明細!$J$2:$J$11,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -7235,19 +7447,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A6,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A6,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A6,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A6,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A6,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A6,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A6,交易明細!$J$2:$J$10,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A6,交易明細!$J$2:$J$11,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7258,27 +7470,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A7,交易明細!$C$2:$C$10,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A7,交易明細!$C$2:$C$11,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A7,交易明細!$C$2:$C$10,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A7,交易明細!$C$2:$C$11,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$10,$A7,交易明細!$J$2:$J$10,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$11,$A7,交易明細!$J$2:$J$11,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A7,交易明細!$J$2:$J$10,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A7,交易明細!$J$2:$J$11,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A7,交易明細!$J$2:$J$10,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A7,交易明細!$J$2:$J$11,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -7286,19 +7498,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A7,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A7,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A7,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A7,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A7,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A7,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A7,交易明細!$J$2:$J$10,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A7,交易明細!$J$2:$J$11,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7309,27 +7521,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A8,交易明細!$C$2:$C$10,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A8,交易明細!$C$2:$C$11,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A8,交易明細!$C$2:$C$10,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A8,交易明細!$C$2:$C$11,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$10,$A8,交易明細!$J$2:$J$10,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$11,$A8,交易明細!$J$2:$J$11,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A8,交易明細!$J$2:$J$10,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A8,交易明細!$J$2:$J$11,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A8,交易明細!$J$2:$J$10,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A8,交易明細!$J$2:$J$11,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -7337,19 +7549,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A8,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A8,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A8,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A8,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A8,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A8,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A8,交易明細!$J$2:$J$10,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A8,交易明細!$J$2:$J$11,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7360,27 +7572,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A9,交易明細!$C$2:$C$10,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A9,交易明細!$C$2:$C$11,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A9,交易明細!$C$2:$C$10,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A9,交易明細!$C$2:$C$11,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$10,$A9,交易明細!$J$2:$J$10,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$11,$A9,交易明細!$J$2:$J$11,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A9,交易明細!$J$2:$J$10,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A9,交易明細!$J$2:$J$11,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A9,交易明細!$J$2:$J$10,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A9,交易明細!$J$2:$J$11,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -7388,19 +7600,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A9,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A9,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A9,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A9,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A9,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A9,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A9,交易明細!$J$2:$J$10,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A9,交易明細!$J$2:$J$11,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7411,27 +7623,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A10,交易明細!$C$2:$C$10,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A10,交易明細!$C$2:$C$11,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A10,交易明細!$C$2:$C$10,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A10,交易明細!$C$2:$C$11,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$10,$A10,交易明細!$J$2:$J$10,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$11,$A10,交易明細!$J$2:$J$11,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A10,交易明細!$J$2:$J$10,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A10,交易明細!$J$2:$J$11,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A10,交易明細!$J$2:$J$10,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A10,交易明細!$J$2:$J$11,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -7439,24 +7651,75 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A10,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A10,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$10,交易明細!$B$2:$B$10,$A10,交易明細!$J$2:$J$10,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A10,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$10,交易明細!$B$2:$B$10,$A10,交易明細!$J$2:$J$10,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A10,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$10,$A10,交易明細!$J$2:$J$10,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A10,交易明細!$J$2:$J$11,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>MOVR_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B11" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A11,交易明細!$C$2:$C$11,"做多")</f>
+        <v/>
+      </c>
+      <c r="D11" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A11,交易明細!$C$2:$C$11,"做空")</f>
+        <v/>
+      </c>
+      <c r="E11" s="2">
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$11,$A11,交易明細!$J$2:$J$11,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F11" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A11,交易明細!$J$2:$J$11,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G11" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A11,交易明細!$J$2:$J$11,"止損")</f>
+        <v/>
+      </c>
+      <c r="H11" s="4">
+        <f>IFERROR(F11/E11,0)</f>
+        <v/>
+      </c>
+      <c r="I11" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A11,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J11" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A11,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K11" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A11,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L11" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$11,$A11,交易明細!$J$2:$J$11,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L10"/>
+  <autoFilter ref="A1:L11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11907,7 +12170,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C245" s="2" t="inlineStr"/>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D245" s="2" t="n"/>
       <c r="E245" s="17" t="n"/>
       <c r="F245" s="17" t="n"/>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,7 +17,7 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$21</f>
+              <f>'資金明細'!$R$2:$R$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 13:21（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 14:49（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,33 +1086,33 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
@@ -1121,90 +1121,90 @@
         <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
@@ -1213,73 +1213,73 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
@@ -1288,21 +1288,21 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
@@ -1311,61 +1311,61 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
@@ -1374,44 +1374,44 @@
         <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
@@ -1426,15 +1426,15 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
@@ -1449,15 +1449,15 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
@@ -1472,15 +1472,15 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
@@ -1495,15 +1495,15 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
@@ -1518,15 +1518,15 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
@@ -1538,18 +1538,18 @@
         <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
@@ -1564,15 +1564,15 @@
         <v>2</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
@@ -1587,15 +1587,15 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
@@ -1610,18 +1610,18 @@
         <v>2</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0</v>
@@ -1633,15 +1633,15 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>441</v>
@@ -1656,15 +1656,15 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>441</v>
@@ -1679,15 +1679,15 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>441</v>
@@ -1702,18 +1702,18 @@
         <v>2</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0</v>
@@ -1722,18 +1722,18 @@
         <v>0</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>440</v>
@@ -1748,15 +1748,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>440</v>
@@ -1771,15 +1771,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>440</v>
@@ -1794,15 +1794,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,18 +2760,18 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>0</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>442</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>442</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>442</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,15 +3197,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3220,6 +3220,29 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B95" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3285,7 +3308,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R21</f>
+        <f>資金明細!R22</f>
         <v/>
       </c>
     </row>
@@ -3323,7 +3346,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$21)</f>
+        <f>MAX(資金明細!$R$2:$R$22)</f>
         <v/>
       </c>
     </row>
@@ -3342,7 +3365,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$21)</f>
+        <f>MIN(資金明細!$R$2:$R$22)</f>
         <v/>
       </c>
     </row>
@@ -3362,7 +3385,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$21)</f>
+        <f>MIN(資金明細!$X$2:$X$22)</f>
         <v/>
       </c>
     </row>
@@ -3381,7 +3404,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$21,"進場",資金明細!$N$2:$N$21,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$22,"進場",資金明細!$N$2:$N$22,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3400,7 +3423,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$21,"進場",資金明細!$N$2:$N$21,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$22,"進場",資金明細!$N$2:$N$22,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3411,7 +3434,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$21,"出場",資金明細!$N$2:$N$21,"已下單",資金明細!$K$2:$K$21,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$22,"出場",資金明細!$N$2:$N$22,"已下單",資金明細!$K$2:$K$22,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3431,7 +3454,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$21,"出場",資金明細!$N$2:$N$21,"已下單",資金明細!$K$2:$K$21,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$22,"出場",資金明細!$N$2:$N$22,"已下單",資金明細!$K$2:$K$22,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3447,7 +3470,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$21,"出場",資金明細!$N$2:$N$21,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$22,"出場",資金明細!$N$2:$N$22,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3463,7 +3486,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$21)</f>
+        <f>MAX(資金明細!$U$2:$U$22)</f>
         <v/>
       </c>
     </row>
@@ -3479,7 +3502,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$21)</f>
+        <f>MAX(資金明細!$S$2:$S$22)</f>
         <v/>
       </c>
     </row>
@@ -3490,7 +3513,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V21</f>
+        <f>B5*資金明細!V22</f>
         <v/>
       </c>
     </row>
@@ -3501,7 +3524,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N21="已下單",資金明細!O21*交易明細!L11,0)</f>
+        <f>0</f>
         <v/>
       </c>
     </row>
@@ -3512,7 +3535,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$21)</f>
+        <f>MAX(資金明細!$Y$2:$Y$22)</f>
         <v/>
       </c>
     </row>
@@ -3534,7 +3557,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$21,MATCH(1,資金明細!$Z$2:$Z$21,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$22,MATCH(1,資金明細!$Z$2:$Z$22,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3545,7 +3568,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$21,"進場",資金明細!$N$2:$N$21,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$22,"進場",資金明細!$N$2:$N$22,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3610,7 +3633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5603,11 +5626,7 @@
         <v>1.0227</v>
       </c>
       <c r="J21" s="17" t="n"/>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K21" s="2" t="n"/>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="16">
         <f>資金模擬!$B$5*V20</f>
@@ -5662,9 +5681,112 @@
         <v/>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>46290.55763888889</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>MOVR_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>0.94478</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>1.0227</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>0.94478</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L22" s="5">
+        <f>交易明細!K11</f>
+        <v/>
+      </c>
+      <c r="M22" s="16">
+        <f>M21</f>
+        <v/>
+      </c>
+      <c r="N22" s="2">
+        <f>N21</f>
+        <v/>
+      </c>
+      <c r="O22" s="16">
+        <f>O21</f>
+        <v/>
+      </c>
+      <c r="P22" s="4">
+        <f>交易明細!L11</f>
+        <v/>
+      </c>
+      <c r="Q22" s="10">
+        <f>IF(N22="已下單",O22*P22,0)</f>
+        <v/>
+      </c>
+      <c r="R22" s="10">
+        <f>R21+Q22</f>
+        <v/>
+      </c>
+      <c r="S22" s="16">
+        <f>S21-IF(N22="已下單",M22,0)</f>
+        <v/>
+      </c>
+      <c r="T22" s="16">
+        <f>R22-S22</f>
+        <v/>
+      </c>
+      <c r="U22" s="2">
+        <f>U21-IF(N22="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V22" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R22,0),MAX(V21,FLOOR(MAX(R22,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W22" s="10">
+        <f>MAX(W21,R22)</f>
+        <v/>
+      </c>
+      <c r="X22" s="4">
+        <f>IF(W22&gt;0,R22/W22-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y22" s="16">
+        <f>IF(R22&gt;0,S22*資金模擬!$B$7/R22,0)</f>
+        <v/>
+      </c>
+      <c r="Z22" s="2">
+        <f>IF(OR(Z21=1,R22&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z21"/>
-  <conditionalFormatting sqref="K2:K21">
+  <autoFilter ref="A1:Z22"/>
+  <conditionalFormatting sqref="K2:K22">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -5672,7 +5794,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N21">
+  <conditionalFormatting sqref="N2:N22">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -5680,7 +5802,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q21">
+  <conditionalFormatting sqref="Q2:Q22">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -5745,7 +5867,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-25 13:21（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-25 14:49（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -7038,14 +7160,14 @@
         <v>1.0227</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>46290.55625</v>
+        <v>46290.55763888889</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>0.988</v>
+        <v>0.94478</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K11" s="5">
@@ -7056,21 +7178,17 @@
         <f>IF(C11="做多",I11/E11-1,1-I11/E11)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="4" t="n"/>
       <c r="O11" s="4" t="n"/>
       <c r="P11" s="4" t="n"/>
       <c r="Q11" s="19" t="n"/>
       <c r="R11" s="19" t="n"/>
       <c r="S11" s="4" t="n">
-        <v>0.01745379876796715</v>
+        <v>0.03</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.01540041067761799</v>
+        <v>0.01642710472279263</v>
       </c>
       <c r="U11" s="16" t="n"/>
       <c r="V11" s="16" t="n"/>
@@ -12170,11 +12288,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C245" s="2" t="inlineStr"/>
       <c r="D245" s="2" t="n"/>
       <c r="E245" s="17" t="n"/>
       <c r="F245" s="17" t="n"/>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,8 +17,8 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
   </definedNames>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$22</f>
+              <f>'資金明細'!$R$2:$R$23</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 14:49（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 15:55（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -796,19 +796,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$11,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$12,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$11,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$12,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$11,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$12,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$11,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$12,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -816,35 +816,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$11,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$12,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$J$2:$J$11,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$J$2:$J$12,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$J$2:$J$11,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$J$2:$J$12,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$J$2:$J$11,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$J$2:$J$12,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$11,"&lt;&gt;未平倉",交易明細!$L$2:$L$11,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$12,"&lt;&gt;未平倉",交易明細!$L$2:$L$12,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$11,"做多",交易明細!$B$2:$B$11,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$12,"做多",交易明細!$B$2:$B$12,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -863,19 +863,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -883,35 +883,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$11,交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$12,交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$11,"做多",交易明細!$J$2:$J$11,"&lt;&gt;未平倉",交易明細!$L$2:$L$11,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"&lt;&gt;未平倉",交易明細!$L$2:$L$12,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$11,"做空",交易明細!$B$2:$B$11,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$12,"做空",交易明細!$B$2:$B$12,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -930,19 +930,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -950,35 +950,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$11,交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$12,交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$11,"做空",交易明細!$J$2:$J$11,"&lt;&gt;未平倉",交易明細!$L$2:$L$11,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"&lt;&gt;未平倉",交易明細!$L$2:$L$12,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,56 +1086,56 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46290.61757802084</v>
+        <v>46290.66382769676</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46290.61666666667</v>
+        <v>46290.6625</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>178.9</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
@@ -1144,90 +1144,90 @@
         <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
@@ -1236,73 +1236,73 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
@@ -1311,21 +1311,21 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -1334,61 +1334,61 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
@@ -1397,44 +1397,44 @@
         <v>3</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
@@ -1449,15 +1449,15 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
@@ -1472,15 +1472,15 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
@@ -1495,15 +1495,15 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
@@ -1518,15 +1518,15 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
@@ -1541,15 +1541,15 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
@@ -1561,18 +1561,18 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
@@ -1587,15 +1587,15 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
@@ -1610,15 +1610,15 @@
         <v>2</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>433</v>
@@ -1633,18 +1633,18 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0</v>
@@ -1656,15 +1656,15 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>441</v>
@@ -1679,15 +1679,15 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>441</v>
@@ -1702,15 +1702,15 @@
         <v>2</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>441</v>
@@ -1725,18 +1725,18 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0</v>
@@ -1745,18 +1745,18 @@
         <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>440</v>
@@ -1771,15 +1771,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>440</v>
@@ -1794,15 +1794,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>440</v>
@@ -2783,18 +2783,18 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>0</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>442</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>442</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3202,10 +3202,10 @@
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3220,15 +3220,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>442</v>
@@ -3243,6 +3243,29 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B96" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3308,7 +3331,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R22</f>
+        <f>資金明細!R23</f>
         <v/>
       </c>
     </row>
@@ -3346,7 +3369,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$22)</f>
+        <f>MAX(資金明細!$R$2:$R$23)</f>
         <v/>
       </c>
     </row>
@@ -3365,7 +3388,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$22)</f>
+        <f>MIN(資金明細!$R$2:$R$23)</f>
         <v/>
       </c>
     </row>
@@ -3385,7 +3408,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$22)</f>
+        <f>MIN(資金明細!$X$2:$X$23)</f>
         <v/>
       </c>
     </row>
@@ -3404,7 +3427,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$22,"進場",資金明細!$N$2:$N$22,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$23,"進場",資金明細!$N$2:$N$23,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3423,7 +3446,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$22,"進場",資金明細!$N$2:$N$22,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$23,"進場",資金明細!$N$2:$N$23,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3434,7 +3457,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$22,"出場",資金明細!$N$2:$N$22,"已下單",資金明細!$K$2:$K$22,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$23,"出場",資金明細!$N$2:$N$23,"已下單",資金明細!$K$2:$K$23,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3445,7 +3468,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$11),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$12),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3454,7 +3477,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$22,"出場",資金明細!$N$2:$N$22,"已下單",資金明細!$K$2:$K$22,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$23,"出場",資金明細!$N$2:$N$23,"已下單",資金明細!$K$2:$K$23,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3470,7 +3493,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$22,"出場",資金明細!$N$2:$N$22,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$23,"出場",資金明細!$N$2:$N$23,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3486,7 +3509,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$22)</f>
+        <f>MAX(資金明細!$U$2:$U$23)</f>
         <v/>
       </c>
     </row>
@@ -3502,7 +3525,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$22)</f>
+        <f>MAX(資金明細!$S$2:$S$23)</f>
         <v/>
       </c>
     </row>
@@ -3513,7 +3536,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V22</f>
+        <f>B5*資金明細!V23</f>
         <v/>
       </c>
     </row>
@@ -3524,7 +3547,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>0</f>
+        <f>IF(資金明細!N23="已下單",資金明細!O23*交易明細!L12,0)</f>
         <v/>
       </c>
     </row>
@@ -3535,7 +3558,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$22)</f>
+        <f>MAX(資金明細!$Y$2:$Y$23)</f>
         <v/>
       </c>
     </row>
@@ -3557,7 +3580,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$22,MATCH(1,資金明細!$Z$2:$Z$22,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$23,MATCH(1,資金明細!$Z$2:$Z$23,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3568,7 +3591,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$22,"進場",資金明細!$N$2:$N$22,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$23,"進場",資金明細!$N$2:$N$23,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3633,7 +3656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5784,9 +5807,103 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>46290.64305555556</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>PHA_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>0.05717</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>0.05545489999999999</v>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>0.0600285</v>
+      </c>
+      <c r="J23" s="17" t="n"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="16">
+        <f>資金模擬!$B$5*V22</f>
+        <v/>
+      </c>
+      <c r="N23" s="2">
+        <f>IF(Z22=1,"已停止",IF(T22&gt;=M23,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O23" s="16">
+        <f>IF(N23="已下單",M23*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="10">
+        <f>R22+Q23</f>
+        <v/>
+      </c>
+      <c r="S23" s="16">
+        <f>S22+IF(N23="已下單",M23,0)</f>
+        <v/>
+      </c>
+      <c r="T23" s="16">
+        <f>R23-S23</f>
+        <v/>
+      </c>
+      <c r="U23" s="2">
+        <f>U22+IF(N23="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V23" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R23,0),MAX(V22,FLOOR(MAX(R23,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W23" s="10">
+        <f>MAX(W22,R23)</f>
+        <v/>
+      </c>
+      <c r="X23" s="4">
+        <f>IF(W23&gt;0,R23/W23-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y23" s="16">
+        <f>IF(R23&gt;0,S23*資金模擬!$B$7/R23,0)</f>
+        <v/>
+      </c>
+      <c r="Z23" s="2">
+        <f>IF(OR(Z22=1,R23&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z22"/>
-  <conditionalFormatting sqref="K2:K22">
+  <autoFilter ref="A1:Z23"/>
+  <conditionalFormatting sqref="K2:K23">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -5794,7 +5911,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N22">
+  <conditionalFormatting sqref="N2:N23">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -5802,7 +5919,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q22">
+  <conditionalFormatting sqref="Q2:Q23">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -5867,7 +5984,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-25 14:49（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-25 15:55（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -6077,7 +6194,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$11),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$12),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -6103,7 +6220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH11"/>
+  <dimension ref="A1:AH12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7224,9 +7341,104 @@
         <v>3</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>PHA_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>46290.64305555556</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0.05717</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>0.05545489999999999</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>0.0600285</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>46290.66319444445</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>0.05704</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K12" s="5">
+        <f>(H12-D12)*24</f>
+        <v/>
+      </c>
+      <c r="L12" s="4">
+        <f>IF(C12="做多",I12/E12-1,1-I12/E12)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
+      <c r="Q12" s="19" t="n"/>
+      <c r="R12" s="19" t="n"/>
+      <c r="S12" s="4" t="n">
+        <v>0.02308903270946305</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>0.02781178940003493</v>
+      </c>
+      <c r="U12" s="16" t="n"/>
+      <c r="V12" s="16" t="n"/>
+      <c r="W12" s="4" t="n"/>
+      <c r="X12" s="4" t="n"/>
+      <c r="Y12" s="4" t="n"/>
+      <c r="Z12" s="4" t="n"/>
+      <c r="AA12" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB12" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC12" s="4">
+        <f>(AB12+2*參數!$B$7)/(AA12+AB12)</f>
+        <v/>
+      </c>
+      <c r="AD12" s="2" t="n">
+        <v>0.06047556637333851</v>
+      </c>
+      <c r="AE12" s="2" t="n">
+        <v>1.017332550709329</v>
+      </c>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>30分1倍</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="n">
+        <v>0.001401296198983992</v>
+      </c>
+      <c r="AH12" s="2" t="n">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AH11"/>
-  <conditionalFormatting sqref="J2:J11">
+  <autoFilter ref="A1:AH12"/>
+  <conditionalFormatting sqref="J2:J12">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -7329,31 +7541,31 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NOM_USDT_PERP</t>
+          <t>PHA_USDT_PERP</t>
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A2,交易明細!$C$2:$C$11,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A2,交易明細!$C$2:$C$12,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A2,交易明細!$C$2:$C$11,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A2,交易明細!$C$2:$C$12,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$11,$A2,交易明細!$J$2:$J$11,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$12,$A2,交易明細!$J$2:$J$12,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A2,交易明細!$J$2:$J$11,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A2,交易明細!$J$2:$J$12,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A2,交易明細!$J$2:$J$11,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A2,交易明細!$J$2:$J$12,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -7361,50 +7573,50 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A2,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A2,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A2,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A2,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A2,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A2,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A2,交易明細!$J$2:$J$11,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A2,交易明細!$J$2:$J$12,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BROCCOLI_USDT_PERP</t>
+          <t>NOM_USDT_PERP</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A3,交易明細!$C$2:$C$11,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A3,交易明細!$C$2:$C$12,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A3,交易明細!$C$2:$C$11,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A3,交易明細!$C$2:$C$12,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$11,$A3,交易明細!$J$2:$J$11,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$12,$A3,交易明細!$J$2:$J$12,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A3,交易明細!$J$2:$J$11,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A3,交易明細!$J$2:$J$12,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A3,交易明細!$J$2:$J$11,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A3,交易明細!$J$2:$J$12,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -7412,50 +7624,50 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A3,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A3,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A3,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A3,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A3,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A3,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A3,交易明細!$J$2:$J$11,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A3,交易明細!$J$2:$J$12,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AGT_USDT_PERP</t>
+          <t>BROCCOLI_USDT_PERP</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A4,交易明細!$C$2:$C$11,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A4,交易明細!$C$2:$C$12,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A4,交易明細!$C$2:$C$11,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A4,交易明細!$C$2:$C$12,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$11,$A4,交易明細!$J$2:$J$11,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$12,$A4,交易明細!$J$2:$J$12,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A4,交易明細!$J$2:$J$11,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A4,交易明細!$J$2:$J$12,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A4,交易明細!$J$2:$J$11,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A4,交易明細!$J$2:$J$12,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -7463,50 +7675,50 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A4,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A4,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A4,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A4,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A4,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A4,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A4,交易明細!$J$2:$J$11,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A4,交易明細!$J$2:$J$12,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PHA_USDT_PERP</t>
+          <t>AGT_USDT_PERP</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A5,交易明細!$C$2:$C$11,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A5,交易明細!$C$2:$C$12,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A5,交易明細!$C$2:$C$11,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A5,交易明細!$C$2:$C$12,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$11,$A5,交易明細!$J$2:$J$11,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$12,$A5,交易明細!$J$2:$J$12,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A5,交易明細!$J$2:$J$11,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A5,交易明細!$J$2:$J$12,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A5,交易明細!$J$2:$J$11,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A5,交易明細!$J$2:$J$12,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -7514,19 +7726,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A5,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A5,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A5,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A5,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A5,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A5,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A5,交易明細!$J$2:$J$11,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A5,交易明細!$J$2:$J$12,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7537,27 +7749,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A6,交易明細!$C$2:$C$11,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A6,交易明細!$C$2:$C$12,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A6,交易明細!$C$2:$C$11,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A6,交易明細!$C$2:$C$12,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$11,$A6,交易明細!$J$2:$J$11,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$12,$A6,交易明細!$J$2:$J$12,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A6,交易明細!$J$2:$J$11,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A6,交易明細!$J$2:$J$12,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A6,交易明細!$J$2:$J$11,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A6,交易明細!$J$2:$J$12,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -7565,19 +7777,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A6,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A6,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A6,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A6,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A6,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A6,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A6,交易明細!$J$2:$J$11,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A6,交易明細!$J$2:$J$12,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7588,27 +7800,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A7,交易明細!$C$2:$C$11,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A7,交易明細!$C$2:$C$12,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A7,交易明細!$C$2:$C$11,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A7,交易明細!$C$2:$C$12,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$11,$A7,交易明細!$J$2:$J$11,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$12,$A7,交易明細!$J$2:$J$12,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A7,交易明細!$J$2:$J$11,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A7,交易明細!$J$2:$J$12,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A7,交易明細!$J$2:$J$11,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A7,交易明細!$J$2:$J$12,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -7616,19 +7828,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A7,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A7,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A7,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A7,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A7,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A7,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A7,交易明細!$J$2:$J$11,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A7,交易明細!$J$2:$J$12,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7639,27 +7851,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A8,交易明細!$C$2:$C$11,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A8,交易明細!$C$2:$C$12,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A8,交易明細!$C$2:$C$11,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A8,交易明細!$C$2:$C$12,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$11,$A8,交易明細!$J$2:$J$11,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$12,$A8,交易明細!$J$2:$J$12,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A8,交易明細!$J$2:$J$11,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A8,交易明細!$J$2:$J$12,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A8,交易明細!$J$2:$J$11,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A8,交易明細!$J$2:$J$12,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -7667,19 +7879,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A8,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A8,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A8,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A8,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A8,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A8,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A8,交易明細!$J$2:$J$11,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A8,交易明細!$J$2:$J$12,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7690,27 +7902,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A9,交易明細!$C$2:$C$11,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A9,交易明細!$C$2:$C$12,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A9,交易明細!$C$2:$C$11,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A9,交易明細!$C$2:$C$12,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$11,$A9,交易明細!$J$2:$J$11,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$12,$A9,交易明細!$J$2:$J$12,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A9,交易明細!$J$2:$J$11,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A9,交易明細!$J$2:$J$12,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A9,交易明細!$J$2:$J$11,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A9,交易明細!$J$2:$J$12,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -7718,19 +7930,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A9,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A9,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A9,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A9,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A9,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A9,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A9,交易明細!$J$2:$J$11,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A9,交易明細!$J$2:$J$12,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7741,27 +7953,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A10,交易明細!$C$2:$C$11,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A10,交易明細!$C$2:$C$12,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A10,交易明細!$C$2:$C$11,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A10,交易明細!$C$2:$C$12,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$11,$A10,交易明細!$J$2:$J$11,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$12,$A10,交易明細!$J$2:$J$12,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A10,交易明細!$J$2:$J$11,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A10,交易明細!$J$2:$J$12,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A10,交易明細!$J$2:$J$11,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A10,交易明細!$J$2:$J$12,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -7769,19 +7981,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A10,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A10,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A10,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A10,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A10,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A10,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A10,交易明細!$J$2:$J$11,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A10,交易明細!$J$2:$J$12,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7792,27 +8004,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A11,交易明細!$C$2:$C$11,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A11,交易明細!$C$2:$C$12,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A11,交易明細!$C$2:$C$11,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A11,交易明細!$C$2:$C$12,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$11,$A11,交易明細!$J$2:$J$11,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$12,$A11,交易明細!$J$2:$J$12,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A11,交易明細!$J$2:$J$11,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A11,交易明細!$J$2:$J$12,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A11,交易明細!$J$2:$J$11,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A11,交易明細!$J$2:$J$12,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -7820,19 +8032,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A11,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A11,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$11,交易明細!$B$2:$B$11,$A11,交易明細!$J$2:$J$11,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A11,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$11,交易明細!$B$2:$B$11,$A11,交易明細!$J$2:$J$11,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A11,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$11,$A11,交易明細!$J$2:$J$11,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$12,$A11,交易明細!$J$2:$J$12,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -12972,7 +13184,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C283" s="2" t="inlineStr"/>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D283" s="2" t="n"/>
       <c r="E283" s="17" t="n"/>
       <c r="F283" s="17" t="n"/>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,9 +17,9 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$23</f>
+              <f>'資金明細'!$R$2:$R$25</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 15:55（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 17:01（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -796,19 +796,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$12,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$13,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$12,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$13,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$12,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$13,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$12,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$13,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -816,35 +816,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$12,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$13,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$J$2:$J$12,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$J$2:$J$13,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$J$2:$J$12,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$J$2:$J$13,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$J$2:$J$12,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$J$2:$J$13,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$12,"&lt;&gt;未平倉",交易明細!$L$2:$L$12,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$13,"&lt;&gt;未平倉",交易明細!$L$2:$L$13,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$12,"做多",交易明細!$B$2:$B$12,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$13,"做多",交易明細!$B$2:$B$13,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -863,19 +863,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -883,35 +883,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$12,交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$13,交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$12,"做多",交易明細!$J$2:$J$12,"&lt;&gt;未平倉",交易明細!$L$2:$L$12,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"&lt;&gt;未平倉",交易明細!$L$2:$L$13,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$12,"做空",交易明細!$B$2:$B$12,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$13,"做空",交易明細!$B$2:$B$13,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -930,19 +930,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -950,35 +950,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$12,交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$13,交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$12,"做空",交易明細!$J$2:$J$12,"&lt;&gt;未平倉",交易明細!$L$2:$L$12,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"&lt;&gt;未平倉",交易明細!$L$2:$L$13,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46290.66382769676</v>
+        <v>46290.709303125</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46290.6625</v>
+        <v>46290.70833333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
@@ -1098,67 +1098,67 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>185.1</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46290.61757802084</v>
+        <v>46290.66382769676</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46290.61666666667</v>
+        <v>46290.6625</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>178.9</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
@@ -1167,90 +1167,90 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
@@ -1259,73 +1259,73 @@
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -1334,21 +1334,21 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
@@ -1357,61 +1357,61 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
@@ -1420,44 +1420,44 @@
         <v>3</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
@@ -1472,15 +1472,15 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
@@ -1495,15 +1495,15 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
@@ -1518,15 +1518,15 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
@@ -1541,15 +1541,15 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
@@ -1564,15 +1564,15 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
@@ -1584,18 +1584,18 @@
         <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
@@ -1610,15 +1610,15 @@
         <v>2</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>433</v>
@@ -1633,15 +1633,15 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>433</v>
@@ -1656,18 +1656,18 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0</v>
@@ -1679,15 +1679,15 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>441</v>
@@ -1702,15 +1702,15 @@
         <v>2</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>441</v>
@@ -1725,15 +1725,15 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>441</v>
@@ -1748,18 +1748,18 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0</v>
@@ -1768,18 +1768,18 @@
         <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>440</v>
@@ -1794,15 +1794,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>440</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>440</v>
@@ -2806,18 +2806,18 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>0</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>442</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,15 +3197,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>442</v>
@@ -3243,15 +3243,15 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>442</v>
@@ -3266,6 +3266,29 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B97" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3331,7 +3354,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R23</f>
+        <f>資金明細!R25</f>
         <v/>
       </c>
     </row>
@@ -3369,7 +3392,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$23)</f>
+        <f>MAX(資金明細!$R$2:$R$25)</f>
         <v/>
       </c>
     </row>
@@ -3388,7 +3411,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$23)</f>
+        <f>MIN(資金明細!$R$2:$R$25)</f>
         <v/>
       </c>
     </row>
@@ -3408,7 +3431,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$23)</f>
+        <f>MIN(資金明細!$X$2:$X$25)</f>
         <v/>
       </c>
     </row>
@@ -3427,7 +3450,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$23,"進場",資金明細!$N$2:$N$23,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$25,"進場",資金明細!$N$2:$N$25,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3446,7 +3469,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$23,"進場",資金明細!$N$2:$N$23,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$25,"進場",資金明細!$N$2:$N$25,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3457,7 +3480,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$23,"出場",資金明細!$N$2:$N$23,"已下單",資金明細!$K$2:$K$23,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$25,"出場",資金明細!$N$2:$N$25,"已下單",資金明細!$K$2:$K$25,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3468,7 +3491,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$12),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$13),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3477,7 +3500,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$23,"出場",資金明細!$N$2:$N$23,"已下單",資金明細!$K$2:$K$23,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$25,"出場",資金明細!$N$2:$N$25,"已下單",資金明細!$K$2:$K$25,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3493,7 +3516,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$23,"出場",資金明細!$N$2:$N$23,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$25,"出場",資金明細!$N$2:$N$25,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3509,7 +3532,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$23)</f>
+        <f>MAX(資金明細!$U$2:$U$25)</f>
         <v/>
       </c>
     </row>
@@ -3525,7 +3548,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$23)</f>
+        <f>MAX(資金明細!$S$2:$S$25)</f>
         <v/>
       </c>
     </row>
@@ -3536,7 +3559,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V23</f>
+        <f>B5*資金明細!V25</f>
         <v/>
       </c>
     </row>
@@ -3547,7 +3570,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N23="已下單",資金明細!O23*交易明細!L12,0)</f>
+        <f>IF(資金明細!N25="已下單",資金明細!O25*交易明細!L13,0)</f>
         <v/>
       </c>
     </row>
@@ -3558,7 +3581,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$23)</f>
+        <f>MAX(資金明細!$Y$2:$Y$25)</f>
         <v/>
       </c>
     </row>
@@ -3580,7 +3603,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$23,MATCH(1,資金明細!$Z$2:$Z$23,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$25,MATCH(1,資金明細!$Z$2:$Z$25,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3591,7 +3614,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$23,"進場",資金明細!$N$2:$N$23,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$25,"進場",資金明細!$N$2:$N$25,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3656,7 +3679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5842,11 +5865,7 @@
         <v>0.0600285</v>
       </c>
       <c r="J23" s="17" t="n"/>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K23" s="2" t="n"/>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="16">
         <f>資金模擬!$B$5*V22</f>
@@ -5901,9 +5920,206 @@
         <v/>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>46290.66527777778</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>PHA_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>0.05717</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>0.05545489999999999</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>0.0600285</v>
+      </c>
+      <c r="J24" s="17" t="n">
+        <v>0.05545489999999999</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L24" s="5">
+        <f>交易明細!K12</f>
+        <v/>
+      </c>
+      <c r="M24" s="16">
+        <f>M23</f>
+        <v/>
+      </c>
+      <c r="N24" s="2">
+        <f>N23</f>
+        <v/>
+      </c>
+      <c r="O24" s="16">
+        <f>O23</f>
+        <v/>
+      </c>
+      <c r="P24" s="4">
+        <f>交易明細!L12</f>
+        <v/>
+      </c>
+      <c r="Q24" s="10">
+        <f>IF(N24="已下單",O24*P24,0)</f>
+        <v/>
+      </c>
+      <c r="R24" s="10">
+        <f>R23+Q24</f>
+        <v/>
+      </c>
+      <c r="S24" s="16">
+        <f>S23-IF(N24="已下單",M24,0)</f>
+        <v/>
+      </c>
+      <c r="T24" s="16">
+        <f>R24-S24</f>
+        <v/>
+      </c>
+      <c r="U24" s="2">
+        <f>U23-IF(N24="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V24" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R24,0),MAX(V23,FLOOR(MAX(R24,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W24" s="10">
+        <f>MAX(W23,R24)</f>
+        <v/>
+      </c>
+      <c r="X24" s="4">
+        <f>IF(W24&gt;0,R24/W24-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y24" s="16">
+        <f>IF(R24&gt;0,S24*資金模擬!$B$7/R24,0)</f>
+        <v/>
+      </c>
+      <c r="Z24" s="2">
+        <f>IF(OR(Z23=1,R24&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>46290.67708333334</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>CASHCAT_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="n">
+        <v>0.1726</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>0.167422</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>0.18123</v>
+      </c>
+      <c r="J25" s="17" t="n"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="16">
+        <f>資金模擬!$B$5*V24</f>
+        <v/>
+      </c>
+      <c r="N25" s="2">
+        <f>IF(Z24=1,"已停止",IF(T24&gt;=M25,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O25" s="16">
+        <f>IF(N25="已下單",M25*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P25" s="4" t="n"/>
+      <c r="Q25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="10">
+        <f>R24+Q25</f>
+        <v/>
+      </c>
+      <c r="S25" s="16">
+        <f>S24+IF(N25="已下單",M25,0)</f>
+        <v/>
+      </c>
+      <c r="T25" s="16">
+        <f>R25-S25</f>
+        <v/>
+      </c>
+      <c r="U25" s="2">
+        <f>U24+IF(N25="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V25" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R25,0),MAX(V24,FLOOR(MAX(R25,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W25" s="10">
+        <f>MAX(W24,R25)</f>
+        <v/>
+      </c>
+      <c r="X25" s="4">
+        <f>IF(W25&gt;0,R25/W25-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y25" s="16">
+        <f>IF(R25&gt;0,S25*資金模擬!$B$7/R25,0)</f>
+        <v/>
+      </c>
+      <c r="Z25" s="2">
+        <f>IF(OR(Z24=1,R25&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z23"/>
-  <conditionalFormatting sqref="K2:K23">
+  <autoFilter ref="A1:Z25"/>
+  <conditionalFormatting sqref="K2:K25">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -5911,7 +6127,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N23">
+  <conditionalFormatting sqref="N2:N25">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -5919,7 +6135,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q23">
+  <conditionalFormatting sqref="Q2:Q25">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -5984,7 +6200,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-25 15:55（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-25 17:01（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -6194,7 +6410,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$12),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$13),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -6220,7 +6436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH12"/>
+  <dimension ref="A1:AH13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7368,14 +7584,14 @@
         <v>0.0600285</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>46290.66319444445</v>
+        <v>46290.66527777778</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>0.05704</v>
+        <v>0.05545489999999999</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止盈</t>
         </is>
       </c>
       <c r="K12" s="5">
@@ -7386,18 +7602,14 @@
         <f>IF(C12="做多",I12/E12-1,1-I12/E12)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="19" t="n"/>
       <c r="R12" s="19" t="n"/>
       <c r="S12" s="4" t="n">
-        <v>0.02308903270946305</v>
+        <v>0.03</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>0.02781178940003493</v>
@@ -7436,9 +7648,104 @@
         <v>26</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>CASHCAT_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>46290.67708333334</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0.1726</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>0.167422</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>0.18123</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>46290.70902777778</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>0.1726</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K13" s="5">
+        <f>(H13-D13)*24</f>
+        <v/>
+      </c>
+      <c r="L13" s="4">
+        <f>IF(C13="做多",I13/E13-1,1-I13/E13)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
+      <c r="Q13" s="19" t="n"/>
+      <c r="R13" s="19" t="n"/>
+      <c r="S13" s="4" t="n">
+        <v>0.008690614136732333</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>0.01969872537659323</v>
+      </c>
+      <c r="U13" s="16" t="n"/>
+      <c r="V13" s="16" t="n"/>
+      <c r="W13" s="4" t="n"/>
+      <c r="X13" s="4" t="n"/>
+      <c r="Y13" s="4" t="n"/>
+      <c r="Z13" s="4" t="n"/>
+      <c r="AA13" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB13" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC13" s="4">
+        <f>(AB13+2*參數!$B$7)/(AA13+AB13)</f>
+        <v/>
+      </c>
+      <c r="AD13" s="2" t="n">
+        <v>0.06574827802128991</v>
+      </c>
+      <c r="AE13" s="2" t="n">
+        <v>0.5128737627342798</v>
+      </c>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>15分0.5倍</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="n">
+        <v>0.009356725146198785</v>
+      </c>
+      <c r="AH13" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AH12"/>
-  <conditionalFormatting sqref="J2:J12">
+  <autoFilter ref="A1:AH13"/>
+  <conditionalFormatting sqref="J2:J13">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -7459,7 +7766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7545,27 +7852,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A2,交易明細!$C$2:$C$12,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A2,交易明細!$C$2:$C$13,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A2,交易明細!$C$2:$C$12,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A2,交易明細!$C$2:$C$13,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$12,$A2,交易明細!$J$2:$J$12,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$13,$A2,交易明細!$J$2:$J$13,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A2,交易明細!$J$2:$J$12,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A2,交易明細!$J$2:$J$13,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A2,交易明細!$J$2:$J$12,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A2,交易明細!$J$2:$J$13,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -7573,19 +7880,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A2,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A2,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A2,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A2,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A2,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A2,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A2,交易明細!$J$2:$J$12,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A2,交易明細!$J$2:$J$13,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7596,27 +7903,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A3,交易明細!$C$2:$C$12,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A3,交易明細!$C$2:$C$13,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A3,交易明細!$C$2:$C$12,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A3,交易明細!$C$2:$C$13,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$12,$A3,交易明細!$J$2:$J$12,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$13,$A3,交易明細!$J$2:$J$13,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A3,交易明細!$J$2:$J$12,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A3,交易明細!$J$2:$J$13,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A3,交易明細!$J$2:$J$12,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A3,交易明細!$J$2:$J$13,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -7624,19 +7931,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A3,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A3,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A3,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A3,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A3,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A3,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A3,交易明細!$J$2:$J$12,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A3,交易明細!$J$2:$J$13,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7647,27 +7954,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A4,交易明細!$C$2:$C$12,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A4,交易明細!$C$2:$C$13,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A4,交易明細!$C$2:$C$12,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A4,交易明細!$C$2:$C$13,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$12,$A4,交易明細!$J$2:$J$12,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$13,$A4,交易明細!$J$2:$J$13,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A4,交易明細!$J$2:$J$12,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A4,交易明細!$J$2:$J$13,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A4,交易明細!$J$2:$J$12,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A4,交易明細!$J$2:$J$13,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -7675,19 +7982,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A4,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A4,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A4,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A4,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A4,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A4,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A4,交易明細!$J$2:$J$12,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A4,交易明細!$J$2:$J$13,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7698,27 +8005,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A5,交易明細!$C$2:$C$12,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A5,交易明細!$C$2:$C$13,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A5,交易明細!$C$2:$C$12,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A5,交易明細!$C$2:$C$13,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$12,$A5,交易明細!$J$2:$J$12,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$13,$A5,交易明細!$J$2:$J$13,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A5,交易明細!$J$2:$J$12,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A5,交易明細!$J$2:$J$13,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A5,交易明細!$J$2:$J$12,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A5,交易明細!$J$2:$J$13,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -7726,19 +8033,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A5,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A5,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A5,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A5,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A5,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A5,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A5,交易明細!$J$2:$J$12,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A5,交易明細!$J$2:$J$13,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7749,27 +8056,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A6,交易明細!$C$2:$C$12,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A6,交易明細!$C$2:$C$13,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A6,交易明細!$C$2:$C$12,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A6,交易明細!$C$2:$C$13,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$12,$A6,交易明細!$J$2:$J$12,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$13,$A6,交易明細!$J$2:$J$13,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A6,交易明細!$J$2:$J$12,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A6,交易明細!$J$2:$J$13,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A6,交易明細!$J$2:$J$12,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A6,交易明細!$J$2:$J$13,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -7777,19 +8084,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A6,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A6,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A6,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A6,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A6,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A6,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A6,交易明細!$J$2:$J$12,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A6,交易明細!$J$2:$J$13,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7800,27 +8107,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A7,交易明細!$C$2:$C$12,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A7,交易明細!$C$2:$C$13,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A7,交易明細!$C$2:$C$12,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A7,交易明細!$C$2:$C$13,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$12,$A7,交易明細!$J$2:$J$12,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$13,$A7,交易明細!$J$2:$J$13,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A7,交易明細!$J$2:$J$12,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A7,交易明細!$J$2:$J$13,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A7,交易明細!$J$2:$J$12,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A7,交易明細!$J$2:$J$13,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -7828,19 +8135,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A7,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A7,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A7,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A7,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A7,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A7,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A7,交易明細!$J$2:$J$12,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A7,交易明細!$J$2:$J$13,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7851,27 +8158,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A8,交易明細!$C$2:$C$12,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A8,交易明細!$C$2:$C$13,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A8,交易明細!$C$2:$C$12,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A8,交易明細!$C$2:$C$13,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$12,$A8,交易明細!$J$2:$J$12,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$13,$A8,交易明細!$J$2:$J$13,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A8,交易明細!$J$2:$J$12,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A8,交易明細!$J$2:$J$13,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A8,交易明細!$J$2:$J$12,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A8,交易明細!$J$2:$J$13,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -7879,19 +8186,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A8,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A8,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A8,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A8,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A8,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A8,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A8,交易明細!$J$2:$J$12,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A8,交易明細!$J$2:$J$13,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7902,27 +8209,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A9,交易明細!$C$2:$C$12,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A9,交易明細!$C$2:$C$13,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A9,交易明細!$C$2:$C$12,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A9,交易明細!$C$2:$C$13,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$12,$A9,交易明細!$J$2:$J$12,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$13,$A9,交易明細!$J$2:$J$13,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A9,交易明細!$J$2:$J$12,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A9,交易明細!$J$2:$J$13,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A9,交易明細!$J$2:$J$12,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A9,交易明細!$J$2:$J$13,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -7930,19 +8237,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A9,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A9,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A9,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A9,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A9,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A9,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A9,交易明細!$J$2:$J$12,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A9,交易明細!$J$2:$J$13,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -7953,27 +8260,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A10,交易明細!$C$2:$C$12,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A10,交易明細!$C$2:$C$13,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A10,交易明細!$C$2:$C$12,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A10,交易明細!$C$2:$C$13,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$12,$A10,交易明細!$J$2:$J$12,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$13,$A10,交易明細!$J$2:$J$13,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A10,交易明細!$J$2:$J$12,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A10,交易明細!$J$2:$J$13,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A10,交易明細!$J$2:$J$12,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A10,交易明細!$J$2:$J$13,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -7981,19 +8288,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A10,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A10,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A10,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A10,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A10,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A10,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A10,交易明細!$J$2:$J$12,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A10,交易明細!$J$2:$J$13,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8004,27 +8311,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A11,交易明細!$C$2:$C$12,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A11,交易明細!$C$2:$C$13,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A11,交易明細!$C$2:$C$12,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A11,交易明細!$C$2:$C$13,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$12,$A11,交易明細!$J$2:$J$12,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$13,$A11,交易明細!$J$2:$J$13,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A11,交易明細!$J$2:$J$12,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A11,交易明細!$J$2:$J$13,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A11,交易明細!$J$2:$J$12,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A11,交易明細!$J$2:$J$13,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -8032,24 +8339,75 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A11,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A11,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$12,交易明細!$B$2:$B$12,$A11,交易明細!$J$2:$J$12,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A11,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$12,交易明細!$B$2:$B$12,$A11,交易明細!$J$2:$J$12,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A11,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$12,$A11,交易明細!$J$2:$J$12,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A11,交易明細!$J$2:$J$13,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CASHCAT_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B12" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A12,交易明細!$C$2:$C$13,"做多")</f>
+        <v/>
+      </c>
+      <c r="D12" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A12,交易明細!$C$2:$C$13,"做空")</f>
+        <v/>
+      </c>
+      <c r="E12" s="2">
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$13,$A12,交易明細!$J$2:$J$13,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F12" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A12,交易明細!$J$2:$J$13,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G12" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A12,交易明細!$J$2:$J$13,"止損")</f>
+        <v/>
+      </c>
+      <c r="H12" s="4">
+        <f>IFERROR(F12/E12,0)</f>
+        <v/>
+      </c>
+      <c r="I12" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A12,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J12" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A12,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K12" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A12,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L12" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$13,$A12,交易明細!$J$2:$J$13,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:L12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9764,7 +10122,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" s="17" t="n"/>
       <c r="F93" s="17" t="n"/>
@@ -13184,11 +13546,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C283" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C283" s="2" t="inlineStr"/>
       <c r="D283" s="2" t="n"/>
       <c r="E283" s="17" t="n"/>
       <c r="F283" s="17" t="n"/>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,7 +17,7 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$25</f>
+              <f>'資金明細'!$R$2:$R$26</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 17:01（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 18:26（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,16 +1086,16 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46290.709303125</v>
+        <v>46290.76820827546</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46290.70833333334</v>
+        <v>46290.76736111111</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -1104,15 +1104,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>187.6</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46290.66382769676</v>
+        <v>46290.709303125</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46290.6625</v>
+        <v>46290.70833333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
@@ -1121,67 +1121,67 @@
         <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>185.1</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46290.61757802084</v>
+        <v>46290.66382769676</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46290.61666666667</v>
+        <v>46290.6625</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>178.9</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
@@ -1190,90 +1190,90 @@
         <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
@@ -1282,73 +1282,73 @@
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
@@ -1357,21 +1357,21 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
@@ -1380,61 +1380,61 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
@@ -1443,44 +1443,44 @@
         <v>3</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
@@ -1495,15 +1495,15 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
@@ -1518,15 +1518,15 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
@@ -1541,15 +1541,15 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
@@ -1564,15 +1564,15 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
@@ -1587,15 +1587,15 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
@@ -1607,18 +1607,18 @@
         <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>433</v>
@@ -1633,15 +1633,15 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>433</v>
@@ -1656,15 +1656,15 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>433</v>
@@ -1679,18 +1679,18 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0</v>
@@ -1702,15 +1702,15 @@
         <v>2</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>441</v>
@@ -1725,15 +1725,15 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>441</v>
@@ -1748,15 +1748,15 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>441</v>
@@ -1771,18 +1771,18 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0</v>
@@ -1791,18 +1791,18 @@
         <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>440</v>
@@ -1817,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>440</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>440</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>440</v>
@@ -2829,18 +2829,18 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>0</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>442</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,15 +3197,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3220,15 +3220,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>442</v>
@@ -3248,10 +3248,10 @@
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>442</v>
@@ -3266,15 +3266,15 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B97" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C97" s="2" t="n">
         <v>442</v>
@@ -3289,6 +3289,29 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B98" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3354,7 +3377,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R25</f>
+        <f>資金明細!R26</f>
         <v/>
       </c>
     </row>
@@ -3392,7 +3415,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$25)</f>
+        <f>MAX(資金明細!$R$2:$R$26)</f>
         <v/>
       </c>
     </row>
@@ -3411,7 +3434,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$25)</f>
+        <f>MIN(資金明細!$R$2:$R$26)</f>
         <v/>
       </c>
     </row>
@@ -3431,7 +3454,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$25)</f>
+        <f>MIN(資金明細!$X$2:$X$26)</f>
         <v/>
       </c>
     </row>
@@ -3450,7 +3473,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$25,"進場",資金明細!$N$2:$N$25,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$26,"進場",資金明細!$N$2:$N$26,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3469,7 +3492,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$25,"進場",資金明細!$N$2:$N$25,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$26,"進場",資金明細!$N$2:$N$26,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3480,7 +3503,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$25,"出場",資金明細!$N$2:$N$25,"已下單",資金明細!$K$2:$K$25,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$26,"出場",資金明細!$N$2:$N$26,"已下單",資金明細!$K$2:$K$26,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3500,7 +3523,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$25,"出場",資金明細!$N$2:$N$25,"已下單",資金明細!$K$2:$K$25,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$26,"出場",資金明細!$N$2:$N$26,"已下單",資金明細!$K$2:$K$26,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3516,7 +3539,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$25,"出場",資金明細!$N$2:$N$25,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$26,"出場",資金明細!$N$2:$N$26,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3532,7 +3555,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$25)</f>
+        <f>MAX(資金明細!$U$2:$U$26)</f>
         <v/>
       </c>
     </row>
@@ -3548,7 +3571,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$25)</f>
+        <f>MAX(資金明細!$S$2:$S$26)</f>
         <v/>
       </c>
     </row>
@@ -3559,7 +3582,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V25</f>
+        <f>B5*資金明細!V26</f>
         <v/>
       </c>
     </row>
@@ -3570,7 +3593,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>IF(資金明細!N25="已下單",資金明細!O25*交易明細!L13,0)</f>
+        <f>0</f>
         <v/>
       </c>
     </row>
@@ -3581,7 +3604,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$25)</f>
+        <f>MAX(資金明細!$Y$2:$Y$26)</f>
         <v/>
       </c>
     </row>
@@ -3603,7 +3626,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$25,MATCH(1,資金明細!$Z$2:$Z$25,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$26,MATCH(1,資金明細!$Z$2:$Z$26,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3614,7 +3637,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$25,"進場",資金明細!$N$2:$N$25,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$26,"進場",資金明細!$N$2:$N$26,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3679,7 +3702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:Z26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6058,11 +6081,7 @@
         <v>0.18123</v>
       </c>
       <c r="J25" s="17" t="n"/>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>未平倉</t>
-        </is>
-      </c>
+      <c r="K25" s="2" t="n"/>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="16">
         <f>資金模擬!$B$5*V24</f>
@@ -6117,9 +6136,112 @@
         <v/>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>46290.76041666666</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>CASHCAT_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>0.1726</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>0.167422</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>0.18123</v>
+      </c>
+      <c r="J26" s="17" t="n">
+        <v>0.18123</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L26" s="5">
+        <f>交易明細!K13</f>
+        <v/>
+      </c>
+      <c r="M26" s="16">
+        <f>M25</f>
+        <v/>
+      </c>
+      <c r="N26" s="2">
+        <f>N25</f>
+        <v/>
+      </c>
+      <c r="O26" s="16">
+        <f>O25</f>
+        <v/>
+      </c>
+      <c r="P26" s="4">
+        <f>交易明細!L13</f>
+        <v/>
+      </c>
+      <c r="Q26" s="10">
+        <f>IF(N26="已下單",O26*P26,0)</f>
+        <v/>
+      </c>
+      <c r="R26" s="10">
+        <f>R25+Q26</f>
+        <v/>
+      </c>
+      <c r="S26" s="16">
+        <f>S25-IF(N26="已下單",M26,0)</f>
+        <v/>
+      </c>
+      <c r="T26" s="16">
+        <f>R26-S26</f>
+        <v/>
+      </c>
+      <c r="U26" s="2">
+        <f>U25-IF(N26="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V26" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R26,0),MAX(V25,FLOOR(MAX(R26,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W26" s="10">
+        <f>MAX(W25,R26)</f>
+        <v/>
+      </c>
+      <c r="X26" s="4">
+        <f>IF(W26&gt;0,R26/W26-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y26" s="16">
+        <f>IF(R26&gt;0,S26*資金模擬!$B$7/R26,0)</f>
+        <v/>
+      </c>
+      <c r="Z26" s="2">
+        <f>IF(OR(Z25=1,R26&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z25"/>
-  <conditionalFormatting sqref="K2:K25">
+  <autoFilter ref="A1:Z26"/>
+  <conditionalFormatting sqref="K2:K26">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -6127,7 +6249,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N25">
+  <conditionalFormatting sqref="N2:N26">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -6135,7 +6257,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q25">
+  <conditionalFormatting sqref="Q2:Q26">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -6200,7 +6322,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-25 17:01（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-25 18:26（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -7675,14 +7797,14 @@
         <v>0.18123</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>46290.70902777778</v>
+        <v>46290.76041666666</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.1726</v>
+        <v>0.18123</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>未平倉</t>
+          <t>止損</t>
         </is>
       </c>
       <c r="K13" s="5">
@@ -7693,11 +7815,7 @@
         <f>IF(C13="做多",I13/E13-1,1-I13/E13)-2*參數!$B$7</f>
         <v/>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>持倉中（以最新收盤估值）</t>
-        </is>
-      </c>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="4" t="n"/>
       <c r="O13" s="4" t="n"/>
       <c r="P13" s="4" t="n"/>
@@ -7707,7 +7825,7 @@
         <v>0.008690614136732333</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.01969872537659323</v>
+        <v>0.05</v>
       </c>
       <c r="U13" s="16" t="n"/>
       <c r="V13" s="16" t="n"/>
@@ -10122,11 +10240,7 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>持倉中</t>
-        </is>
-      </c>
+      <c r="C93" s="2" t="inlineStr"/>
       <c r="D93" s="2" t="n"/>
       <c r="E93" s="17" t="n"/>
       <c r="F93" s="17" t="n"/>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 18:26（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 19:42（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46290.76820827546</v>
+        <v>46290.82088560185</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46290.76736111111</v>
+        <v>46290.82013888889</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
@@ -1098,27 +1098,27 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>187</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46290.709303125</v>
+        <v>46290.76820827546</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46290.70833333334</v>
+        <v>46290.76736111111</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
@@ -1127,15 +1127,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>187.6</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46290.66382769676</v>
+        <v>46290.709303125</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46290.6625</v>
+        <v>46290.70833333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
@@ -1144,67 +1144,67 @@
         <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>185.1</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46290.61757802084</v>
+        <v>46290.66382769676</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46290.61666666667</v>
+        <v>46290.6625</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>178.9</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
@@ -1213,90 +1213,90 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
@@ -1305,73 +1305,73 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
@@ -1380,21 +1380,21 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -1403,61 +1403,61 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
@@ -1466,44 +1466,44 @@
         <v>3</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
@@ -1518,15 +1518,15 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
@@ -1541,15 +1541,15 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
@@ -1564,15 +1564,15 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
@@ -1587,15 +1587,15 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
@@ -1610,15 +1610,15 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>433</v>
@@ -1630,18 +1630,18 @@
         <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>433</v>
@@ -1656,15 +1656,15 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>433</v>
@@ -1679,15 +1679,15 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>433</v>
@@ -1702,18 +1702,18 @@
         <v>2</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0</v>
@@ -1725,15 +1725,15 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>441</v>
@@ -1748,15 +1748,15 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>441</v>
@@ -1771,15 +1771,15 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>441</v>
@@ -1794,18 +1794,18 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>0</v>
@@ -1814,18 +1814,18 @@
         <v>0</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>440</v>
@@ -1840,15 +1840,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>440</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>440</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>440</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>440</v>
@@ -2852,18 +2852,18 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>0</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>442</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,15 +3197,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3220,15 +3220,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>442</v>
@@ -3243,15 +3243,15 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>442</v>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B97" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C97" s="2" t="n">
         <v>442</v>
@@ -3289,15 +3289,15 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B98" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C98" s="2" t="n">
         <v>442</v>
@@ -3312,6 +3312,29 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B99" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -6322,7 +6345,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-25 18:26（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-25 19:42（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,9 +17,9 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$26</f>
+              <f>'資金明細'!$R$2:$R$28</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 19:42（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 21:54（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -796,19 +796,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$13,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$14,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$13,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$14,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$13,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$14,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$13,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$14,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -816,35 +816,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$13,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$14,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$J$2:$J$13,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$J$2:$J$14,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$J$2:$J$13,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$J$2:$J$14,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$J$2:$J$13,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$J$2:$J$14,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$13,"&lt;&gt;未平倉",交易明細!$L$2:$L$13,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$14,"&lt;&gt;未平倉",交易明細!$L$2:$L$14,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$13,"做多",交易明細!$B$2:$B$13,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$14,"做多",交易明細!$B$2:$B$14,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -863,19 +863,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -883,35 +883,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$13,交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$14,交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$13,"做多",交易明細!$J$2:$J$13,"&lt;&gt;未平倉",交易明細!$L$2:$L$13,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"&lt;&gt;未平倉",交易明細!$L$2:$L$14,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$13,"做空",交易明細!$B$2:$B$13,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$14,"做空",交易明細!$B$2:$B$14,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -930,19 +930,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -950,35 +950,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$13,交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$14,交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$13,"做空",交易明細!$J$2:$J$13,"&lt;&gt;未平倉",交易明細!$L$2:$L$13,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"&lt;&gt;未平倉",交易明細!$L$2:$L$14,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,33 +1086,33 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46290.82088560185</v>
+        <v>46290.91267655093</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46290.82013888889</v>
+        <v>46290.91180555556</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>174.9</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46290.76820827546</v>
+        <v>46290.82088560185</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46290.76736111111</v>
+        <v>46290.82013888889</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
@@ -1121,27 +1121,27 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>187</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46290.709303125</v>
+        <v>46290.76820827546</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46290.70833333334</v>
+        <v>46290.76736111111</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
@@ -1150,15 +1150,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>187.6</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46290.66382769676</v>
+        <v>46290.709303125</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46290.6625</v>
+        <v>46290.70833333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
@@ -1167,67 +1167,67 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>185.1</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46290.61757802084</v>
+        <v>46290.66382769676</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46290.61666666667</v>
+        <v>46290.6625</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>178.9</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
@@ -1236,90 +1236,90 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
@@ -1328,73 +1328,73 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -1403,21 +1403,21 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
@@ -1426,61 +1426,61 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
@@ -1489,44 +1489,44 @@
         <v>3</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
@@ -1541,15 +1541,15 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
@@ -1564,15 +1564,15 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
@@ -1587,15 +1587,15 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
@@ -1610,15 +1610,15 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>433</v>
@@ -1633,15 +1633,15 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>433</v>
@@ -1653,18 +1653,18 @@
         <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>433</v>
@@ -1679,15 +1679,15 @@
         <v>2</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>433</v>
@@ -1702,15 +1702,15 @@
         <v>2</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>433</v>
@@ -1725,18 +1725,18 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0</v>
@@ -1748,15 +1748,15 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>441</v>
@@ -1771,15 +1771,15 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>441</v>
@@ -1794,15 +1794,15 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>441</v>
@@ -1817,18 +1817,18 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>0</v>
@@ -1837,18 +1837,18 @@
         <v>0</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>440</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>440</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>440</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>440</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>440</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>440</v>
@@ -2875,18 +2875,18 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>0</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>442</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,15 +3197,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3220,15 +3220,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>442</v>
@@ -3243,15 +3243,15 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>442</v>
@@ -3266,15 +3266,15 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B97" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C97" s="2" t="n">
         <v>442</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B98" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C98" s="2" t="n">
         <v>442</v>
@@ -3312,15 +3312,15 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B99" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C99" s="2" t="n">
         <v>442</v>
@@ -3335,6 +3335,29 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B100" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3400,7 +3423,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R26</f>
+        <f>資金明細!R28</f>
         <v/>
       </c>
     </row>
@@ -3438,7 +3461,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$26)</f>
+        <f>MAX(資金明細!$R$2:$R$28)</f>
         <v/>
       </c>
     </row>
@@ -3457,7 +3480,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$26)</f>
+        <f>MIN(資金明細!$R$2:$R$28)</f>
         <v/>
       </c>
     </row>
@@ -3477,7 +3500,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$26)</f>
+        <f>MIN(資金明細!$X$2:$X$28)</f>
         <v/>
       </c>
     </row>
@@ -3496,7 +3519,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$26,"進場",資金明細!$N$2:$N$26,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$28,"進場",資金明細!$N$2:$N$28,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3515,7 +3538,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$26,"進場",資金明細!$N$2:$N$26,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$28,"進場",資金明細!$N$2:$N$28,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3526,7 +3549,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$26,"出場",資金明細!$N$2:$N$26,"已下單",資金明細!$K$2:$K$26,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$28,"出場",資金明細!$N$2:$N$28,"已下單",資金明細!$K$2:$K$28,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3537,7 +3560,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$13),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$14),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3546,7 +3569,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$26,"出場",資金明細!$N$2:$N$26,"已下單",資金明細!$K$2:$K$26,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$28,"出場",資金明細!$N$2:$N$28,"已下單",資金明細!$K$2:$K$28,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3562,7 +3585,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$26,"出場",資金明細!$N$2:$N$26,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$28,"出場",資金明細!$N$2:$N$28,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3578,7 +3601,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$26)</f>
+        <f>MAX(資金明細!$U$2:$U$28)</f>
         <v/>
       </c>
     </row>
@@ -3594,7 +3617,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$26)</f>
+        <f>MAX(資金明細!$S$2:$S$28)</f>
         <v/>
       </c>
     </row>
@@ -3605,7 +3628,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V26</f>
+        <f>B5*資金明細!V28</f>
         <v/>
       </c>
     </row>
@@ -3627,7 +3650,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$26)</f>
+        <f>MAX(資金明細!$Y$2:$Y$28)</f>
         <v/>
       </c>
     </row>
@@ -3649,7 +3672,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$26,MATCH(1,資金明細!$Z$2:$Z$26,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$28,MATCH(1,資金明細!$Z$2:$Z$28,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3660,7 +3683,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$26,"進場",資金明細!$N$2:$N$26,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$28,"進場",資金明細!$N$2:$N$28,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3725,7 +3748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6262,9 +6285,202 @@
         <v/>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>46290.84166666667</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>MUBARAK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="n">
+        <v>0.04613</v>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>0.0447461</v>
+      </c>
+      <c r="I27" s="17" t="n">
+        <v>0.0484365</v>
+      </c>
+      <c r="J27" s="17" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="16">
+        <f>資金模擬!$B$5*V26</f>
+        <v/>
+      </c>
+      <c r="N27" s="2">
+        <f>IF(Z26=1,"已停止",IF(T26&gt;=M27,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O27" s="16">
+        <f>IF(N27="已下單",M27*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P27" s="4" t="n"/>
+      <c r="Q27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="10">
+        <f>R26+Q27</f>
+        <v/>
+      </c>
+      <c r="S27" s="16">
+        <f>S26+IF(N27="已下單",M27,0)</f>
+        <v/>
+      </c>
+      <c r="T27" s="16">
+        <f>R27-S27</f>
+        <v/>
+      </c>
+      <c r="U27" s="2">
+        <f>U26+IF(N27="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V27" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R27,0),MAX(V26,FLOOR(MAX(R27,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W27" s="10">
+        <f>MAX(W26,R27)</f>
+        <v/>
+      </c>
+      <c r="X27" s="4">
+        <f>IF(W27&gt;0,R27/W27-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y27" s="16">
+        <f>IF(R27&gt;0,S27*資金模擬!$B$7/R27,0)</f>
+        <v/>
+      </c>
+      <c r="Z27" s="2">
+        <f>IF(OR(Z26=1,R27&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>46290.86875</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>MUBARAK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>0.04613</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>0.0447461</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>0.0484365</v>
+      </c>
+      <c r="J28" s="17" t="n">
+        <v>0.0447461</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L28" s="5">
+        <f>交易明細!K14</f>
+        <v/>
+      </c>
+      <c r="M28" s="16">
+        <f>M27</f>
+        <v/>
+      </c>
+      <c r="N28" s="2">
+        <f>N27</f>
+        <v/>
+      </c>
+      <c r="O28" s="16">
+        <f>O27</f>
+        <v/>
+      </c>
+      <c r="P28" s="4">
+        <f>交易明細!L14</f>
+        <v/>
+      </c>
+      <c r="Q28" s="10">
+        <f>IF(N28="已下單",O28*P28,0)</f>
+        <v/>
+      </c>
+      <c r="R28" s="10">
+        <f>R27+Q28</f>
+        <v/>
+      </c>
+      <c r="S28" s="16">
+        <f>S27-IF(N28="已下單",M28,0)</f>
+        <v/>
+      </c>
+      <c r="T28" s="16">
+        <f>R28-S28</f>
+        <v/>
+      </c>
+      <c r="U28" s="2">
+        <f>U27-IF(N28="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V28" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R28,0),MAX(V27,FLOOR(MAX(R28,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W28" s="10">
+        <f>MAX(W27,R28)</f>
+        <v/>
+      </c>
+      <c r="X28" s="4">
+        <f>IF(W28&gt;0,R28/W28-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y28" s="16">
+        <f>IF(R28&gt;0,S28*資金模擬!$B$7/R28,0)</f>
+        <v/>
+      </c>
+      <c r="Z28" s="2">
+        <f>IF(OR(Z27=1,R28&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z26"/>
-  <conditionalFormatting sqref="K2:K26">
+  <autoFilter ref="A1:Z28"/>
+  <conditionalFormatting sqref="K2:K28">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -6272,7 +6488,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N26">
+  <conditionalFormatting sqref="N2:N28">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -6280,7 +6496,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q26">
+  <conditionalFormatting sqref="Q2:Q28">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -6345,7 +6561,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-25 19:42（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-25 21:54（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -6555,7 +6771,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$13),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$14),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -6581,7 +6797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH13"/>
+  <dimension ref="A1:AH14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7884,9 +8100,100 @@
         <v>15</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>MUBARAK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>46290.84166666667</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0.04613</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>0.0447461</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>0.0484365</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>46290.86875</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>0.0447461</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K14" s="5">
+        <f>(H14-D14)*24</f>
+        <v/>
+      </c>
+      <c r="L14" s="4">
+        <f>IF(C14="做多",I14/E14-1,1-I14/E14)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
+      <c r="Q14" s="19" t="n"/>
+      <c r="R14" s="19" t="n"/>
+      <c r="S14" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>0.003468458703663524</v>
+      </c>
+      <c r="U14" s="16" t="n"/>
+      <c r="V14" s="16" t="n"/>
+      <c r="W14" s="4" t="n"/>
+      <c r="X14" s="4" t="n"/>
+      <c r="Y14" s="4" t="n"/>
+      <c r="Z14" s="4" t="n"/>
+      <c r="AA14" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB14" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC14" s="4">
+        <f>(AB14+2*參數!$B$7)/(AA14+AB14)</f>
+        <v/>
+      </c>
+      <c r="AD14" s="2" t="n">
+        <v>0.06917504089740589</v>
+      </c>
+      <c r="AE14" s="2" t="n">
+        <v>0.52803218169666</v>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>15分0.5倍</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="n">
+        <v>0.0008678672163158208</v>
+      </c>
+      <c r="AH14" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AH13"/>
-  <conditionalFormatting sqref="J2:J13">
+  <autoFilter ref="A1:AH14"/>
+  <conditionalFormatting sqref="J2:J14">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -7907,7 +8214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7993,27 +8300,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A2,交易明細!$C$2:$C$13,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A2,交易明細!$C$2:$C$14,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A2,交易明細!$C$2:$C$13,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A2,交易明細!$C$2:$C$14,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$13,$A2,交易明細!$J$2:$J$13,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$14,$A2,交易明細!$J$2:$J$14,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A2,交易明細!$J$2:$J$13,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A2,交易明細!$J$2:$J$14,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A2,交易明細!$J$2:$J$13,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A2,交易明細!$J$2:$J$14,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -8021,19 +8328,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A2,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A2,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A2,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A2,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A2,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A2,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A2,交易明細!$J$2:$J$13,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A2,交易明細!$J$2:$J$14,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8044,27 +8351,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A3,交易明細!$C$2:$C$13,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A3,交易明細!$C$2:$C$14,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A3,交易明細!$C$2:$C$13,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A3,交易明細!$C$2:$C$14,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$13,$A3,交易明細!$J$2:$J$13,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$14,$A3,交易明細!$J$2:$J$14,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A3,交易明細!$J$2:$J$13,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A3,交易明細!$J$2:$J$14,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A3,交易明細!$J$2:$J$13,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A3,交易明細!$J$2:$J$14,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -8072,19 +8379,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A3,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A3,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A3,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A3,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A3,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A3,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A3,交易明細!$J$2:$J$13,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A3,交易明細!$J$2:$J$14,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8095,27 +8402,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A4,交易明細!$C$2:$C$13,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A4,交易明細!$C$2:$C$14,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A4,交易明細!$C$2:$C$13,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A4,交易明細!$C$2:$C$14,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$13,$A4,交易明細!$J$2:$J$13,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$14,$A4,交易明細!$J$2:$J$14,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A4,交易明細!$J$2:$J$13,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A4,交易明細!$J$2:$J$14,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A4,交易明細!$J$2:$J$13,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A4,交易明細!$J$2:$J$14,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -8123,19 +8430,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A4,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A4,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A4,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A4,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A4,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A4,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A4,交易明細!$J$2:$J$13,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A4,交易明細!$J$2:$J$14,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8146,27 +8453,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A5,交易明細!$C$2:$C$13,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A5,交易明細!$C$2:$C$14,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A5,交易明細!$C$2:$C$13,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A5,交易明細!$C$2:$C$14,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$13,$A5,交易明細!$J$2:$J$13,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$14,$A5,交易明細!$J$2:$J$14,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A5,交易明細!$J$2:$J$13,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A5,交易明細!$J$2:$J$14,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A5,交易明細!$J$2:$J$13,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A5,交易明細!$J$2:$J$14,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -8174,19 +8481,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A5,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A5,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A5,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A5,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A5,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A5,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A5,交易明細!$J$2:$J$13,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A5,交易明細!$J$2:$J$14,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8197,27 +8504,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A6,交易明細!$C$2:$C$13,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A6,交易明細!$C$2:$C$14,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A6,交易明細!$C$2:$C$13,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A6,交易明細!$C$2:$C$14,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$13,$A6,交易明細!$J$2:$J$13,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$14,$A6,交易明細!$J$2:$J$14,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A6,交易明細!$J$2:$J$13,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A6,交易明細!$J$2:$J$14,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A6,交易明細!$J$2:$J$13,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A6,交易明細!$J$2:$J$14,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -8225,19 +8532,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A6,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A6,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A6,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A6,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A6,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A6,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A6,交易明細!$J$2:$J$13,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A6,交易明細!$J$2:$J$14,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8248,27 +8555,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A7,交易明細!$C$2:$C$13,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A7,交易明細!$C$2:$C$14,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A7,交易明細!$C$2:$C$13,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A7,交易明細!$C$2:$C$14,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$13,$A7,交易明細!$J$2:$J$13,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$14,$A7,交易明細!$J$2:$J$14,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A7,交易明細!$J$2:$J$13,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A7,交易明細!$J$2:$J$14,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A7,交易明細!$J$2:$J$13,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A7,交易明細!$J$2:$J$14,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -8276,19 +8583,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A7,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A7,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A7,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A7,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A7,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A7,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A7,交易明細!$J$2:$J$13,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A7,交易明細!$J$2:$J$14,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8299,27 +8606,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A8,交易明細!$C$2:$C$13,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A8,交易明細!$C$2:$C$14,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A8,交易明細!$C$2:$C$13,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A8,交易明細!$C$2:$C$14,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$13,$A8,交易明細!$J$2:$J$13,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$14,$A8,交易明細!$J$2:$J$14,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A8,交易明細!$J$2:$J$13,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A8,交易明細!$J$2:$J$14,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A8,交易明細!$J$2:$J$13,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A8,交易明細!$J$2:$J$14,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -8327,19 +8634,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A8,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A8,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A8,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A8,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A8,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A8,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A8,交易明細!$J$2:$J$13,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A8,交易明細!$J$2:$J$14,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8350,27 +8657,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A9,交易明細!$C$2:$C$13,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A9,交易明細!$C$2:$C$14,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A9,交易明細!$C$2:$C$13,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A9,交易明細!$C$2:$C$14,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$13,$A9,交易明細!$J$2:$J$13,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$14,$A9,交易明細!$J$2:$J$14,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A9,交易明細!$J$2:$J$13,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A9,交易明細!$J$2:$J$14,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A9,交易明細!$J$2:$J$13,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A9,交易明細!$J$2:$J$14,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -8378,19 +8685,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A9,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A9,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A9,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A9,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A9,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A9,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A9,交易明細!$J$2:$J$13,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A9,交易明細!$J$2:$J$14,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8401,27 +8708,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A10,交易明細!$C$2:$C$13,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A10,交易明細!$C$2:$C$14,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A10,交易明細!$C$2:$C$13,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A10,交易明細!$C$2:$C$14,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$13,$A10,交易明細!$J$2:$J$13,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$14,$A10,交易明細!$J$2:$J$14,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A10,交易明細!$J$2:$J$13,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A10,交易明細!$J$2:$J$14,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A10,交易明細!$J$2:$J$13,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A10,交易明細!$J$2:$J$14,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -8429,19 +8736,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A10,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A10,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A10,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A10,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A10,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A10,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A10,交易明細!$J$2:$J$13,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A10,交易明細!$J$2:$J$14,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8452,27 +8759,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A11,交易明細!$C$2:$C$13,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A11,交易明細!$C$2:$C$14,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A11,交易明細!$C$2:$C$13,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A11,交易明細!$C$2:$C$14,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$13,$A11,交易明細!$J$2:$J$13,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$14,$A11,交易明細!$J$2:$J$14,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A11,交易明細!$J$2:$J$13,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A11,交易明細!$J$2:$J$14,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A11,交易明細!$J$2:$J$13,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A11,交易明細!$J$2:$J$14,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -8480,19 +8787,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A11,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A11,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A11,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A11,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A11,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A11,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A11,交易明細!$J$2:$J$13,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A11,交易明細!$J$2:$J$14,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8503,27 +8810,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A12,交易明細!$C$2:$C$13,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A12,交易明細!$C$2:$C$14,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A12,交易明細!$C$2:$C$13,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A12,交易明細!$C$2:$C$14,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$13,$A12,交易明細!$J$2:$J$13,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$14,$A12,交易明細!$J$2:$J$14,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A12,交易明細!$J$2:$J$13,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A12,交易明細!$J$2:$J$14,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A12,交易明細!$J$2:$J$13,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A12,交易明細!$J$2:$J$14,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -8531,24 +8838,75 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A12,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A12,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$13,交易明細!$B$2:$B$13,$A12,交易明細!$J$2:$J$13,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A12,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$13,交易明細!$B$2:$B$13,$A12,交易明細!$J$2:$J$13,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A12,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$13,$A12,交易明細!$J$2:$J$13,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A12,交易明細!$J$2:$J$14,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>MUBARAK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A13,交易明細!$C$2:$C$14,"做多")</f>
+        <v/>
+      </c>
+      <c r="D13" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A13,交易明細!$C$2:$C$14,"做空")</f>
+        <v/>
+      </c>
+      <c r="E13" s="2">
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$14,$A13,交易明細!$J$2:$J$14,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F13" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A13,交易明細!$J$2:$J$14,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G13" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A13,交易明細!$J$2:$J$14,"止損")</f>
+        <v/>
+      </c>
+      <c r="H13" s="4">
+        <f>IFERROR(F13/E13,0)</f>
+        <v/>
+      </c>
+      <c r="I13" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A13,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J13" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A13,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K13" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A13,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L13" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$14,$A13,交易明細!$J$2:$J$14,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L12"/>
+  <autoFilter ref="A1:L13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,8 +17,8 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
   </definedNames>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$28</f>
+              <f>'資金明細'!$R$2:$R$30</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 21:54（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 23:58（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -796,19 +796,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$14,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$15,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$14,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$15,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$14,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$15,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$14,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$15,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -816,35 +816,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$14,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$15,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$J$2:$J$14,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$J$2:$J$15,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$J$2:$J$14,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$J$2:$J$15,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$J$2:$J$14,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$J$2:$J$15,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$14,"&lt;&gt;未平倉",交易明細!$L$2:$L$14,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$15,"&lt;&gt;未平倉",交易明細!$L$2:$L$15,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$14,"做多",交易明細!$B$2:$B$14,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$15,"做多",交易明細!$B$2:$B$15,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -863,19 +863,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -883,35 +883,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$14,交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$15,交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$14,"做多",交易明細!$J$2:$J$14,"&lt;&gt;未平倉",交易明細!$L$2:$L$14,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"&lt;&gt;未平倉",交易明細!$L$2:$L$15,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$14,"做空",交易明細!$B$2:$B$14,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$15,"做空",交易明細!$B$2:$B$15,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -930,19 +930,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -950,35 +950,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$14,交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$15,交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$14,"做空",交易明細!$J$2:$J$14,"&lt;&gt;未平倉",交易明細!$L$2:$L$14,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"&lt;&gt;未平倉",交易明細!$L$2:$L$15,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46290.91267655093</v>
+        <v>46290.9990443287</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46290.91180555556</v>
+        <v>46290.99791666667</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
@@ -1104,38 +1104,38 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>193.4</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46290.82088560185</v>
+        <v>46290.91267655093</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46290.82013888889</v>
+        <v>46290.91180555556</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>174.9</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46290.76820827546</v>
+        <v>46290.82088560185</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46290.76736111111</v>
+        <v>46290.82013888889</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
@@ -1144,27 +1144,27 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>187</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46290.709303125</v>
+        <v>46290.76820827546</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46290.70833333334</v>
+        <v>46290.76736111111</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
@@ -1173,15 +1173,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>187.6</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46290.66382769676</v>
+        <v>46290.709303125</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46290.6625</v>
+        <v>46290.70833333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
@@ -1190,67 +1190,67 @@
         <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>185.1</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46290.61757802084</v>
+        <v>46290.66382769676</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46290.61666666667</v>
+        <v>46290.6625</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>178.9</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
@@ -1259,90 +1259,90 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
@@ -1351,73 +1351,73 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
@@ -1426,21 +1426,21 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
@@ -1449,61 +1449,61 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D19" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
@@ -1512,44 +1512,44 @@
         <v>3</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
@@ -1564,15 +1564,15 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
@@ -1587,15 +1587,15 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
@@ -1610,15 +1610,15 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>433</v>
@@ -1633,15 +1633,15 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>433</v>
@@ -1656,15 +1656,15 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>433</v>
@@ -1676,18 +1676,18 @@
         <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>433</v>
@@ -1702,15 +1702,15 @@
         <v>2</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>433</v>
@@ -1725,15 +1725,15 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>433</v>
@@ -1748,18 +1748,18 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0</v>
@@ -1771,15 +1771,15 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>441</v>
@@ -1794,15 +1794,15 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>441</v>
@@ -1817,15 +1817,15 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>441</v>
@@ -1840,18 +1840,18 @@
         <v>2</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>0</v>
@@ -1860,18 +1860,18 @@
         <v>0</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>440</v>
@@ -1886,15 +1886,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>440</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>440</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>440</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>440</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>440</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>440</v>
@@ -2898,18 +2898,18 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>0</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>442</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,15 +3197,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3220,15 +3220,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>442</v>
@@ -3243,15 +3243,15 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>442</v>
@@ -3266,15 +3266,15 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B97" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C97" s="2" t="n">
         <v>442</v>
@@ -3289,15 +3289,15 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B98" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C98" s="2" t="n">
         <v>442</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B99" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C99" s="2" t="n">
         <v>442</v>
@@ -3335,15 +3335,15 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B100" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C100" s="2" t="n">
         <v>442</v>
@@ -3358,6 +3358,29 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B101" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3423,7 +3446,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R28</f>
+        <f>資金明細!R30</f>
         <v/>
       </c>
     </row>
@@ -3461,7 +3484,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$28)</f>
+        <f>MAX(資金明細!$R$2:$R$30)</f>
         <v/>
       </c>
     </row>
@@ -3480,7 +3503,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$28)</f>
+        <f>MIN(資金明細!$R$2:$R$30)</f>
         <v/>
       </c>
     </row>
@@ -3500,7 +3523,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$28)</f>
+        <f>MIN(資金明細!$X$2:$X$30)</f>
         <v/>
       </c>
     </row>
@@ -3519,7 +3542,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$28,"進場",資金明細!$N$2:$N$28,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$30,"進場",資金明細!$N$2:$N$30,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3538,7 +3561,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$28,"進場",資金明細!$N$2:$N$28,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$30,"進場",資金明細!$N$2:$N$30,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3549,7 +3572,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$28,"出場",資金明細!$N$2:$N$28,"已下單",資金明細!$K$2:$K$28,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$30,"出場",資金明細!$N$2:$N$30,"已下單",資金明細!$K$2:$K$30,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3560,7 +3583,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$14),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$15),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3569,7 +3592,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$28,"出場",資金明細!$N$2:$N$28,"已下單",資金明細!$K$2:$K$28,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$30,"出場",資金明細!$N$2:$N$30,"已下單",資金明細!$K$2:$K$30,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3585,7 +3608,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$28,"出場",資金明細!$N$2:$N$28,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$30,"出場",資金明細!$N$2:$N$30,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3601,7 +3624,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$28)</f>
+        <f>MAX(資金明細!$U$2:$U$30)</f>
         <v/>
       </c>
     </row>
@@ -3617,7 +3640,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$28)</f>
+        <f>MAX(資金明細!$S$2:$S$30)</f>
         <v/>
       </c>
     </row>
@@ -3628,7 +3651,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V28</f>
+        <f>B5*資金明細!V30</f>
         <v/>
       </c>
     </row>
@@ -3650,7 +3673,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$28)</f>
+        <f>MAX(資金明細!$Y$2:$Y$30)</f>
         <v/>
       </c>
     </row>
@@ -3672,7 +3695,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$28,MATCH(1,資金明細!$Z$2:$Z$28,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$30,MATCH(1,資金明細!$Z$2:$Z$30,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3683,7 +3706,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$28,"進場",資金明細!$N$2:$N$28,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$30,"進場",資金明細!$N$2:$N$30,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3748,7 +3771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6478,9 +6501,202 @@
         <v/>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>46290.96875</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>MOVR_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>1.08543</v>
+      </c>
+      <c r="I29" s="17" t="n">
+        <v>1.17495</v>
+      </c>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="16">
+        <f>資金模擬!$B$5*V28</f>
+        <v/>
+      </c>
+      <c r="N29" s="2">
+        <f>IF(Z28=1,"已停止",IF(T28&gt;=M29,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O29" s="16">
+        <f>IF(N29="已下單",M29*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P29" s="4" t="n"/>
+      <c r="Q29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="10">
+        <f>R28+Q29</f>
+        <v/>
+      </c>
+      <c r="S29" s="16">
+        <f>S28+IF(N29="已下單",M29,0)</f>
+        <v/>
+      </c>
+      <c r="T29" s="16">
+        <f>R29-S29</f>
+        <v/>
+      </c>
+      <c r="U29" s="2">
+        <f>U28+IF(N29="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V29" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R29,0),MAX(V28,FLOOR(MAX(R29,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W29" s="10">
+        <f>MAX(W28,R29)</f>
+        <v/>
+      </c>
+      <c r="X29" s="4">
+        <f>IF(W29&gt;0,R29/W29-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y29" s="16">
+        <f>IF(R29&gt;0,S29*資金模擬!$B$7/R29,0)</f>
+        <v/>
+      </c>
+      <c r="Z29" s="2">
+        <f>IF(OR(Z28=1,R29&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>46290.97430555556</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>MOVR_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>1.08543</v>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>1.17495</v>
+      </c>
+      <c r="J30" s="17" t="n">
+        <v>1.08543</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L30" s="5">
+        <f>交易明細!K15</f>
+        <v/>
+      </c>
+      <c r="M30" s="16">
+        <f>M29</f>
+        <v/>
+      </c>
+      <c r="N30" s="2">
+        <f>N29</f>
+        <v/>
+      </c>
+      <c r="O30" s="16">
+        <f>O29</f>
+        <v/>
+      </c>
+      <c r="P30" s="4">
+        <f>交易明細!L15</f>
+        <v/>
+      </c>
+      <c r="Q30" s="10">
+        <f>IF(N30="已下單",O30*P30,0)</f>
+        <v/>
+      </c>
+      <c r="R30" s="10">
+        <f>R29+Q30</f>
+        <v/>
+      </c>
+      <c r="S30" s="16">
+        <f>S29-IF(N30="已下單",M30,0)</f>
+        <v/>
+      </c>
+      <c r="T30" s="16">
+        <f>R30-S30</f>
+        <v/>
+      </c>
+      <c r="U30" s="2">
+        <f>U29-IF(N30="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V30" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R30,0),MAX(V29,FLOOR(MAX(R30,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W30" s="10">
+        <f>MAX(W29,R30)</f>
+        <v/>
+      </c>
+      <c r="X30" s="4">
+        <f>IF(W30&gt;0,R30/W30-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y30" s="16">
+        <f>IF(R30&gt;0,S30*資金模擬!$B$7/R30,0)</f>
+        <v/>
+      </c>
+      <c r="Z30" s="2">
+        <f>IF(OR(Z29=1,R30&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z28"/>
-  <conditionalFormatting sqref="K2:K28">
+  <autoFilter ref="A1:Z30"/>
+  <conditionalFormatting sqref="K2:K30">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -6488,7 +6704,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N28">
+  <conditionalFormatting sqref="N2:N30">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -6496,7 +6712,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q28">
+  <conditionalFormatting sqref="Q2:Q30">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -6561,7 +6777,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-25 21:54（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-25 23:58（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -6771,7 +6987,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$14),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$15),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -6797,7 +7013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH14"/>
+  <dimension ref="A1:AH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8191,9 +8407,100 @@
         <v>12</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>MOVR_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>46290.96875</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>1.08543</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>1.17495</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>46290.97430555556</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>1.08543</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K15" s="5">
+        <f>(H15-D15)*24</f>
+        <v/>
+      </c>
+      <c r="L15" s="4">
+        <f>IF(C15="做多",I15/E15-1,1-I15/E15)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="19" t="n"/>
+      <c r="R15" s="19" t="n"/>
+      <c r="S15" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>0.01251117068811447</v>
+      </c>
+      <c r="U15" s="16" t="n"/>
+      <c r="V15" s="16" t="n"/>
+      <c r="W15" s="4" t="n"/>
+      <c r="X15" s="4" t="n"/>
+      <c r="Y15" s="4" t="n"/>
+      <c r="Z15" s="4" t="n"/>
+      <c r="AA15" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB15" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC15" s="4">
+        <f>(AB15+2*參數!$B$7)/(AA15+AB15)</f>
+        <v/>
+      </c>
+      <c r="AD15" s="2" t="n">
+        <v>0.06886227544910173</v>
+      </c>
+      <c r="AE15" s="2" t="n">
+        <v>0.5088775642603551</v>
+      </c>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>15分0.5倍</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="n">
+        <v>0.04384328358208944</v>
+      </c>
+      <c r="AH15" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AH14"/>
-  <conditionalFormatting sqref="J2:J14">
+  <autoFilter ref="A1:AH15"/>
+  <conditionalFormatting sqref="J2:J15">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -8300,27 +8607,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A2,交易明細!$C$2:$C$14,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A2,交易明細!$C$2:$C$15,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A2,交易明細!$C$2:$C$14,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A2,交易明細!$C$2:$C$15,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$14,$A2,交易明細!$J$2:$J$14,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$15,$A2,交易明細!$J$2:$J$15,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A2,交易明細!$J$2:$J$14,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A2,交易明細!$J$2:$J$15,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A2,交易明細!$J$2:$J$14,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A2,交易明細!$J$2:$J$15,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -8328,50 +8635,50 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A2,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A2,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A2,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A2,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A2,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A2,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A2,交易明細!$J$2:$J$14,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A2,交易明細!$J$2:$J$15,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>NOM_USDT_PERP</t>
+          <t>MOVR_USDT_PERP</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A3,交易明細!$C$2:$C$14,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A3,交易明細!$C$2:$C$15,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A3,交易明細!$C$2:$C$14,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A3,交易明細!$C$2:$C$15,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$14,$A3,交易明細!$J$2:$J$14,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$15,$A3,交易明細!$J$2:$J$15,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A3,交易明細!$J$2:$J$14,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A3,交易明細!$J$2:$J$15,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A3,交易明細!$J$2:$J$14,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A3,交易明細!$J$2:$J$15,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -8379,50 +8686,50 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A3,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A3,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A3,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A3,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A3,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A3,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A3,交易明細!$J$2:$J$14,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A3,交易明細!$J$2:$J$15,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BROCCOLI_USDT_PERP</t>
+          <t>NOM_USDT_PERP</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A4,交易明細!$C$2:$C$14,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A4,交易明細!$C$2:$C$15,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A4,交易明細!$C$2:$C$14,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A4,交易明細!$C$2:$C$15,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$14,$A4,交易明細!$J$2:$J$14,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$15,$A4,交易明細!$J$2:$J$15,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A4,交易明細!$J$2:$J$14,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A4,交易明細!$J$2:$J$15,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A4,交易明細!$J$2:$J$14,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A4,交易明細!$J$2:$J$15,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -8430,50 +8737,50 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A4,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A4,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A4,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A4,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A4,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A4,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A4,交易明細!$J$2:$J$14,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A4,交易明細!$J$2:$J$15,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AGT_USDT_PERP</t>
+          <t>BROCCOLI_USDT_PERP</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A5,交易明細!$C$2:$C$14,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A5,交易明細!$C$2:$C$15,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A5,交易明細!$C$2:$C$14,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A5,交易明細!$C$2:$C$15,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$14,$A5,交易明細!$J$2:$J$14,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$15,$A5,交易明細!$J$2:$J$15,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A5,交易明細!$J$2:$J$14,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A5,交易明細!$J$2:$J$15,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A5,交易明細!$J$2:$J$14,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A5,交易明細!$J$2:$J$15,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -8481,50 +8788,50 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A5,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A5,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A5,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A5,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A5,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A5,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A5,交易明細!$J$2:$J$14,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A5,交易明細!$J$2:$J$15,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BB_USDT_PERP</t>
+          <t>AGT_USDT_PERP</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A6,交易明細!$C$2:$C$14,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A6,交易明細!$C$2:$C$15,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A6,交易明細!$C$2:$C$14,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A6,交易明細!$C$2:$C$15,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$14,$A6,交易明細!$J$2:$J$14,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$15,$A6,交易明細!$J$2:$J$15,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A6,交易明細!$J$2:$J$14,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A6,交易明細!$J$2:$J$15,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A6,交易明細!$J$2:$J$14,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A6,交易明細!$J$2:$J$15,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -8532,50 +8839,50 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A6,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A6,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A6,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A6,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A6,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A6,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A6,交易明細!$J$2:$J$14,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A6,交易明細!$J$2:$J$15,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>RIVER_USDT_PERP</t>
+          <t>BB_USDT_PERP</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A7,交易明細!$C$2:$C$14,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A7,交易明細!$C$2:$C$15,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A7,交易明細!$C$2:$C$14,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A7,交易明細!$C$2:$C$15,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$14,$A7,交易明細!$J$2:$J$14,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$15,$A7,交易明細!$J$2:$J$15,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A7,交易明細!$J$2:$J$14,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A7,交易明細!$J$2:$J$15,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A7,交易明細!$J$2:$J$14,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A7,交易明細!$J$2:$J$15,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -8583,50 +8890,50 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A7,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A7,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A7,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A7,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A7,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A7,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A7,交易明細!$J$2:$J$14,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A7,交易明細!$J$2:$J$15,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>LAB_USDT_PERP</t>
+          <t>RIVER_USDT_PERP</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A8,交易明細!$C$2:$C$14,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A8,交易明細!$C$2:$C$15,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A8,交易明細!$C$2:$C$14,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A8,交易明細!$C$2:$C$15,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$14,$A8,交易明細!$J$2:$J$14,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$15,$A8,交易明細!$J$2:$J$15,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A8,交易明細!$J$2:$J$14,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A8,交易明細!$J$2:$J$15,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A8,交易明細!$J$2:$J$14,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A8,交易明細!$J$2:$J$15,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -8634,50 +8941,50 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A8,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A8,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A8,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A8,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A8,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A8,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A8,交易明細!$J$2:$J$14,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A8,交易明細!$J$2:$J$15,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SAGA_USDT_PERP</t>
+          <t>LAB_USDT_PERP</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A9,交易明細!$C$2:$C$14,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A9,交易明細!$C$2:$C$15,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A9,交易明細!$C$2:$C$14,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A9,交易明細!$C$2:$C$15,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$14,$A9,交易明細!$J$2:$J$14,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$15,$A9,交易明細!$J$2:$J$15,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A9,交易明細!$J$2:$J$14,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A9,交易明細!$J$2:$J$15,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A9,交易明細!$J$2:$J$14,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A9,交易明細!$J$2:$J$15,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -8685,50 +8992,50 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A9,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A9,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A9,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A9,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A9,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A9,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A9,交易明細!$J$2:$J$14,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A9,交易明細!$J$2:$J$15,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PLAY_USDT_PERP</t>
+          <t>SAGA_USDT_PERP</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A10,交易明細!$C$2:$C$14,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A10,交易明細!$C$2:$C$15,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A10,交易明細!$C$2:$C$14,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A10,交易明細!$C$2:$C$15,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$14,$A10,交易明細!$J$2:$J$14,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$15,$A10,交易明細!$J$2:$J$15,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A10,交易明細!$J$2:$J$14,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A10,交易明細!$J$2:$J$15,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A10,交易明細!$J$2:$J$14,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A10,交易明細!$J$2:$J$15,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -8736,50 +9043,50 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A10,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A10,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A10,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A10,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A10,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A10,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A10,交易明細!$J$2:$J$14,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A10,交易明細!$J$2:$J$15,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>MOVR_USDT_PERP</t>
+          <t>PLAY_USDT_PERP</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A11,交易明細!$C$2:$C$14,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A11,交易明細!$C$2:$C$15,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A11,交易明細!$C$2:$C$14,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A11,交易明細!$C$2:$C$15,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$14,$A11,交易明細!$J$2:$J$14,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$15,$A11,交易明細!$J$2:$J$15,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A11,交易明細!$J$2:$J$14,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A11,交易明細!$J$2:$J$15,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A11,交易明細!$J$2:$J$14,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A11,交易明細!$J$2:$J$15,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -8787,19 +9094,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A11,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A11,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A11,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A11,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A11,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A11,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A11,交易明細!$J$2:$J$14,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A11,交易明細!$J$2:$J$15,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8810,27 +9117,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A12,交易明細!$C$2:$C$14,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A12,交易明細!$C$2:$C$15,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A12,交易明細!$C$2:$C$14,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A12,交易明細!$C$2:$C$15,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$14,$A12,交易明細!$J$2:$J$14,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$15,$A12,交易明細!$J$2:$J$15,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A12,交易明細!$J$2:$J$14,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A12,交易明細!$J$2:$J$15,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A12,交易明細!$J$2:$J$14,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A12,交易明細!$J$2:$J$15,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -8838,19 +9145,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A12,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A12,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A12,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A12,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A12,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A12,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A12,交易明細!$J$2:$J$14,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A12,交易明細!$J$2:$J$15,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8861,27 +9168,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A13,交易明細!$C$2:$C$14,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A13,交易明細!$C$2:$C$15,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A13,交易明細!$C$2:$C$14,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A13,交易明細!$C$2:$C$15,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$14,$A13,交易明細!$J$2:$J$14,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$15,$A13,交易明細!$J$2:$J$15,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A13,交易明細!$J$2:$J$14,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A13,交易明細!$J$2:$J$15,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A13,交易明細!$J$2:$J$14,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A13,交易明細!$J$2:$J$15,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -8889,19 +9196,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A13,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A13,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$14,交易明細!$B$2:$B$14,$A13,交易明細!$J$2:$J$14,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A13,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$14,交易明細!$B$2:$B$14,$A13,交易明細!$J$2:$J$14,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A13,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$14,$A13,交易明細!$J$2:$J$14,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$15,$A13,交易明細!$J$2:$J$15,"未平倉")</f>
         <v/>
       </c>
     </row>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,9 +17,9 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$30</f>
+              <f>'資金明細'!$R$2:$R$34</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-25 23:58（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 00:33（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -796,19 +796,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$15,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$17,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$15,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$17,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$15,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$17,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$15,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$17,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -816,35 +816,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$15,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$17,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$J$2:$J$15,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$J$2:$J$17,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$J$2:$J$15,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$J$2:$J$17,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$J$2:$J$15,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$J$2:$J$17,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$15,"&lt;&gt;未平倉",交易明細!$L$2:$L$15,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$17,"&lt;&gt;未平倉",交易明細!$L$2:$L$17,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$15,"做多",交易明細!$B$2:$B$15,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$17,"做多",交易明細!$B$2:$B$17,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -863,19 +863,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -883,35 +883,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$15,交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$17,交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$15,"做多",交易明細!$J$2:$J$15,"&lt;&gt;未平倉",交易明細!$L$2:$L$15,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"&lt;&gt;未平倉",交易明細!$L$2:$L$17,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$15,"做空",交易明細!$B$2:$B$15,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$17,"做空",交易明細!$B$2:$B$17,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -930,19 +930,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -950,35 +950,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$15,交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$17,交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$15,"做空",交易明細!$J$2:$J$15,"&lt;&gt;未平倉",交易明細!$L$2:$L$15,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"&lt;&gt;未平倉",交易明細!$L$2:$L$17,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,33 +1086,33 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46290.9990443287</v>
+        <v>46291.02308788194</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46290.99791666667</v>
+        <v>46291.02222222222</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>197.5</v>
+        <v>140.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46290.91267655093</v>
+        <v>46290.9990443287</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46290.91180555556</v>
+        <v>46290.99791666667</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
@@ -1127,38 +1127,38 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>193.4</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46290.82088560185</v>
+        <v>46290.91267655093</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46290.82013888889</v>
+        <v>46290.91180555556</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>174.9</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46290.76820827546</v>
+        <v>46290.82088560185</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46290.76736111111</v>
+        <v>46290.82013888889</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
@@ -1167,27 +1167,27 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>187</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46290.709303125</v>
+        <v>46290.76820827546</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46290.70833333334</v>
+        <v>46290.76736111111</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -1196,15 +1196,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>187.6</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46290.66382769676</v>
+        <v>46290.709303125</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46290.6625</v>
+        <v>46290.70833333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
@@ -1213,67 +1213,67 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>185.1</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46290.61757802084</v>
+        <v>46290.66382769676</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46290.61666666667</v>
+        <v>46290.6625</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>178.9</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
@@ -1282,90 +1282,90 @@
         <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
@@ -1374,73 +1374,73 @@
         <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
@@ -1449,21 +1449,21 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -1472,61 +1472,61 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
@@ -1535,44 +1535,44 @@
         <v>3</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
@@ -1587,15 +1587,15 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
@@ -1610,15 +1610,15 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>433</v>
@@ -1633,15 +1633,15 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>433</v>
@@ -1656,15 +1656,15 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>433</v>
@@ -1679,15 +1679,15 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>433</v>
@@ -1699,18 +1699,18 @@
         <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>433</v>
@@ -1725,15 +1725,15 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>433</v>
@@ -1748,15 +1748,15 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>433</v>
@@ -1771,18 +1771,18 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0</v>
@@ -1794,15 +1794,15 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>441</v>
@@ -1817,15 +1817,15 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>441</v>
@@ -1840,15 +1840,15 @@
         <v>2</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>441</v>
@@ -1863,18 +1863,18 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>0</v>
@@ -1883,18 +1883,18 @@
         <v>0</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>440</v>
@@ -1909,15 +1909,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>440</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>440</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>440</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>440</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>440</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>440</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>440</v>
@@ -2921,18 +2921,18 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>0</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>442</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,15 +3197,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3220,15 +3220,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>442</v>
@@ -3243,15 +3243,15 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>442</v>
@@ -3266,15 +3266,15 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B97" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C97" s="2" t="n">
         <v>442</v>
@@ -3289,15 +3289,15 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B98" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C98" s="2" t="n">
         <v>442</v>
@@ -3312,15 +3312,15 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B99" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C99" s="2" t="n">
         <v>442</v>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B100" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C100" s="2" t="n">
         <v>442</v>
@@ -3358,15 +3358,15 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B101" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C101" s="2" t="n">
         <v>442</v>
@@ -3381,6 +3381,29 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B102" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3446,7 +3469,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R30</f>
+        <f>資金明細!R34</f>
         <v/>
       </c>
     </row>
@@ -3484,7 +3507,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$30)</f>
+        <f>MAX(資金明細!$R$2:$R$34)</f>
         <v/>
       </c>
     </row>
@@ -3503,7 +3526,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$30)</f>
+        <f>MIN(資金明細!$R$2:$R$34)</f>
         <v/>
       </c>
     </row>
@@ -3523,7 +3546,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$30)</f>
+        <f>MIN(資金明細!$X$2:$X$34)</f>
         <v/>
       </c>
     </row>
@@ -3542,7 +3565,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$30,"進場",資金明細!$N$2:$N$30,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$34,"進場",資金明細!$N$2:$N$34,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3561,7 +3584,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$30,"進場",資金明細!$N$2:$N$30,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$34,"進場",資金明細!$N$2:$N$34,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3572,7 +3595,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$30,"出場",資金明細!$N$2:$N$30,"已下單",資金明細!$K$2:$K$30,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$34,"出場",資金明細!$N$2:$N$34,"已下單",資金明細!$K$2:$K$34,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3583,7 +3606,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$15),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$17),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3592,7 +3615,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$30,"出場",資金明細!$N$2:$N$30,"已下單",資金明細!$K$2:$K$30,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$34,"出場",資金明細!$N$2:$N$34,"已下單",資金明細!$K$2:$K$34,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3608,7 +3631,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$30,"出場",資金明細!$N$2:$N$30,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$34,"出場",資金明細!$N$2:$N$34,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3624,7 +3647,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$30)</f>
+        <f>MAX(資金明細!$U$2:$U$34)</f>
         <v/>
       </c>
     </row>
@@ -3640,7 +3663,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$30)</f>
+        <f>MAX(資金明細!$S$2:$S$34)</f>
         <v/>
       </c>
     </row>
@@ -3651,7 +3674,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V30</f>
+        <f>B5*資金明細!V34</f>
         <v/>
       </c>
     </row>
@@ -3673,7 +3696,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$30)</f>
+        <f>MAX(資金明細!$Y$2:$Y$34)</f>
         <v/>
       </c>
     </row>
@@ -3695,7 +3718,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$30,MATCH(1,資金明細!$Z$2:$Z$30,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$34,MATCH(1,資金明細!$Z$2:$Z$34,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3706,7 +3729,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$30,"進場",資金明細!$N$2:$N$30,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$34,"進場",資金明細!$N$2:$N$34,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3771,7 +3794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6694,9 +6717,395 @@
         <v/>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>46291.00694444445</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>LYN_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>0.04478</v>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>0.0434366</v>
+      </c>
+      <c r="I31" s="17" t="n">
+        <v>0.04701900000000001</v>
+      </c>
+      <c r="J31" s="17" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="16">
+        <f>資金模擬!$B$5*V30</f>
+        <v/>
+      </c>
+      <c r="N31" s="2">
+        <f>IF(Z30=1,"已停止",IF(T30&gt;=M31,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O31" s="16">
+        <f>IF(N31="已下單",M31*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P31" s="4" t="n"/>
+      <c r="Q31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="10">
+        <f>R30+Q31</f>
+        <v/>
+      </c>
+      <c r="S31" s="16">
+        <f>S30+IF(N31="已下單",M31,0)</f>
+        <v/>
+      </c>
+      <c r="T31" s="16">
+        <f>R31-S31</f>
+        <v/>
+      </c>
+      <c r="U31" s="2">
+        <f>U30+IF(N31="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V31" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R31,0),MAX(V30,FLOOR(MAX(R31,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W31" s="10">
+        <f>MAX(W30,R31)</f>
+        <v/>
+      </c>
+      <c r="X31" s="4">
+        <f>IF(W31&gt;0,R31/W31-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y31" s="16">
+        <f>IF(R31&gt;0,S31*資金模擬!$B$7/R31,0)</f>
+        <v/>
+      </c>
+      <c r="Z31" s="2">
+        <f>IF(OR(Z30=1,R31&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>46291.00833333333</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>LYN_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>0.04478</v>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>0.0434366</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>0.04701900000000001</v>
+      </c>
+      <c r="J32" s="17" t="n">
+        <v>0.0434366</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L32" s="5">
+        <f>交易明細!K16</f>
+        <v/>
+      </c>
+      <c r="M32" s="16">
+        <f>M31</f>
+        <v/>
+      </c>
+      <c r="N32" s="2">
+        <f>N31</f>
+        <v/>
+      </c>
+      <c r="O32" s="16">
+        <f>O31</f>
+        <v/>
+      </c>
+      <c r="P32" s="4">
+        <f>交易明細!L16</f>
+        <v/>
+      </c>
+      <c r="Q32" s="10">
+        <f>IF(N32="已下單",O32*P32,0)</f>
+        <v/>
+      </c>
+      <c r="R32" s="10">
+        <f>R31+Q32</f>
+        <v/>
+      </c>
+      <c r="S32" s="16">
+        <f>S31-IF(N32="已下單",M32,0)</f>
+        <v/>
+      </c>
+      <c r="T32" s="16">
+        <f>R32-S32</f>
+        <v/>
+      </c>
+      <c r="U32" s="2">
+        <f>U31-IF(N32="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V32" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R32,0),MAX(V31,FLOOR(MAX(R32,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W32" s="10">
+        <f>MAX(W31,R32)</f>
+        <v/>
+      </c>
+      <c r="X32" s="4">
+        <f>IF(W32&gt;0,R32/W32-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y32" s="16">
+        <f>IF(R32&gt;0,S32*資金模擬!$B$7/R32,0)</f>
+        <v/>
+      </c>
+      <c r="Z32" s="2">
+        <f>IF(OR(Z31=1,R32&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>46291.00833333333</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>SPK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>0.023765</v>
+      </c>
+      <c r="I33" s="17" t="n">
+        <v>0.025725</v>
+      </c>
+      <c r="J33" s="17" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="16">
+        <f>資金模擬!$B$5*V32</f>
+        <v/>
+      </c>
+      <c r="N33" s="2">
+        <f>IF(Z32=1,"已停止",IF(T32&gt;=M33,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O33" s="16">
+        <f>IF(N33="已下單",M33*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="10">
+        <f>R32+Q33</f>
+        <v/>
+      </c>
+      <c r="S33" s="16">
+        <f>S32+IF(N33="已下單",M33,0)</f>
+        <v/>
+      </c>
+      <c r="T33" s="16">
+        <f>R33-S33</f>
+        <v/>
+      </c>
+      <c r="U33" s="2">
+        <f>U32+IF(N33="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V33" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R33,0),MAX(V32,FLOOR(MAX(R33,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W33" s="10">
+        <f>MAX(W32,R33)</f>
+        <v/>
+      </c>
+      <c r="X33" s="4">
+        <f>IF(W33&gt;0,R33/W33-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y33" s="16">
+        <f>IF(R33&gt;0,S33*資金模擬!$B$7/R33,0)</f>
+        <v/>
+      </c>
+      <c r="Z33" s="2">
+        <f>IF(OR(Z32=1,R33&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>46291.01805555556</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>SPK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>0.023765</v>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>0.025725</v>
+      </c>
+      <c r="J34" s="17" t="n">
+        <v>0.025725</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L34" s="5">
+        <f>交易明細!K17</f>
+        <v/>
+      </c>
+      <c r="M34" s="16">
+        <f>M33</f>
+        <v/>
+      </c>
+      <c r="N34" s="2">
+        <f>N33</f>
+        <v/>
+      </c>
+      <c r="O34" s="16">
+        <f>O33</f>
+        <v/>
+      </c>
+      <c r="P34" s="4">
+        <f>交易明細!L17</f>
+        <v/>
+      </c>
+      <c r="Q34" s="10">
+        <f>IF(N34="已下單",O34*P34,0)</f>
+        <v/>
+      </c>
+      <c r="R34" s="10">
+        <f>R33+Q34</f>
+        <v/>
+      </c>
+      <c r="S34" s="16">
+        <f>S33-IF(N34="已下單",M34,0)</f>
+        <v/>
+      </c>
+      <c r="T34" s="16">
+        <f>R34-S34</f>
+        <v/>
+      </c>
+      <c r="U34" s="2">
+        <f>U33-IF(N34="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V34" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R34,0),MAX(V33,FLOOR(MAX(R34,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W34" s="10">
+        <f>MAX(W33,R34)</f>
+        <v/>
+      </c>
+      <c r="X34" s="4">
+        <f>IF(W34&gt;0,R34/W34-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y34" s="16">
+        <f>IF(R34&gt;0,S34*資金模擬!$B$7/R34,0)</f>
+        <v/>
+      </c>
+      <c r="Z34" s="2">
+        <f>IF(OR(Z33=1,R34&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z30"/>
-  <conditionalFormatting sqref="K2:K30">
+  <autoFilter ref="A1:Z34"/>
+  <conditionalFormatting sqref="K2:K34">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -6704,7 +7113,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N30">
+  <conditionalFormatting sqref="N2:N34">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -6712,7 +7121,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q30">
+  <conditionalFormatting sqref="Q2:Q34">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -6777,7 +7186,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-25 23:58（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-26 00:33（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -6987,7 +7396,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$15),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$17),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7013,7 +7422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH15"/>
+  <dimension ref="A1:AH17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8498,9 +8907,191 @@
         <v>15</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>LYN_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>46291.00694444445</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0.04478</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>0.0434366</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>0.04701900000000001</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>46291.00833333333</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>0.0434366</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K16" s="5">
+        <f>(H16-D16)*24</f>
+        <v/>
+      </c>
+      <c r="L16" s="4">
+        <f>IF(C16="做多",I16/E16-1,1-I16/E16)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n"/>
+      <c r="Q16" s="19" t="n"/>
+      <c r="R16" s="19" t="n"/>
+      <c r="S16" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>0.01987494417150515</v>
+      </c>
+      <c r="U16" s="16" t="n"/>
+      <c r="V16" s="16" t="n"/>
+      <c r="W16" s="4" t="n"/>
+      <c r="X16" s="4" t="n"/>
+      <c r="Y16" s="4" t="n"/>
+      <c r="Z16" s="4" t="n"/>
+      <c r="AA16" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB16" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC16" s="4">
+        <f>(AB16+2*參數!$B$7)/(AA16+AB16)</f>
+        <v/>
+      </c>
+      <c r="AD16" s="2" t="n">
+        <v>0.1174261392088132</v>
+      </c>
+      <c r="AE16" s="2" t="n">
+        <v>0.6496533063496981</v>
+      </c>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>15分0.5倍</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="n">
+        <v>0.001565645269514748</v>
+      </c>
+      <c r="AH16" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SPK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>46291.00833333333</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>0.023765</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>0.025725</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>46291.01805555556</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>0.025725</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="K17" s="5">
+        <f>(H17-D17)*24</f>
+        <v/>
+      </c>
+      <c r="L17" s="4">
+        <f>IF(C17="做多",I17/E17-1,1-I17/E17)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
+      <c r="Q17" s="19" t="n"/>
+      <c r="R17" s="19" t="n"/>
+      <c r="S17" s="4" t="n">
+        <v>0.01836734693877562</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U17" s="16" t="n"/>
+      <c r="V17" s="16" t="n"/>
+      <c r="W17" s="4" t="n"/>
+      <c r="X17" s="4" t="n"/>
+      <c r="Y17" s="4" t="n"/>
+      <c r="Z17" s="4" t="n"/>
+      <c r="AA17" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB17" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC17" s="4">
+        <f>(AB17+2*參數!$B$7)/(AA17+AB17)</f>
+        <v/>
+      </c>
+      <c r="AD17" s="2" t="n">
+        <v>0.06481481481481488</v>
+      </c>
+      <c r="AE17" s="2" t="n">
+        <v>0.5050397363242459</v>
+      </c>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>15分0.5倍</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="n">
+        <v>0.01072607260726066</v>
+      </c>
+      <c r="AH17" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AH15"/>
-  <conditionalFormatting sqref="J2:J15">
+  <autoFilter ref="A1:AH17"/>
+  <conditionalFormatting sqref="J2:J17">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -8521,7 +9112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8607,27 +9198,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A2,交易明細!$C$2:$C$15,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A2,交易明細!$C$2:$C$17,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A2,交易明細!$C$2:$C$15,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A2,交易明細!$C$2:$C$17,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$15,$A2,交易明細!$J$2:$J$15,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$17,$A2,交易明細!$J$2:$J$17,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A2,交易明細!$J$2:$J$15,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A2,交易明細!$J$2:$J$17,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A2,交易明細!$J$2:$J$15,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A2,交易明細!$J$2:$J$17,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -8635,19 +9226,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A2,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A2,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A2,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A2,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A2,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A2,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A2,交易明細!$J$2:$J$15,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A2,交易明細!$J$2:$J$17,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8658,27 +9249,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A3,交易明細!$C$2:$C$15,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A3,交易明細!$C$2:$C$17,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A3,交易明細!$C$2:$C$15,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A3,交易明細!$C$2:$C$17,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$15,$A3,交易明細!$J$2:$J$15,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$17,$A3,交易明細!$J$2:$J$17,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A3,交易明細!$J$2:$J$15,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A3,交易明細!$J$2:$J$17,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A3,交易明細!$J$2:$J$15,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A3,交易明細!$J$2:$J$17,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -8686,19 +9277,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A3,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A3,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A3,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A3,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A3,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A3,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A3,交易明細!$J$2:$J$15,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A3,交易明細!$J$2:$J$17,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8709,27 +9300,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A4,交易明細!$C$2:$C$15,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A4,交易明細!$C$2:$C$17,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A4,交易明細!$C$2:$C$15,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A4,交易明細!$C$2:$C$17,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$15,$A4,交易明細!$J$2:$J$15,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$17,$A4,交易明細!$J$2:$J$17,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A4,交易明細!$J$2:$J$15,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A4,交易明細!$J$2:$J$17,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A4,交易明細!$J$2:$J$15,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A4,交易明細!$J$2:$J$17,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -8737,19 +9328,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A4,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A4,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A4,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A4,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A4,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A4,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A4,交易明細!$J$2:$J$15,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A4,交易明細!$J$2:$J$17,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8760,27 +9351,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A5,交易明細!$C$2:$C$15,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A5,交易明細!$C$2:$C$17,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A5,交易明細!$C$2:$C$15,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A5,交易明細!$C$2:$C$17,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$15,$A5,交易明細!$J$2:$J$15,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$17,$A5,交易明細!$J$2:$J$17,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A5,交易明細!$J$2:$J$15,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A5,交易明細!$J$2:$J$17,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A5,交易明細!$J$2:$J$15,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A5,交易明細!$J$2:$J$17,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -8788,19 +9379,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A5,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A5,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A5,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A5,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A5,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A5,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A5,交易明細!$J$2:$J$15,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A5,交易明細!$J$2:$J$17,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8811,27 +9402,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A6,交易明細!$C$2:$C$15,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A6,交易明細!$C$2:$C$17,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A6,交易明細!$C$2:$C$15,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A6,交易明細!$C$2:$C$17,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$15,$A6,交易明細!$J$2:$J$15,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$17,$A6,交易明細!$J$2:$J$17,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A6,交易明細!$J$2:$J$15,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A6,交易明細!$J$2:$J$17,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A6,交易明細!$J$2:$J$15,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A6,交易明細!$J$2:$J$17,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -8839,19 +9430,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A6,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A6,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A6,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A6,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A6,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A6,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A6,交易明細!$J$2:$J$15,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A6,交易明細!$J$2:$J$17,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8862,27 +9453,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A7,交易明細!$C$2:$C$15,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A7,交易明細!$C$2:$C$17,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A7,交易明細!$C$2:$C$15,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A7,交易明細!$C$2:$C$17,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$15,$A7,交易明細!$J$2:$J$15,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$17,$A7,交易明細!$J$2:$J$17,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A7,交易明細!$J$2:$J$15,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A7,交易明細!$J$2:$J$17,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A7,交易明細!$J$2:$J$15,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A7,交易明細!$J$2:$J$17,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -8890,19 +9481,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A7,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A7,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A7,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A7,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A7,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A7,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A7,交易明細!$J$2:$J$15,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A7,交易明細!$J$2:$J$17,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8913,27 +9504,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A8,交易明細!$C$2:$C$15,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A8,交易明細!$C$2:$C$17,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A8,交易明細!$C$2:$C$15,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A8,交易明細!$C$2:$C$17,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$15,$A8,交易明細!$J$2:$J$15,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$17,$A8,交易明細!$J$2:$J$17,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A8,交易明細!$J$2:$J$15,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A8,交易明細!$J$2:$J$17,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A8,交易明細!$J$2:$J$15,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A8,交易明細!$J$2:$J$17,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -8941,19 +9532,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A8,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A8,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A8,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A8,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A8,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A8,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A8,交易明細!$J$2:$J$15,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A8,交易明細!$J$2:$J$17,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -8964,27 +9555,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A9,交易明細!$C$2:$C$15,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A9,交易明細!$C$2:$C$17,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A9,交易明細!$C$2:$C$15,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A9,交易明細!$C$2:$C$17,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$15,$A9,交易明細!$J$2:$J$15,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$17,$A9,交易明細!$J$2:$J$17,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A9,交易明細!$J$2:$J$15,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A9,交易明細!$J$2:$J$17,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A9,交易明細!$J$2:$J$15,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A9,交易明細!$J$2:$J$17,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -8992,19 +9583,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A9,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A9,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A9,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A9,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A9,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A9,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A9,交易明細!$J$2:$J$15,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A9,交易明細!$J$2:$J$17,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -9015,27 +9606,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A10,交易明細!$C$2:$C$15,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A10,交易明細!$C$2:$C$17,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A10,交易明細!$C$2:$C$15,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A10,交易明細!$C$2:$C$17,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$15,$A10,交易明細!$J$2:$J$15,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$17,$A10,交易明細!$J$2:$J$17,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A10,交易明細!$J$2:$J$15,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A10,交易明細!$J$2:$J$17,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A10,交易明細!$J$2:$J$15,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A10,交易明細!$J$2:$J$17,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -9043,19 +9634,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A10,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A10,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A10,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A10,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A10,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A10,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A10,交易明細!$J$2:$J$15,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A10,交易明細!$J$2:$J$17,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -9066,27 +9657,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A11,交易明細!$C$2:$C$15,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A11,交易明細!$C$2:$C$17,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A11,交易明細!$C$2:$C$15,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A11,交易明細!$C$2:$C$17,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$15,$A11,交易明細!$J$2:$J$15,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$17,$A11,交易明細!$J$2:$J$17,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A11,交易明細!$J$2:$J$15,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A11,交易明細!$J$2:$J$17,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A11,交易明細!$J$2:$J$15,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A11,交易明細!$J$2:$J$17,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -9094,19 +9685,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A11,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A11,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A11,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A11,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A11,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A11,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A11,交易明細!$J$2:$J$15,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A11,交易明細!$J$2:$J$17,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -9117,27 +9708,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A12,交易明細!$C$2:$C$15,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A12,交易明細!$C$2:$C$17,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A12,交易明細!$C$2:$C$15,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A12,交易明細!$C$2:$C$17,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$15,$A12,交易明細!$J$2:$J$15,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$17,$A12,交易明細!$J$2:$J$17,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A12,交易明細!$J$2:$J$15,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A12,交易明細!$J$2:$J$17,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A12,交易明細!$J$2:$J$15,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A12,交易明細!$J$2:$J$17,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -9145,19 +9736,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A12,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A12,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A12,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A12,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A12,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A12,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A12,交易明細!$J$2:$J$15,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A12,交易明細!$J$2:$J$17,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -9168,27 +9759,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A13,交易明細!$C$2:$C$15,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A13,交易明細!$C$2:$C$17,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A13,交易明細!$C$2:$C$15,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A13,交易明細!$C$2:$C$17,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$15,$A13,交易明細!$J$2:$J$15,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$17,$A13,交易明細!$J$2:$J$17,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A13,交易明細!$J$2:$J$15,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A13,交易明細!$J$2:$J$17,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A13,交易明細!$J$2:$J$15,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A13,交易明細!$J$2:$J$17,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -9196,24 +9787,126 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A13,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A13,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$15,交易明細!$B$2:$B$15,$A13,交易明細!$J$2:$J$15,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A13,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$15,交易明細!$B$2:$B$15,$A13,交易明細!$J$2:$J$15,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A13,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$15,$A13,交易明細!$J$2:$J$15,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A13,交易明細!$J$2:$J$17,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>LYN_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A14,交易明細!$C$2:$C$17,"做多")</f>
+        <v/>
+      </c>
+      <c r="D14" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A14,交易明細!$C$2:$C$17,"做空")</f>
+        <v/>
+      </c>
+      <c r="E14" s="2">
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$17,$A14,交易明細!$J$2:$J$17,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F14" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A14,交易明細!$J$2:$J$17,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G14" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A14,交易明細!$J$2:$J$17,"止損")</f>
+        <v/>
+      </c>
+      <c r="H14" s="4">
+        <f>IFERROR(F14/E14,0)</f>
+        <v/>
+      </c>
+      <c r="I14" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A14,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J14" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A14,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K14" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A14,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L14" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A14,交易明細!$J$2:$J$17,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SPK_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B15" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A15,交易明細!$C$2:$C$17,"做多")</f>
+        <v/>
+      </c>
+      <c r="D15" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A15,交易明細!$C$2:$C$17,"做空")</f>
+        <v/>
+      </c>
+      <c r="E15" s="2">
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$17,$A15,交易明細!$J$2:$J$17,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F15" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A15,交易明細!$J$2:$J$17,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G15" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A15,交易明細!$J$2:$J$17,"止損")</f>
+        <v/>
+      </c>
+      <c r="H15" s="4">
+        <f>IFERROR(F15/E15,0)</f>
+        <v/>
+      </c>
+      <c r="I15" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A15,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J15" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A15,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K15" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A15,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L15" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$17,$A15,交易明細!$J$2:$J$17,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L13"/>
+  <autoFilter ref="A1:L15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,8 +17,8 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
   </definedNames>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$34</f>
+              <f>'資金明細'!$R$2:$R$36</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 00:33（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 02:41（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -796,19 +796,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -816,35 +816,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$17,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$18,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$J$2:$J$17,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$J$2:$J$18,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$J$2:$J$17,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$J$2:$J$18,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$J$2:$J$17,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$J$2:$J$18,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$17,"&lt;&gt;未平倉",交易明細!$L$2:$L$17,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$18,"&lt;&gt;未平倉",交易明細!$L$2:$L$18,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$17,"做多",交易明細!$B$2:$B$17,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$18,"做多",交易明細!$B$2:$B$18,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -863,19 +863,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -883,35 +883,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$17,交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$18,交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$17,"做多",交易明細!$J$2:$J$17,"&lt;&gt;未平倉",交易明細!$L$2:$L$17,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"&lt;&gt;未平倉",交易明細!$L$2:$L$18,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$17,"做空",交易明細!$B$2:$B$17,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$18,"做空",交易明細!$B$2:$B$18,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -930,19 +930,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -950,35 +950,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$17,交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$18,交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$17,"做空",交易明細!$J$2:$J$17,"&lt;&gt;未平倉",交易明細!$L$2:$L$17,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"&lt;&gt;未平倉",交易明細!$L$2:$L$18,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,56 +1086,56 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46291.02308788194</v>
+        <v>46291.11246790509</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46291.02222222222</v>
+        <v>46291.11111111111</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>140.5</v>
+        <v>182.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46290.9990443287</v>
+        <v>46291.02308788194</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46290.99791666667</v>
+        <v>46291.02222222222</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>197.5</v>
+        <v>140.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46290.91267655093</v>
+        <v>46290.9990443287</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46290.91180555556</v>
+        <v>46290.99791666667</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
@@ -1150,38 +1150,38 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>193.4</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46290.82088560185</v>
+        <v>46290.91267655093</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46290.82013888889</v>
+        <v>46290.91180555556</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>174.9</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46290.76820827546</v>
+        <v>46290.82088560185</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46290.76736111111</v>
+        <v>46290.82013888889</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
@@ -1190,27 +1190,27 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>187</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46290.709303125</v>
+        <v>46290.76820827546</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46290.70833333334</v>
+        <v>46290.76736111111</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
@@ -1219,15 +1219,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>187.6</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46290.66382769676</v>
+        <v>46290.709303125</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46290.6625</v>
+        <v>46290.70833333334</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
@@ -1236,67 +1236,67 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>185.1</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46290.61757802084</v>
+        <v>46290.66382769676</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46290.61666666667</v>
+        <v>46290.6625</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>178.9</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
@@ -1305,90 +1305,90 @@
         <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
@@ -1397,73 +1397,73 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -1472,21 +1472,21 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -1495,61 +1495,61 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
@@ -1558,44 +1558,44 @@
         <v>3</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
@@ -1610,15 +1610,15 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>433</v>
@@ -1633,15 +1633,15 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>433</v>
@@ -1656,15 +1656,15 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>433</v>
@@ -1679,15 +1679,15 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>433</v>
@@ -1702,15 +1702,15 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>433</v>
@@ -1722,18 +1722,18 @@
         <v>0</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>433</v>
@@ -1748,15 +1748,15 @@
         <v>2</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>433</v>
@@ -1771,15 +1771,15 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>433</v>
@@ -1794,18 +1794,18 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>0</v>
@@ -1817,15 +1817,15 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>441</v>
@@ -1840,15 +1840,15 @@
         <v>2</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>441</v>
@@ -1863,15 +1863,15 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>441</v>
@@ -1886,18 +1886,18 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>0</v>
@@ -1906,18 +1906,18 @@
         <v>0</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>440</v>
@@ -1932,15 +1932,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>440</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>440</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>440</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>440</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>440</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>440</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>440</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>440</v>
@@ -2944,18 +2944,18 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>0</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>442</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,15 +3197,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3220,15 +3220,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>442</v>
@@ -3243,15 +3243,15 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>442</v>
@@ -3266,15 +3266,15 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B97" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C97" s="2" t="n">
         <v>442</v>
@@ -3289,15 +3289,15 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B98" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C98" s="2" t="n">
         <v>442</v>
@@ -3312,15 +3312,15 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B99" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C99" s="2" t="n">
         <v>442</v>
@@ -3335,15 +3335,15 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B100" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C100" s="2" t="n">
         <v>442</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B101" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C101" s="2" t="n">
         <v>442</v>
@@ -3381,15 +3381,15 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B102" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C102" s="2" t="n">
         <v>442</v>
@@ -3404,6 +3404,29 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B103" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3469,7 +3492,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R34</f>
+        <f>資金明細!R36</f>
         <v/>
       </c>
     </row>
@@ -3507,7 +3530,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$34)</f>
+        <f>MAX(資金明細!$R$2:$R$36)</f>
         <v/>
       </c>
     </row>
@@ -3526,7 +3549,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$34)</f>
+        <f>MIN(資金明細!$R$2:$R$36)</f>
         <v/>
       </c>
     </row>
@@ -3546,7 +3569,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$34)</f>
+        <f>MIN(資金明細!$X$2:$X$36)</f>
         <v/>
       </c>
     </row>
@@ -3565,7 +3588,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$34,"進場",資金明細!$N$2:$N$34,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$36,"進場",資金明細!$N$2:$N$36,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3584,7 +3607,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$34,"進場",資金明細!$N$2:$N$34,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$36,"進場",資金明細!$N$2:$N$36,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3595,7 +3618,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$34,"出場",資金明細!$N$2:$N$34,"已下單",資金明細!$K$2:$K$34,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$36,"出場",資金明細!$N$2:$N$36,"已下單",資金明細!$K$2:$K$36,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3606,7 +3629,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$17),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$18),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3615,7 +3638,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$34,"出場",資金明細!$N$2:$N$34,"已下單",資金明細!$K$2:$K$34,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$36,"出場",資金明細!$N$2:$N$36,"已下單",資金明細!$K$2:$K$36,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3631,7 +3654,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$34,"出場",資金明細!$N$2:$N$34,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$36,"出場",資金明細!$N$2:$N$36,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3647,7 +3670,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$34)</f>
+        <f>MAX(資金明細!$U$2:$U$36)</f>
         <v/>
       </c>
     </row>
@@ -3663,7 +3686,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$34)</f>
+        <f>MAX(資金明細!$S$2:$S$36)</f>
         <v/>
       </c>
     </row>
@@ -3674,7 +3697,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V34</f>
+        <f>B5*資金明細!V36</f>
         <v/>
       </c>
     </row>
@@ -3696,7 +3719,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$34)</f>
+        <f>MAX(資金明細!$Y$2:$Y$36)</f>
         <v/>
       </c>
     </row>
@@ -3718,7 +3741,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$34,MATCH(1,資金明細!$Z$2:$Z$34,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$36,MATCH(1,資金明細!$Z$2:$Z$36,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3729,7 +3752,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$34,"進場",資金明細!$N$2:$N$34,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$36,"進場",資金明細!$N$2:$N$36,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3794,7 +3817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7103,9 +7126,202 @@
         <v/>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>46291.05</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>LYN_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>0.07316</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>0.07096520000000001</v>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>0.07681800000000001</v>
+      </c>
+      <c r="J35" s="17" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="16">
+        <f>資金模擬!$B$5*V34</f>
+        <v/>
+      </c>
+      <c r="N35" s="2">
+        <f>IF(Z34=1,"已停止",IF(T34&gt;=M35,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O35" s="16">
+        <f>IF(N35="已下單",M35*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P35" s="4" t="n"/>
+      <c r="Q35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="10">
+        <f>R34+Q35</f>
+        <v/>
+      </c>
+      <c r="S35" s="16">
+        <f>S34+IF(N35="已下單",M35,0)</f>
+        <v/>
+      </c>
+      <c r="T35" s="16">
+        <f>R35-S35</f>
+        <v/>
+      </c>
+      <c r="U35" s="2">
+        <f>U34+IF(N35="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V35" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R35,0),MAX(V34,FLOOR(MAX(R35,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W35" s="10">
+        <f>MAX(W34,R35)</f>
+        <v/>
+      </c>
+      <c r="X35" s="4">
+        <f>IF(W35&gt;0,R35/W35-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y35" s="16">
+        <f>IF(R35&gt;0,S35*資金模擬!$B$7/R35,0)</f>
+        <v/>
+      </c>
+      <c r="Z35" s="2">
+        <f>IF(OR(Z34=1,R35&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>46291.05069444444</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>LYN_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>0.07316</v>
+      </c>
+      <c r="H36" s="17" t="n">
+        <v>0.07096520000000001</v>
+      </c>
+      <c r="I36" s="17" t="n">
+        <v>0.07681800000000001</v>
+      </c>
+      <c r="J36" s="17" t="n">
+        <v>0.07096520000000001</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="L36" s="5">
+        <f>交易明細!K18</f>
+        <v/>
+      </c>
+      <c r="M36" s="16">
+        <f>M35</f>
+        <v/>
+      </c>
+      <c r="N36" s="2">
+        <f>N35</f>
+        <v/>
+      </c>
+      <c r="O36" s="16">
+        <f>O35</f>
+        <v/>
+      </c>
+      <c r="P36" s="4">
+        <f>交易明細!L18</f>
+        <v/>
+      </c>
+      <c r="Q36" s="10">
+        <f>IF(N36="已下單",O36*P36,0)</f>
+        <v/>
+      </c>
+      <c r="R36" s="10">
+        <f>R35+Q36</f>
+        <v/>
+      </c>
+      <c r="S36" s="16">
+        <f>S35-IF(N36="已下單",M36,0)</f>
+        <v/>
+      </c>
+      <c r="T36" s="16">
+        <f>R36-S36</f>
+        <v/>
+      </c>
+      <c r="U36" s="2">
+        <f>U35-IF(N36="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V36" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R36,0),MAX(V35,FLOOR(MAX(R36,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W36" s="10">
+        <f>MAX(W35,R36)</f>
+        <v/>
+      </c>
+      <c r="X36" s="4">
+        <f>IF(W36&gt;0,R36/W36-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y36" s="16">
+        <f>IF(R36&gt;0,S36*資金模擬!$B$7/R36,0)</f>
+        <v/>
+      </c>
+      <c r="Z36" s="2">
+        <f>IF(OR(Z35=1,R36&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z34"/>
-  <conditionalFormatting sqref="K2:K34">
+  <autoFilter ref="A1:Z36"/>
+  <conditionalFormatting sqref="K2:K36">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -7113,7 +7329,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N34">
+  <conditionalFormatting sqref="N2:N36">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -7121,7 +7337,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q34">
+  <conditionalFormatting sqref="Q2:Q36">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -7186,7 +7402,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-26 00:33（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-26 02:41（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -7396,7 +7612,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$17),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$18),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7422,7 +7638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH17"/>
+  <dimension ref="A1:AH18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9089,9 +9305,100 @@
         <v>12</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>LYN_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>46291.05</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0.07316</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>0.07096520000000001</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>0.07681800000000001</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>46291.05069444444</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>0.07096520000000001</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>止盈</t>
+        </is>
+      </c>
+      <c r="K18" s="5">
+        <f>(H18-D18)*24</f>
+        <v/>
+      </c>
+      <c r="L18" s="4">
+        <f>IF(C18="做多",I18/E18-1,1-I18/E18)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
+      <c r="Q18" s="19" t="n"/>
+      <c r="R18" s="19" t="n"/>
+      <c r="S18" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="16" t="n"/>
+      <c r="V18" s="16" t="n"/>
+      <c r="W18" s="4" t="n"/>
+      <c r="X18" s="4" t="n"/>
+      <c r="Y18" s="4" t="n"/>
+      <c r="Z18" s="4" t="n"/>
+      <c r="AA18" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB18" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC18" s="4">
+        <f>(AB18+2*參數!$B$7)/(AA18+AB18)</f>
+        <v/>
+      </c>
+      <c r="AD18" s="2" t="n">
+        <v>0.5736051982971095</v>
+      </c>
+      <c r="AE18" s="2" t="n">
+        <v>0.5566970423952549</v>
+      </c>
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>15分0.5倍</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="n">
+        <v>0.0283947146471748</v>
+      </c>
+      <c r="AH18" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AH17"/>
-  <conditionalFormatting sqref="J2:J17">
+  <autoFilter ref="A1:AH18"/>
+  <conditionalFormatting sqref="J2:J18">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -9198,27 +9505,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A2,交易明細!$C$2:$C$17,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A2,交易明細!$C$2:$C$18,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A2,交易明細!$C$2:$C$17,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A2,交易明細!$C$2:$C$18,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$17,$A2,交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$18,$A2,交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A2,交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A2,交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A2,交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A2,交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -9226,19 +9533,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A2,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A2,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A2,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A2,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A2,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A2,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A2,交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A2,交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -9249,27 +9556,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A3,交易明細!$C$2:$C$17,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A3,交易明細!$C$2:$C$18,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A3,交易明細!$C$2:$C$17,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A3,交易明細!$C$2:$C$18,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$17,$A3,交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$18,$A3,交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A3,交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A3,交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A3,交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A3,交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -9277,50 +9584,50 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A3,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A3,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A3,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A3,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A3,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A3,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A3,交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A3,交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NOM_USDT_PERP</t>
+          <t>LYN_USDT_PERP</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A4,交易明細!$C$2:$C$17,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A4,交易明細!$C$2:$C$18,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A4,交易明細!$C$2:$C$17,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A4,交易明細!$C$2:$C$18,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$17,$A4,交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$18,$A4,交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A4,交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A4,交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A4,交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A4,交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -9328,50 +9635,50 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A4,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A4,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A4,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A4,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A4,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A4,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A4,交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A4,交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BROCCOLI_USDT_PERP</t>
+          <t>NOM_USDT_PERP</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A5,交易明細!$C$2:$C$17,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A5,交易明細!$C$2:$C$18,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A5,交易明細!$C$2:$C$17,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A5,交易明細!$C$2:$C$18,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$17,$A5,交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$18,$A5,交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A5,交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A5,交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A5,交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A5,交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -9379,50 +9686,50 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A5,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A5,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A5,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A5,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A5,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A5,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A5,交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A5,交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AGT_USDT_PERP</t>
+          <t>BROCCOLI_USDT_PERP</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A6,交易明細!$C$2:$C$17,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A6,交易明細!$C$2:$C$18,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A6,交易明細!$C$2:$C$17,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A6,交易明細!$C$2:$C$18,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$17,$A6,交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$18,$A6,交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A6,交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A6,交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A6,交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A6,交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -9430,50 +9737,50 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A6,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A6,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A6,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A6,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A6,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A6,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A6,交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A6,交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BB_USDT_PERP</t>
+          <t>AGT_USDT_PERP</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A7,交易明細!$C$2:$C$17,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A7,交易明細!$C$2:$C$18,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A7,交易明細!$C$2:$C$17,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A7,交易明細!$C$2:$C$18,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$17,$A7,交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$18,$A7,交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A7,交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A7,交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A7,交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A7,交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -9481,50 +9788,50 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A7,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A7,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A7,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A7,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A7,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A7,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A7,交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A7,交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RIVER_USDT_PERP</t>
+          <t>BB_USDT_PERP</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A8,交易明細!$C$2:$C$17,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A8,交易明細!$C$2:$C$18,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A8,交易明細!$C$2:$C$17,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A8,交易明細!$C$2:$C$18,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$17,$A8,交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$18,$A8,交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A8,交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A8,交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A8,交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A8,交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -9532,50 +9839,50 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A8,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A8,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A8,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A8,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A8,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A8,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A8,交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A8,交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>LAB_USDT_PERP</t>
+          <t>RIVER_USDT_PERP</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A9,交易明細!$C$2:$C$17,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A9,交易明細!$C$2:$C$18,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A9,交易明細!$C$2:$C$17,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A9,交易明細!$C$2:$C$18,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$17,$A9,交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$18,$A9,交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A9,交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A9,交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A9,交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A9,交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -9583,50 +9890,50 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A9,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A9,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A9,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A9,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A9,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A9,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A9,交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A9,交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SAGA_USDT_PERP</t>
+          <t>LAB_USDT_PERP</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A10,交易明細!$C$2:$C$17,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A10,交易明細!$C$2:$C$18,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A10,交易明細!$C$2:$C$17,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A10,交易明細!$C$2:$C$18,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$17,$A10,交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$18,$A10,交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A10,交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A10,交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A10,交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A10,交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -9634,50 +9941,50 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A10,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A10,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A10,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A10,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A10,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A10,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A10,交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A10,交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>PLAY_USDT_PERP</t>
+          <t>SAGA_USDT_PERP</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A11,交易明細!$C$2:$C$17,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A11,交易明細!$C$2:$C$18,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A11,交易明細!$C$2:$C$17,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A11,交易明細!$C$2:$C$18,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$17,$A11,交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$18,$A11,交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A11,交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A11,交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A11,交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A11,交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -9685,50 +9992,50 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A11,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A11,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A11,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A11,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A11,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A11,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A11,交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A11,交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CASHCAT_USDT_PERP</t>
+          <t>PLAY_USDT_PERP</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A12,交易明細!$C$2:$C$17,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A12,交易明細!$C$2:$C$18,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A12,交易明細!$C$2:$C$17,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A12,交易明細!$C$2:$C$18,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$17,$A12,交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$18,$A12,交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A12,交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A12,交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A12,交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A12,交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -9736,50 +10043,50 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A12,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A12,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A12,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A12,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A12,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A12,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A12,交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A12,交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MUBARAK_USDT_PERP</t>
+          <t>CASHCAT_USDT_PERP</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A13,交易明細!$C$2:$C$17,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A13,交易明細!$C$2:$C$18,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A13,交易明細!$C$2:$C$17,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A13,交易明細!$C$2:$C$18,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$17,$A13,交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$18,$A13,交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A13,交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A13,交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A13,交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A13,交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -9787,50 +10094,50 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A13,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A13,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A13,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A13,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A13,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A13,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A13,交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A13,交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>LYN_USDT_PERP</t>
+          <t>MUBARAK_USDT_PERP</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A14,交易明細!$C$2:$C$17,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A14,交易明細!$C$2:$C$18,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A14,交易明細!$C$2:$C$17,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A14,交易明細!$C$2:$C$18,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$17,$A14,交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$18,$A14,交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A14,交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A14,交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A14,交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A14,交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -9838,19 +10145,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A14,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A14,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A14,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A14,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A14,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A14,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A14,交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A14,交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -9861,27 +10168,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A15,交易明細!$C$2:$C$17,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A15,交易明細!$C$2:$C$18,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A15,交易明細!$C$2:$C$17,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A15,交易明細!$C$2:$C$18,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$17,$A15,交易明細!$J$2:$J$17,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$18,$A15,交易明細!$J$2:$J$18,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A15,交易明細!$J$2:$J$17,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A15,交易明細!$J$2:$J$18,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A15,交易明細!$J$2:$J$17,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A15,交易明細!$J$2:$J$18,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -9889,19 +10196,19 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A15,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A15,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$17,交易明細!$B$2:$B$17,$A15,交易明細!$J$2:$J$17,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A15,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$17,交易明細!$B$2:$B$17,$A15,交易明細!$J$2:$J$17,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A15,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$17,$A15,交易明細!$J$2:$J$17,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$18,$A15,交易明細!$J$2:$J$18,"未平倉")</f>
         <v/>
       </c>
     </row>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 02:41（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 06:08（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,79 +1086,79 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46291.11246790509</v>
+        <v>46291.2560487963</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46291.11111111111</v>
+        <v>46291.25486111111</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>182.3</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46291.02308788194</v>
+        <v>46291.11246790509</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46291.02222222222</v>
+        <v>46291.11111111111</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>140.5</v>
+        <v>182.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46290.9990443287</v>
+        <v>46291.02308788194</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46290.99791666667</v>
+        <v>46291.02222222222</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>197.5</v>
+        <v>140.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46290.91267655093</v>
+        <v>46290.9990443287</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46290.91180555556</v>
+        <v>46290.99791666667</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
@@ -1173,38 +1173,38 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>193.4</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46290.82088560185</v>
+        <v>46290.91267655093</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46290.82013888889</v>
+        <v>46290.91180555556</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>174.9</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46290.76820827546</v>
+        <v>46290.82088560185</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46290.76736111111</v>
+        <v>46290.82013888889</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
@@ -1213,27 +1213,27 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>187</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46290.709303125</v>
+        <v>46290.76820827546</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46290.70833333334</v>
+        <v>46290.76736111111</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -1242,15 +1242,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>187.6</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46290.66382769676</v>
+        <v>46290.709303125</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46290.6625</v>
+        <v>46290.70833333334</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
@@ -1259,67 +1259,67 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>185.1</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46290.61757802084</v>
+        <v>46290.66382769676</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46290.61666666667</v>
+        <v>46290.6625</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>178.9</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
@@ -1328,90 +1328,90 @@
         <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
@@ -1420,73 +1420,73 @@
         <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -1495,21 +1495,21 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -1518,61 +1518,61 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
@@ -1581,44 +1581,44 @@
         <v>3</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>433</v>
@@ -1633,15 +1633,15 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>433</v>
@@ -1656,15 +1656,15 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>433</v>
@@ -1679,15 +1679,15 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>433</v>
@@ -1702,15 +1702,15 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>433</v>
@@ -1725,15 +1725,15 @@
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>433</v>
@@ -1745,18 +1745,18 @@
         <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>433</v>
@@ -1771,15 +1771,15 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>433</v>
@@ -1794,15 +1794,15 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>433</v>
@@ -1817,18 +1817,18 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>0</v>
@@ -1840,15 +1840,15 @@
         <v>2</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>441</v>
@@ -1863,15 +1863,15 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>441</v>
@@ -1886,15 +1886,15 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>441</v>
@@ -1909,18 +1909,18 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>0</v>
@@ -1929,18 +1929,18 @@
         <v>0</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>440</v>
@@ -1955,15 +1955,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>440</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>440</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>440</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>440</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>440</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>440</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>440</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>440</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>440</v>
@@ -2967,18 +2967,18 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>0</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>442</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,15 +3197,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3220,15 +3220,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>442</v>
@@ -3243,15 +3243,15 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>442</v>
@@ -3266,15 +3266,15 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B97" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C97" s="2" t="n">
         <v>442</v>
@@ -3289,15 +3289,15 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B98" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C98" s="2" t="n">
         <v>442</v>
@@ -3312,15 +3312,15 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B99" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C99" s="2" t="n">
         <v>442</v>
@@ -3335,15 +3335,15 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B100" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C100" s="2" t="n">
         <v>442</v>
@@ -3358,15 +3358,15 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B101" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C101" s="2" t="n">
         <v>442</v>
@@ -3386,10 +3386,10 @@
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B102" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C102" s="2" t="n">
         <v>442</v>
@@ -3404,15 +3404,15 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B103" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C103" s="2" t="n">
         <v>442</v>
@@ -3427,6 +3427,29 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B104" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7402,7 +7425,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-26 02:41（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-26 06:08（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 06:08（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 06:27（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46291.2560487963</v>
+        <v>46291.26887001158</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46291.25486111111</v>
+        <v>46291.26805555556</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
@@ -1104,84 +1104,84 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>191.6</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46291.11246790509</v>
+        <v>46291.2560487963</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46291.11111111111</v>
+        <v>46291.25486111111</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>182.3</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46291.02308788194</v>
+        <v>46291.11246790509</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46291.02222222222</v>
+        <v>46291.11111111111</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>140.5</v>
+        <v>182.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46290.9990443287</v>
+        <v>46291.02308788194</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46290.99791666667</v>
+        <v>46291.02222222222</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>197.5</v>
+        <v>140.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46290.91267655093</v>
+        <v>46290.9990443287</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46290.91180555556</v>
+        <v>46290.99791666667</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
@@ -1196,38 +1196,38 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>193.4</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46290.82088560185</v>
+        <v>46290.91267655093</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46290.82013888889</v>
+        <v>46290.91180555556</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>174.9</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46290.76820827546</v>
+        <v>46290.82088560185</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46290.76736111111</v>
+        <v>46290.82013888889</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
@@ -1236,27 +1236,27 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>187</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46290.709303125</v>
+        <v>46290.76820827546</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46290.70833333334</v>
+        <v>46290.76736111111</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -1265,15 +1265,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>187.6</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46290.66382769676</v>
+        <v>46290.709303125</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46290.6625</v>
+        <v>46290.70833333334</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
@@ -1282,67 +1282,67 @@
         <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>185.1</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46290.61757802084</v>
+        <v>46290.66382769676</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46290.61666666667</v>
+        <v>46290.6625</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>178.9</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
@@ -1351,90 +1351,90 @@
         <v>1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
@@ -1443,73 +1443,73 @@
         <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -1518,21 +1518,21 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -1541,61 +1541,61 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
@@ -1604,44 +1604,44 @@
         <v>3</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>433</v>
@@ -1656,15 +1656,15 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>433</v>
@@ -1679,15 +1679,15 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>433</v>
@@ -1702,15 +1702,15 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>433</v>
@@ -1725,15 +1725,15 @@
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>433</v>
@@ -1748,15 +1748,15 @@
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>433</v>
@@ -1768,18 +1768,18 @@
         <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>433</v>
@@ -1794,15 +1794,15 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>433</v>
@@ -1817,15 +1817,15 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>433</v>
@@ -1840,18 +1840,18 @@
         <v>2</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>0</v>
@@ -1863,15 +1863,15 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>441</v>
@@ -1886,15 +1886,15 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>441</v>
@@ -1909,15 +1909,15 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>441</v>
@@ -1932,18 +1932,18 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>0</v>
@@ -1952,18 +1952,18 @@
         <v>0</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>440</v>
@@ -1978,15 +1978,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>440</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>440</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>440</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>440</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>440</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>440</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>440</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>440</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>440</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>440</v>
@@ -2990,18 +2990,18 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>0</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>442</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,15 +3197,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3220,15 +3220,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>442</v>
@@ -3243,15 +3243,15 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>442</v>
@@ -3266,15 +3266,15 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B97" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C97" s="2" t="n">
         <v>442</v>
@@ -3289,15 +3289,15 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B98" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C98" s="2" t="n">
         <v>442</v>
@@ -3312,15 +3312,15 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B99" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C99" s="2" t="n">
         <v>442</v>
@@ -3335,15 +3335,15 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B100" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C100" s="2" t="n">
         <v>442</v>
@@ -3358,15 +3358,15 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B101" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C101" s="2" t="n">
         <v>442</v>
@@ -3381,15 +3381,15 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B102" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C102" s="2" t="n">
         <v>442</v>
@@ -3409,10 +3409,10 @@
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B103" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C103" s="2" t="n">
         <v>442</v>
@@ -3427,15 +3427,15 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B104" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C104" s="2" t="n">
         <v>442</v>
@@ -3450,6 +3450,29 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B105" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7425,7 +7448,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-26 06:08（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-26 06:27（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 06:27（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 08:46（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46291.26887001158</v>
+        <v>46291.36540915509</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46291.26805555556</v>
+        <v>46291.36458333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
@@ -1104,15 +1104,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>184.5</v>
+        <v>163.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46291.2560487963</v>
+        <v>46291.26887001158</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46291.25486111111</v>
+        <v>46291.26805555556</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
@@ -1127,84 +1127,84 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>191.6</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46291.11246790509</v>
+        <v>46291.2560487963</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46291.11111111111</v>
+        <v>46291.25486111111</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>182.3</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46291.02308788194</v>
+        <v>46291.11246790509</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46291.02222222222</v>
+        <v>46291.11111111111</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>140.5</v>
+        <v>182.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46290.9990443287</v>
+        <v>46291.02308788194</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46290.99791666667</v>
+        <v>46291.02222222222</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>197.5</v>
+        <v>140.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46290.91267655093</v>
+        <v>46290.9990443287</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46290.91180555556</v>
+        <v>46290.99791666667</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
@@ -1219,38 +1219,38 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>193.4</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46290.82088560185</v>
+        <v>46290.91267655093</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46290.82013888889</v>
+        <v>46290.91180555556</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>174.9</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46290.76820827546</v>
+        <v>46290.82088560185</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46290.76736111111</v>
+        <v>46290.82013888889</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
@@ -1259,27 +1259,27 @@
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>187</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46290.709303125</v>
+        <v>46290.76820827546</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46290.70833333334</v>
+        <v>46290.76736111111</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
@@ -1288,15 +1288,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>187.6</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46290.66382769676</v>
+        <v>46290.709303125</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46290.6625</v>
+        <v>46290.70833333334</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>185.1</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46290.61757802084</v>
+        <v>46290.66382769676</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46290.61666666667</v>
+        <v>46290.6625</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>178.9</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
@@ -1374,90 +1374,90 @@
         <v>1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
@@ -1466,73 +1466,73 @@
         <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -1541,21 +1541,21 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -1564,61 +1564,61 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>433</v>
@@ -1627,44 +1627,44 @@
         <v>3</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>433</v>
@@ -1679,15 +1679,15 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>433</v>
@@ -1702,15 +1702,15 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>433</v>
@@ -1725,15 +1725,15 @@
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>433</v>
@@ -1748,15 +1748,15 @@
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>433</v>
@@ -1771,15 +1771,15 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>433</v>
@@ -1791,18 +1791,18 @@
         <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>433</v>
@@ -1817,15 +1817,15 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>433</v>
@@ -1840,15 +1840,15 @@
         <v>2</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>433</v>
@@ -1863,18 +1863,18 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>0</v>
@@ -1886,15 +1886,15 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>441</v>
@@ -1909,15 +1909,15 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>441</v>
@@ -1932,15 +1932,15 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>441</v>
@@ -1955,18 +1955,18 @@
         <v>2</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0</v>
@@ -1975,18 +1975,18 @@
         <v>0</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>440</v>
@@ -2001,15 +2001,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>440</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>440</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>440</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>440</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>440</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>440</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>440</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>440</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>440</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>440</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>440</v>
@@ -3013,18 +3013,18 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>0</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>442</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,15 +3197,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3220,15 +3220,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>442</v>
@@ -3243,15 +3243,15 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>442</v>
@@ -3266,15 +3266,15 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B97" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C97" s="2" t="n">
         <v>442</v>
@@ -3289,15 +3289,15 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B98" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C98" s="2" t="n">
         <v>442</v>
@@ -3312,15 +3312,15 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B99" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C99" s="2" t="n">
         <v>442</v>
@@ -3335,15 +3335,15 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B100" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C100" s="2" t="n">
         <v>442</v>
@@ -3358,15 +3358,15 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B101" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C101" s="2" t="n">
         <v>442</v>
@@ -3381,15 +3381,15 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B102" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C102" s="2" t="n">
         <v>442</v>
@@ -3404,15 +3404,15 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B103" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C103" s="2" t="n">
         <v>442</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B104" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C104" s="2" t="n">
         <v>442</v>
@@ -3450,15 +3450,15 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B105" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C105" s="2" t="n">
         <v>442</v>
@@ -3473,6 +3473,29 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B106" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7448,7 +7471,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-26 06:27（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-26 08:46（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 08:46（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 09:38（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46291.36540915509</v>
+        <v>46291.40186751157</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46291.36458333334</v>
+        <v>46291.40069444444</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
@@ -1104,15 +1104,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>163.5</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46291.26887001158</v>
+        <v>46291.36540915509</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46291.26805555556</v>
+        <v>46291.36458333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
@@ -1127,15 +1127,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>184.5</v>
+        <v>163.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46291.2560487963</v>
+        <v>46291.26887001158</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46291.25486111111</v>
+        <v>46291.26805555556</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
@@ -1150,84 +1150,84 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>191.6</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46291.11246790509</v>
+        <v>46291.2560487963</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46291.11111111111</v>
+        <v>46291.25486111111</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>182.3</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46291.02308788194</v>
+        <v>46291.11246790509</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46291.02222222222</v>
+        <v>46291.11111111111</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>140.5</v>
+        <v>182.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46290.9990443287</v>
+        <v>46291.02308788194</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46290.99791666667</v>
+        <v>46291.02222222222</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>197.5</v>
+        <v>140.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46290.91267655093</v>
+        <v>46290.9990443287</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46290.91180555556</v>
+        <v>46290.99791666667</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
@@ -1242,38 +1242,38 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>193.4</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46290.82088560185</v>
+        <v>46290.91267655093</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46290.82013888889</v>
+        <v>46290.91180555556</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>174.9</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46290.76820827546</v>
+        <v>46290.82088560185</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46290.76736111111</v>
+        <v>46290.82013888889</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
@@ -1282,27 +1282,27 @@
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>187</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46290.709303125</v>
+        <v>46290.76820827546</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46290.70833333334</v>
+        <v>46290.76736111111</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -1311,15 +1311,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>187.6</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46290.66382769676</v>
+        <v>46290.709303125</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46290.6625</v>
+        <v>46290.70833333334</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
@@ -1328,67 +1328,67 @@
         <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>185.1</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46290.61757802084</v>
+        <v>46290.66382769676</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46290.61666666667</v>
+        <v>46290.6625</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>178.9</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
@@ -1397,90 +1397,90 @@
         <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
@@ -1489,73 +1489,73 @@
         <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -1564,21 +1564,21 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
@@ -1587,61 +1587,61 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>433</v>
@@ -1650,44 +1650,44 @@
         <v>3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>433</v>
@@ -1702,15 +1702,15 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>433</v>
@@ -1725,15 +1725,15 @@
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>433</v>
@@ -1748,15 +1748,15 @@
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>433</v>
@@ -1771,15 +1771,15 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>433</v>
@@ -1794,15 +1794,15 @@
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>433</v>
@@ -1814,18 +1814,18 @@
         <v>0</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>433</v>
@@ -1840,15 +1840,15 @@
         <v>2</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>433</v>
@@ -1863,15 +1863,15 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>433</v>
@@ -1886,18 +1886,18 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>0</v>
@@ -1909,15 +1909,15 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>441</v>
@@ -1932,15 +1932,15 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>441</v>
@@ -1955,15 +1955,15 @@
         <v>2</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>441</v>
@@ -1978,18 +1978,18 @@
         <v>2</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>0</v>
@@ -1998,18 +1998,18 @@
         <v>0</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>440</v>
@@ -2024,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>440</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>440</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>440</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>440</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>440</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>440</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>440</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>440</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>440</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>440</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>440</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>440</v>
@@ -3036,18 +3036,18 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>0</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>442</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,15 +3197,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3220,15 +3220,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>442</v>
@@ -3243,15 +3243,15 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>442</v>
@@ -3266,15 +3266,15 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B97" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C97" s="2" t="n">
         <v>442</v>
@@ -3289,15 +3289,15 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B98" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C98" s="2" t="n">
         <v>442</v>
@@ -3312,15 +3312,15 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B99" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C99" s="2" t="n">
         <v>442</v>
@@ -3335,15 +3335,15 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B100" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C100" s="2" t="n">
         <v>442</v>
@@ -3358,15 +3358,15 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B101" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C101" s="2" t="n">
         <v>442</v>
@@ -3381,15 +3381,15 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B102" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C102" s="2" t="n">
         <v>442</v>
@@ -3404,15 +3404,15 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B103" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C103" s="2" t="n">
         <v>442</v>
@@ -3427,15 +3427,15 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B104" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C104" s="2" t="n">
         <v>442</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B105" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C105" s="2" t="n">
         <v>442</v>
@@ -3473,15 +3473,15 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B106" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C106" s="2" t="n">
         <v>442</v>
@@ -3496,6 +3496,29 @@
         <v>0</v>
       </c>
       <c r="G106" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B107" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7471,7 +7494,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-26 08:46（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-26 09:38（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 09:38（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 12:31（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46291.40186751157</v>
+        <v>46291.52177836806</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46291.40069444444</v>
+        <v>46291.52083333334</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
@@ -1104,15 +1104,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>188.1</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46291.36540915509</v>
+        <v>46291.40186751157</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46291.36458333334</v>
+        <v>46291.40069444444</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
@@ -1127,15 +1127,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>163.5</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46291.26887001158</v>
+        <v>46291.36540915509</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46291.26805555556</v>
+        <v>46291.36458333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
@@ -1150,15 +1150,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>184.5</v>
+        <v>163.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46291.2560487963</v>
+        <v>46291.26887001158</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46291.25486111111</v>
+        <v>46291.26805555556</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
@@ -1173,84 +1173,84 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>191.6</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46291.11246790509</v>
+        <v>46291.2560487963</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46291.11111111111</v>
+        <v>46291.25486111111</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>182.3</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46291.02308788194</v>
+        <v>46291.11246790509</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46291.02222222222</v>
+        <v>46291.11111111111</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>140.5</v>
+        <v>182.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46290.9990443287</v>
+        <v>46291.02308788194</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46290.99791666667</v>
+        <v>46291.02222222222</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>197.5</v>
+        <v>140.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46290.91267655093</v>
+        <v>46290.9990443287</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46290.91180555556</v>
+        <v>46290.99791666667</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
@@ -1265,38 +1265,38 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>193.4</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46290.82088560185</v>
+        <v>46290.91267655093</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46290.82013888889</v>
+        <v>46290.91180555556</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>174.9</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46290.76820827546</v>
+        <v>46290.82088560185</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46290.76736111111</v>
+        <v>46290.82013888889</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
@@ -1305,27 +1305,27 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>187</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46290.709303125</v>
+        <v>46290.76820827546</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46290.70833333334</v>
+        <v>46290.76736111111</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1</v>
@@ -1334,15 +1334,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>187.6</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46290.66382769676</v>
+        <v>46290.709303125</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46290.6625</v>
+        <v>46290.70833333334</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
@@ -1351,67 +1351,67 @@
         <v>1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>185.1</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46290.61757802084</v>
+        <v>46290.66382769676</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46290.61666666667</v>
+        <v>46290.6625</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>178.9</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
@@ -1420,90 +1420,90 @@
         <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
@@ -1512,73 +1512,73 @@
         <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
@@ -1587,21 +1587,21 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>0</v>
@@ -1610,61 +1610,61 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D26" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>433</v>
@@ -1673,44 +1673,44 @@
         <v>3</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>433</v>
@@ -1725,15 +1725,15 @@
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>433</v>
@@ -1748,15 +1748,15 @@
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>433</v>
@@ -1771,15 +1771,15 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>433</v>
@@ -1794,15 +1794,15 @@
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>433</v>
@@ -1817,15 +1817,15 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>433</v>
@@ -1837,18 +1837,18 @@
         <v>0</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>433</v>
@@ -1863,15 +1863,15 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>433</v>
@@ -1886,15 +1886,15 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>433</v>
@@ -1909,18 +1909,18 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>0</v>
@@ -1932,15 +1932,15 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>441</v>
@@ -1955,15 +1955,15 @@
         <v>2</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>441</v>
@@ -1978,15 +1978,15 @@
         <v>2</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>441</v>
@@ -2001,18 +2001,18 @@
         <v>2</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>0</v>
@@ -2021,18 +2021,18 @@
         <v>0</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>440</v>
@@ -2047,15 +2047,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>440</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>440</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>440</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>440</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>440</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>440</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>440</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>440</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>440</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>440</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>440</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>440</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>440</v>
@@ -3059,18 +3059,18 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>0</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>442</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,15 +3197,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3220,15 +3220,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>442</v>
@@ -3243,15 +3243,15 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>442</v>
@@ -3266,15 +3266,15 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B97" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C97" s="2" t="n">
         <v>442</v>
@@ -3289,15 +3289,15 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B98" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C98" s="2" t="n">
         <v>442</v>
@@ -3312,15 +3312,15 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B99" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C99" s="2" t="n">
         <v>442</v>
@@ -3335,15 +3335,15 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B100" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C100" s="2" t="n">
         <v>442</v>
@@ -3358,15 +3358,15 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B101" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C101" s="2" t="n">
         <v>442</v>
@@ -3381,15 +3381,15 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B102" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C102" s="2" t="n">
         <v>442</v>
@@ -3404,15 +3404,15 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B103" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C103" s="2" t="n">
         <v>442</v>
@@ -3427,15 +3427,15 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B104" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C104" s="2" t="n">
         <v>442</v>
@@ -3450,15 +3450,15 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B105" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C105" s="2" t="n">
         <v>442</v>
@@ -3478,10 +3478,10 @@
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B106" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C106" s="2" t="n">
         <v>442</v>
@@ -3496,15 +3496,15 @@
         <v>0</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B107" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C107" s="2" t="n">
         <v>442</v>
@@ -3519,6 +3519,29 @@
         <v>0</v>
       </c>
       <c r="G107" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B108" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7494,7 +7517,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-26 09:38（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-26 12:31（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 12:31（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 14:05（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46291.52177836806</v>
+        <v>46291.58748165509</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46291.52083333334</v>
+        <v>46291.58611111111</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
@@ -1104,15 +1104,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>187.5</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46291.40186751157</v>
+        <v>46291.52177836806</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46291.40069444444</v>
+        <v>46291.52083333334</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
@@ -1127,15 +1127,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>188.1</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46291.36540915509</v>
+        <v>46291.40186751157</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46291.36458333334</v>
+        <v>46291.40069444444</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
@@ -1150,15 +1150,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>163.5</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46291.26887001158</v>
+        <v>46291.36540915509</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46291.26805555556</v>
+        <v>46291.36458333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
@@ -1173,15 +1173,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>184.5</v>
+        <v>163.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46291.2560487963</v>
+        <v>46291.26887001158</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46291.25486111111</v>
+        <v>46291.26805555556</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
@@ -1196,84 +1196,84 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>191.6</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46291.11246790509</v>
+        <v>46291.2560487963</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46291.11111111111</v>
+        <v>46291.25486111111</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>182.3</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46291.02308788194</v>
+        <v>46291.11246790509</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46291.02222222222</v>
+        <v>46291.11111111111</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>140.5</v>
+        <v>182.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46290.9990443287</v>
+        <v>46291.02308788194</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46290.99791666667</v>
+        <v>46291.02222222222</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>197.5</v>
+        <v>140.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46290.91267655093</v>
+        <v>46290.9990443287</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46290.91180555556</v>
+        <v>46290.99791666667</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
@@ -1288,38 +1288,38 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>193.4</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46290.82088560185</v>
+        <v>46290.91267655093</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46290.82013888889</v>
+        <v>46290.91180555556</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>174.9</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46290.76820827546</v>
+        <v>46290.82088560185</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46290.76736111111</v>
+        <v>46290.82013888889</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
@@ -1328,27 +1328,27 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>187</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46290.709303125</v>
+        <v>46290.76820827546</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46290.70833333334</v>
+        <v>46290.76736111111</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1</v>
@@ -1357,15 +1357,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>187.6</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46290.66382769676</v>
+        <v>46290.709303125</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46290.6625</v>
+        <v>46290.70833333334</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
@@ -1374,67 +1374,67 @@
         <v>1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>185.1</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46290.61757802084</v>
+        <v>46290.66382769676</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46290.61666666667</v>
+        <v>46290.6625</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>178.9</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
@@ -1443,90 +1443,90 @@
         <v>1</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
@@ -1535,73 +1535,73 @@
         <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>0</v>
@@ -1610,21 +1610,21 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -1633,61 +1633,61 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>433</v>
@@ -1696,44 +1696,44 @@
         <v>3</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>433</v>
@@ -1748,15 +1748,15 @@
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>433</v>
@@ -1771,15 +1771,15 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>433</v>
@@ -1794,15 +1794,15 @@
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>433</v>
@@ -1817,15 +1817,15 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>433</v>
@@ -1840,15 +1840,15 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>433</v>
@@ -1860,18 +1860,18 @@
         <v>0</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>433</v>
@@ -1886,15 +1886,15 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>433</v>
@@ -1909,15 +1909,15 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>433</v>
@@ -1932,18 +1932,18 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>0</v>
@@ -1955,15 +1955,15 @@
         <v>2</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>441</v>
@@ -1978,15 +1978,15 @@
         <v>2</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>441</v>
@@ -2001,15 +2001,15 @@
         <v>2</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>441</v>
@@ -2024,18 +2024,18 @@
         <v>2</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>0</v>
@@ -2044,18 +2044,18 @@
         <v>0</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>440</v>
@@ -2070,15 +2070,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>440</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>440</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>440</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>440</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>440</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>440</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>440</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>440</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>440</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>440</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>440</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>440</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>440</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>440</v>
@@ -3082,18 +3082,18 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>0</v>
@@ -3105,15 +3105,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C90" s="2" t="n">
         <v>442</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,15 +3197,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3220,15 +3220,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>442</v>
@@ -3243,15 +3243,15 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>442</v>
@@ -3266,15 +3266,15 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B97" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C97" s="2" t="n">
         <v>442</v>
@@ -3289,15 +3289,15 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B98" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C98" s="2" t="n">
         <v>442</v>
@@ -3312,15 +3312,15 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B99" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C99" s="2" t="n">
         <v>442</v>
@@ -3335,15 +3335,15 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B100" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C100" s="2" t="n">
         <v>442</v>
@@ -3358,15 +3358,15 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B101" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C101" s="2" t="n">
         <v>442</v>
@@ -3381,15 +3381,15 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B102" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C102" s="2" t="n">
         <v>442</v>
@@ -3404,15 +3404,15 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B103" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C103" s="2" t="n">
         <v>442</v>
@@ -3427,15 +3427,15 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B104" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C104" s="2" t="n">
         <v>442</v>
@@ -3450,15 +3450,15 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B105" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C105" s="2" t="n">
         <v>442</v>
@@ -3473,15 +3473,15 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B106" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C106" s="2" t="n">
         <v>442</v>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B107" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C107" s="2" t="n">
         <v>442</v>
@@ -3519,15 +3519,15 @@
         <v>0</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B108" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C108" s="2" t="n">
         <v>442</v>
@@ -3542,6 +3542,29 @@
         <v>0</v>
       </c>
       <c r="G108" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B109" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7517,7 +7540,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-26 12:31（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-26 14:05（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -17,9 +17,9 @@
     <sheet name="掃描清單" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'資金明細'!$A$1:$Z$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'交易明細'!$A$1:$AH$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'幣種統計'!$A$1:$L$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'掃描清單'!$A$1:$H$434</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -281,7 +281,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'資金明細'!$R$2:$R$36</f>
+              <f>'資金明細'!$R$2:$R$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 14:05（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 15:09（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="2">
@@ -796,19 +796,19 @@
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -816,35 +816,35 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$18,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$20,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$J$2:$J$18,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$J$2:$J$20,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$J$2:$J$18,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$J$2:$J$20,"止損"),0)</f>
         <v/>
       </c>
       <c r="O5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$J$2:$J$18,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$J$2:$J$20,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P5" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$18,"&lt;&gt;未平倉",交易明細!$L$2:$L$18,"&gt;0")/C5,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$J$2:$J$20,"&lt;&gt;未平倉",交易明細!$L$2:$L$20,"&gt;0")/C5,0)</f>
         <v/>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$18,"做多",交易明細!$B$2:$B$18,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$20,"做多",交易明細!$B$2:$B$20,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="2">
@@ -863,19 +863,19 @@
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$20,"做多",交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$20,"做多",交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$20,"做多",交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$20,"做多",交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -883,35 +883,35 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$18,交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$20,交易明細!$C$2:$C$20,"做多",交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$C$2:$C$20,"做多",交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$C$2:$C$20,"做多",交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$C$2:$C$20,"做多",交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$C$2:$C$20,"做多",交易明細!$J$2:$J$20,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$C$2:$C$20,"做多",交易明細!$J$2:$J$20,"止損"),0)</f>
         <v/>
       </c>
       <c r="O6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$C$2:$C$20,"做多",交易明細!$J$2:$J$20,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P6" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$18,"做多",交易明細!$J$2:$J$18,"&lt;&gt;未平倉",交易明細!$L$2:$L$18,"&gt;0")/C6,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$20,"做多",交易明細!$J$2:$J$20,"&lt;&gt;未平倉",交易明細!$L$2:$L$20,"&gt;0")/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$18,"做空",交易明細!$B$2:$B$18,"&lt;&gt;")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$20,"做空",交易明細!$B$2:$B$20,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="2">
@@ -930,19 +930,19 @@
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$20,"做空",交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$20,"做空",交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$20,"做空",交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$C$2:$C$20,"做空",交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -950,35 +950,35 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$18,交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),參數!$B$16)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$AC$2:$AC$20,交易明細!$C$2:$C$20,"做空",交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),參數!$B$16)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$C$2:$C$20,"做空",交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="K7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$C$2:$C$20,"做空",交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$C$2:$C$20,"做空",交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"止盈"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$C$2:$C$20,"做空",交易明細!$J$2:$J$20,"止盈"),0)</f>
         <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"止損"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$C$2:$C$20,"做空",交易明細!$J$2:$J$20,"止損"),0)</f>
         <v/>
       </c>
       <c r="O7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"時間出場"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$C$2:$C$20,"做空",交易明細!$J$2:$J$20,"時間出場"),0)</f>
         <v/>
       </c>
       <c r="P7" s="4">
-        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$18,"做空",交易明細!$J$2:$J$18,"&lt;&gt;未平倉",交易明細!$L$2:$L$18,"&gt;0")/C7,0)</f>
+        <f>IFERROR(COUNTIFS(交易明細!$C$2:$C$20,"做空",交易明細!$J$2:$J$20,"&lt;&gt;未平倉",交易明細!$L$2:$L$20,"&gt;0")/C7,0)</f>
         <v/>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,33 +1086,33 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46291.58748165509</v>
+        <v>46291.63155474537</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46291.58611111111</v>
+        <v>46291.63055555556</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>148</v>
+        <v>172.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46291.52177836806</v>
+        <v>46291.58748165509</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46291.52083333334</v>
+        <v>46291.58611111111</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
@@ -1127,15 +1127,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>187.5</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46291.40186751157</v>
+        <v>46291.52177836806</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46291.40069444444</v>
+        <v>46291.52083333334</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
@@ -1150,15 +1150,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>188.1</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46291.36540915509</v>
+        <v>46291.40186751157</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46291.36458333334</v>
+        <v>46291.40069444444</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
@@ -1173,15 +1173,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>163.5</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46291.26887001158</v>
+        <v>46291.36540915509</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46291.26805555556</v>
+        <v>46291.36458333334</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
@@ -1196,15 +1196,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>184.5</v>
+        <v>163.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46291.2560487963</v>
+        <v>46291.26887001158</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46291.25486111111</v>
+        <v>46291.26805555556</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
@@ -1219,84 +1219,84 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>191.6</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46291.11246790509</v>
+        <v>46291.2560487963</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46291.11111111111</v>
+        <v>46291.25486111111</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>182.3</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46291.02308788194</v>
+        <v>46291.11246790509</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46291.02222222222</v>
+        <v>46291.11111111111</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>140.5</v>
+        <v>182.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46290.9990443287</v>
+        <v>46291.02308788194</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46290.99791666667</v>
+        <v>46291.02222222222</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>197.5</v>
+        <v>140.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46290.91267655093</v>
+        <v>46290.9990443287</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46290.91180555556</v>
+        <v>46290.99791666667</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
@@ -1311,38 +1311,38 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>193.4</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46290.82088560185</v>
+        <v>46290.91267655093</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46290.82013888889</v>
+        <v>46290.91180555556</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>174.9</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46290.76820827546</v>
+        <v>46290.82088560185</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46290.76736111111</v>
+        <v>46290.82013888889</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>433</v>
@@ -1351,27 +1351,27 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>187</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46290.709303125</v>
+        <v>46290.76820827546</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>46290.70833333334</v>
+        <v>46290.76736111111</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1</v>
@@ -1380,15 +1380,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>187.6</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>46290.66382769676</v>
+        <v>46290.709303125</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>46290.6625</v>
+        <v>46290.70833333334</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>433</v>
@@ -1397,67 +1397,67 @@
         <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>185.1</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46290.61757802084</v>
+        <v>46290.66382769676</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>46290.61666666667</v>
+        <v>46290.6625</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>178.9</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>46290.55632820602</v>
+        <v>46290.61757802084</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>46290.55555555555</v>
+        <v>46290.61666666667</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>179.4</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>46290.50409561343</v>
+        <v>46290.55632820602</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46290.50277777778</v>
+        <v>46290.55555555555</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>433</v>
@@ -1466,90 +1466,90 @@
         <v>1</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>174.5</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>46290.39966920139</v>
+        <v>46290.50409561343</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>46290.39861111111</v>
+        <v>46290.50277777778</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>189.8</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>46290.3483633912</v>
+        <v>46290.39966920139</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>46290.34722222222</v>
+        <v>46290.39861111111</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>163.4</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>46290.27195019676</v>
+        <v>46290.3483633912</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>46290.27083333334</v>
+        <v>46290.34722222222</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>182.9</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>46290.13587655093</v>
+        <v>46290.27195019676</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>46290.13472222222</v>
+        <v>46290.27083333334</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>433</v>
@@ -1558,73 +1558,73 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>191.6</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>46290.02908936342</v>
+        <v>46290.13587655093</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>46290.02777777778</v>
+        <v>46290.13472222222</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>166.2</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>46289.96715996528</v>
+        <v>46290.02908936342</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>46289.96597222222</v>
+        <v>46290.02777777778</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>190.1</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>46289.95004011574</v>
+        <v>46289.96715996528</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>46289.94930555556</v>
+        <v>46289.96597222222</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -1633,21 +1633,21 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>178.4</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>46289.94135959491</v>
+        <v>46289.95004011574</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46289.94027777778</v>
+        <v>46289.94930555556</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>0</v>
@@ -1656,61 +1656,61 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>183.8</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>46289.92565313658</v>
+        <v>46289.94135959491</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>46289.92430555556</v>
+        <v>46289.94027777778</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>226.2</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>46289.84896370371</v>
+        <v>46289.92565313658</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>46289.84791666667</v>
+        <v>46289.92430555556</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>147.5</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>46289.78526427083</v>
+        <v>46289.84896370371</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>46289.78402777778</v>
+        <v>46289.84791666667</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>433</v>
@@ -1719,44 +1719,44 @@
         <v>3</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>186.8</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>46289.75543116898</v>
+        <v>46289.78526427083</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>46289.75</v>
+        <v>46289.78402777778</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>109.8</v>
+        <v>186.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>46289.54138961805</v>
+        <v>46289.75543116898</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>46289.53472222222</v>
+        <v>46289.75</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>433</v>
@@ -1771,15 +1771,15 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>125.8</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>46289.32358565972</v>
+        <v>46289.54138961805</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>46289.31944444445</v>
+        <v>46289.53472222222</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>433</v>
@@ -1794,15 +1794,15 @@
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>130.2</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>46289.18599210648</v>
+        <v>46289.32358565972</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>46289.18055555555</v>
+        <v>46289.31944444445</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>433</v>
@@ -1817,15 +1817,15 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>129.3</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>46289.04908521991</v>
+        <v>46289.18599210648</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>46289.04513888889</v>
+        <v>46289.18055555555</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>433</v>
@@ -1840,15 +1840,15 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>46289.00944646991</v>
+        <v>46289.04908521991</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>46289.00347222222</v>
+        <v>46289.04513888889</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>433</v>
@@ -1863,15 +1863,15 @@
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>127</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>46288.82408041666</v>
+        <v>46289.00944646991</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>46288.81944444445</v>
+        <v>46289.00347222222</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>433</v>
@@ -1883,18 +1883,18 @@
         <v>0</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>118.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>46288.75275025463</v>
+        <v>46288.82408041666</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>46288.74652777778</v>
+        <v>46288.81944444445</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>433</v>
@@ -1909,15 +1909,15 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>125.5</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>46288.58577883102</v>
+        <v>46288.75275025463</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>46288.57986111111</v>
+        <v>46288.74652777778</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>433</v>
@@ -1932,15 +1932,15 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>112.8</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>46288.57218969907</v>
+        <v>46288.58577883102</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>46288.56597222222</v>
+        <v>46288.57986111111</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>433</v>
@@ -1955,18 +1955,18 @@
         <v>2</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>99.7</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>46288.36332482639</v>
+        <v>46288.57218969907</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>46288.35763888889</v>
+        <v>46288.56597222222</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0</v>
@@ -1978,15 +1978,15 @@
         <v>2</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>46288.26120461806</v>
+        <v>46288.36332482639</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>46288.25694444445</v>
+        <v>46288.35763888889</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>441</v>
@@ -2001,15 +2001,15 @@
         <v>2</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>103.1</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>46288.12397528935</v>
+        <v>46288.26120461806</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>46288.11805555555</v>
+        <v>46288.25694444445</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>441</v>
@@ -2024,15 +2024,15 @@
         <v>2</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>114.4</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>46287.95840076389</v>
+        <v>46288.12397528935</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>46287.95486111111</v>
+        <v>46288.11805555555</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>441</v>
@@ -2047,18 +2047,18 @@
         <v>2</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>135.1</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>46287.75277884259</v>
+        <v>46287.95840076389</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>46287.74652777778</v>
+        <v>46287.95486111111</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>0</v>
@@ -2067,18 +2067,18 @@
         <v>0</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>130.3</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>46287.6758560301</v>
+        <v>46287.75277884259</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>46287.67013888889</v>
+        <v>46287.74652777778</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>440</v>
@@ -2093,15 +2093,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>91.7</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>46287.54602564815</v>
+        <v>46287.6758560301</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.67013888889</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>440</v>
@@ -2116,15 +2116,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>125.4</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>46287.51247143518</v>
+        <v>46287.54602564815</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46287.50694444445</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>440</v>
@@ -2139,15 +2139,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>102.8</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>46287.30635083334</v>
+        <v>46287.51247143518</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>46287.30208333334</v>
+        <v>46287.50694444445</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>440</v>
@@ -2162,15 +2162,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>135.9</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>46287.14961865741</v>
+        <v>46287.30635083334</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>46287.14583333334</v>
+        <v>46287.30208333334</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>440</v>
@@ -2185,15 +2185,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>130.5</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>46286.92852005787</v>
+        <v>46287.14961865741</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>46286.92361111111</v>
+        <v>46287.14583333334</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>440</v>
@@ -2208,15 +2208,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>112.2</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>46286.83222814815</v>
+        <v>46286.92852005787</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>46286.82638888889</v>
+        <v>46286.92361111111</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>440</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>126.4</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46286.60261268519</v>
+        <v>46286.83222814815</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>46286.59722222222</v>
+        <v>46286.82638888889</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>440</v>
@@ -2254,15 +2254,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>111.5</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>46286.38294268519</v>
+        <v>46286.60261268519</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>46286.37847222222</v>
+        <v>46286.59722222222</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>440</v>
@@ -2277,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46286.27148542824</v>
+        <v>46286.38294268519</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>46286.26736111111</v>
+        <v>46286.37847222222</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>440</v>
@@ -2300,15 +2300,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>126.7</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>46286.14641391204</v>
+        <v>46286.27148542824</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>46286.14236111111</v>
+        <v>46286.26736111111</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>440</v>
@@ -2323,15 +2323,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>131.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>46286.03573545139</v>
+        <v>46286.14641391204</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>46286.03125</v>
+        <v>46286.14236111111</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>440</v>
@@ -2346,15 +2346,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>127.3</v>
+        <v>131.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>46286.00283136574</v>
+        <v>46286.03573545139</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>46285.99652777778</v>
+        <v>46286.03125</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>440</v>
@@ -2369,15 +2369,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>101.9</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>46285.85245594908</v>
+        <v>46286.00283136574</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>46285.84722222222</v>
+        <v>46285.99652777778</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>440</v>
@@ -2392,15 +2392,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>100.6</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
-        <v>46285.60105145833</v>
+        <v>46285.85245594908</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>46285.59722222222</v>
+        <v>46285.84722222222</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>440</v>
@@ -2415,15 +2415,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>129.1</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>46285.38559789352</v>
+        <v>46285.60105145833</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>46285.38194444445</v>
+        <v>46285.59722222222</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>440</v>
@@ -2438,15 +2438,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>112.5</v>
+        <v>129.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>46285.29994834491</v>
+        <v>46285.38559789352</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>46285.29513888889</v>
+        <v>46285.38194444445</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>440</v>
@@ -2461,15 +2461,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>128.1</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>46285.19964518519</v>
+        <v>46285.29994834491</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>46285.19444444445</v>
+        <v>46285.29513888889</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>440</v>
@@ -2484,15 +2484,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>110.6</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>46285.08704527777</v>
+        <v>46285.19964518519</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>46285.08333333334</v>
+        <v>46285.19444444445</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>440</v>
@@ -2507,15 +2507,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>46284.93748335648</v>
+        <v>46285.08704527777</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>46284.93055555555</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>440</v>
@@ -2530,15 +2530,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>128.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>46284.79727659722</v>
+        <v>46284.93748335648</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>46284.79166666666</v>
+        <v>46284.93055555555</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>440</v>
@@ -2553,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>109.7</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>46284.58365538195</v>
+        <v>46284.79727659722</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>46284.57986111111</v>
+        <v>46284.79166666666</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>440</v>
@@ -2576,15 +2576,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>101.8</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>46284.38530752315</v>
+        <v>46284.58365538195</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>46284.37847222222</v>
+        <v>46284.57986111111</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>440</v>
@@ -2599,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>130.8</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>46284.27664920139</v>
+        <v>46284.38530752315</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>46284.27083333334</v>
+        <v>46284.37847222222</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>440</v>
@@ -2622,15 +2622,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>127.8</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>46284.15392047453</v>
+        <v>46284.27664920139</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>46284.14930555555</v>
+        <v>46284.27083333334</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>440</v>
@@ -2645,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>135.6</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>46284.02123533565</v>
+        <v>46284.15392047453</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>46284.01736111111</v>
+        <v>46284.14930555555</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>440</v>
@@ -2668,15 +2668,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>102.8</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>46283.99753837963</v>
+        <v>46284.02123533565</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>46283.99305555555</v>
+        <v>46284.01736111111</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>440</v>
@@ -2691,15 +2691,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>129.8</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>46283.80859936342</v>
+        <v>46283.99753837963</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>46283.80208333334</v>
+        <v>46283.99305555555</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>440</v>
@@ -2714,15 +2714,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>127.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>46283.78916202546</v>
+        <v>46283.80859936342</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>46283.78472222222</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>440</v>
@@ -2737,15 +2737,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>119.1</v>
+        <v>127.7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>46283.58323265046</v>
+        <v>46283.78916202546</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>46283.57638888889</v>
+        <v>46283.78472222222</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>440</v>
@@ -2760,15 +2760,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>126.7</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>46283.57323743056</v>
+        <v>46283.58323265046</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>46283.56944444445</v>
+        <v>46283.57638888889</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>440</v>
@@ -2783,15 +2783,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>94.3</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>46283.45181144676</v>
+        <v>46283.57323743056</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>46283.44791666666</v>
+        <v>46283.56944444445</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>440</v>
@@ -2806,15 +2806,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>132.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>46283.44134394676</v>
+        <v>46283.45181144676</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>46283.4375</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>440</v>
@@ -2829,15 +2829,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>373.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>46283.35273409722</v>
+        <v>46283.44134394676</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>46283.34722222222</v>
+        <v>46283.4375</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>440</v>
@@ -2852,15 +2852,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>132.3</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>46283.26014016203</v>
+        <v>46283.35273409722</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>46283.25347222222</v>
+        <v>46283.34722222222</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>440</v>
@@ -2875,15 +2875,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>129.5</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>46283.09637409722</v>
+        <v>46283.26014016203</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>46283.09027777778</v>
+        <v>46283.25347222222</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>440</v>
@@ -2898,15 +2898,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>131.2</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>46282.89824439815</v>
+        <v>46283.09637409722</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>46282.89236111111</v>
+        <v>46283.09027777778</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>440</v>
@@ -2921,15 +2921,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>137</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>46282.65711792824</v>
+        <v>46282.89824439815</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>46282.65277777778</v>
+        <v>46282.89236111111</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>440</v>
@@ -2944,15 +2944,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>126.6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>46282.40350203704</v>
+        <v>46282.65711792824</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>46282.39930555555</v>
+        <v>46282.65277777778</v>
       </c>
       <c r="C83" s="2" t="n">
         <v>440</v>
@@ -2967,15 +2967,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>323.7</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>46282.39577758102</v>
+        <v>46282.40350203704</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>46282.33333333334</v>
+        <v>46282.39930555555</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>440</v>
@@ -2990,15 +2990,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>50.5</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>46282.29222982639</v>
+        <v>46282.39577758102</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>46282.25</v>
+        <v>46282.33333333334</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>440</v>
@@ -3013,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>46282.17576607639</v>
+        <v>46282.29222982639</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>46282.125</v>
+        <v>46282.25</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>440</v>
@@ -3036,15 +3036,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>46282.04552453704</v>
+        <v>46282.17576607639</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>46282</v>
+        <v>46282.125</v>
       </c>
       <c r="C87" s="2" t="n">
         <v>440</v>
@@ -3059,15 +3059,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>52.9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>46281.82298537037</v>
+        <v>46282.04552453704</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>46281.75</v>
+        <v>46282</v>
       </c>
       <c r="C88" s="2" t="n">
         <v>440</v>
@@ -3082,15 +3082,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>65.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>46281.58829054398</v>
+        <v>46281.82298537037</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>46281.54166666666</v>
+        <v>46281.75</v>
       </c>
       <c r="C89" s="2" t="n">
         <v>440</v>
@@ -3105,18 +3105,18 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>54.5</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>46281.35205523148</v>
+        <v>46281.58829054398</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>46281.29166666666</v>
+        <v>46281.54166666666</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>0</v>
@@ -3128,15 +3128,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>46281.22963460648</v>
+        <v>46281.35205523148</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>46281.16666666666</v>
+        <v>46281.29166666666</v>
       </c>
       <c r="C91" s="2" t="n">
         <v>442</v>
@@ -3151,15 +3151,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>61.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>46281.094529375</v>
+        <v>46281.22963460648</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>46281.04166666666</v>
+        <v>46281.16666666666</v>
       </c>
       <c r="C92" s="2" t="n">
         <v>442</v>
@@ -3174,15 +3174,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>46.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>46280.9017994676</v>
+        <v>46281.094529375</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>46280.83333333334</v>
+        <v>46281.04166666666</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>442</v>
@@ -3197,15 +3197,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>56.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>46280.66002480324</v>
+        <v>46280.9017994676</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>46280.58333333334</v>
+        <v>46280.83333333334</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>442</v>
@@ -3220,15 +3220,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>46280.4778358449</v>
+        <v>46280.66002480324</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>46280.41666666666</v>
+        <v>46280.58333333334</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>442</v>
@@ -3243,15 +3243,15 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>61.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>46280.39795681713</v>
+        <v>46280.4778358449</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>46280.33333333334</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="C96" s="2" t="n">
         <v>442</v>
@@ -3266,15 +3266,15 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>46280.29983445602</v>
+        <v>46280.39795681713</v>
       </c>
       <c r="B97" s="7" t="n">
-        <v>46280.25</v>
+        <v>46280.33333333334</v>
       </c>
       <c r="C97" s="2" t="n">
         <v>442</v>
@@ -3289,15 +3289,15 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>51.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>46280.14350143519</v>
+        <v>46280.29983445602</v>
       </c>
       <c r="B98" s="7" t="n">
-        <v>46280.08333333334</v>
+        <v>46280.25</v>
       </c>
       <c r="C98" s="2" t="n">
         <v>442</v>
@@ -3312,15 +3312,15 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>57.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>46279.92418226852</v>
+        <v>46280.14350143519</v>
       </c>
       <c r="B99" s="7" t="n">
-        <v>46279.875</v>
+        <v>46280.08333333334</v>
       </c>
       <c r="C99" s="2" t="n">
         <v>442</v>
@@ -3335,15 +3335,15 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>46279.59996445602</v>
+        <v>46279.92418226852</v>
       </c>
       <c r="B100" s="7" t="n">
-        <v>46279.54166666666</v>
+        <v>46279.875</v>
       </c>
       <c r="C100" s="2" t="n">
         <v>442</v>
@@ -3358,15 +3358,15 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>61</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
-        <v>46279.38316741898</v>
+        <v>46279.59996445602</v>
       </c>
       <c r="B101" s="7" t="n">
-        <v>46279.33333333334</v>
+        <v>46279.54166666666</v>
       </c>
       <c r="C101" s="2" t="n">
         <v>442</v>
@@ -3381,15 +3381,15 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>46279.26932584491</v>
+        <v>46279.38316741898</v>
       </c>
       <c r="B102" s="7" t="n">
-        <v>46279.20833333334</v>
+        <v>46279.33333333334</v>
       </c>
       <c r="C102" s="2" t="n">
         <v>442</v>
@@ -3404,15 +3404,15 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>61.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
-        <v>46279.14665413195</v>
+        <v>46279.26932584491</v>
       </c>
       <c r="B103" s="7" t="n">
-        <v>46279.08333333334</v>
+        <v>46279.20833333334</v>
       </c>
       <c r="C103" s="2" t="n">
         <v>442</v>
@@ -3427,15 +3427,15 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>46279.01733591435</v>
+        <v>46279.14665413195</v>
       </c>
       <c r="B104" s="7" t="n">
-        <v>46278.95833333334</v>
+        <v>46279.08333333334</v>
       </c>
       <c r="C104" s="2" t="n">
         <v>442</v>
@@ -3450,15 +3450,15 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>59.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
-        <v>46278.83725055555</v>
+        <v>46279.01733591435</v>
       </c>
       <c r="B105" s="7" t="n">
-        <v>46278.79166666666</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="C105" s="2" t="n">
         <v>442</v>
@@ -3473,15 +3473,15 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
-        <v>46278.71111972223</v>
+        <v>46278.83725055555</v>
       </c>
       <c r="B106" s="7" t="n">
-        <v>46278.66666666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="C106" s="2" t="n">
         <v>442</v>
@@ -3496,15 +3496,15 @@
         <v>0</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
-        <v>46278.68053923611</v>
+        <v>46278.71111972223</v>
       </c>
       <c r="B107" s="7" t="n">
-        <v>46278.625</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="C107" s="2" t="n">
         <v>442</v>
@@ -3524,10 +3524,10 @@
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
-        <v>46278.07354997685</v>
+        <v>46278.68053923611</v>
       </c>
       <c r="B108" s="7" t="n">
-        <v>46278</v>
+        <v>46278.625</v>
       </c>
       <c r="C108" s="2" t="n">
         <v>442</v>
@@ -3542,15 +3542,15 @@
         <v>0</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>50.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
-        <v>46277.94390239583</v>
+        <v>46278.07354997685</v>
       </c>
       <c r="B109" s="7" t="n">
-        <v>46277.875</v>
+        <v>46278</v>
       </c>
       <c r="C109" s="2" t="n">
         <v>442</v>
@@ -3565,6 +3565,29 @@
         <v>0</v>
       </c>
       <c r="G109" s="2" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="n">
+        <v>46277.94390239583</v>
+      </c>
+      <c r="B110" s="7" t="n">
+        <v>46277.875</v>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="2" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3630,7 +3653,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <f>資金明細!R36</f>
+        <f>資金明細!R39</f>
         <v/>
       </c>
     </row>
@@ -3668,7 +3691,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>MAX(資金明細!$R$2:$R$36)</f>
+        <f>MAX(資金明細!$R$2:$R$39)</f>
         <v/>
       </c>
     </row>
@@ -3687,7 +3710,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <f>MIN(資金明細!$R$2:$R$36)</f>
+        <f>MIN(資金明細!$R$2:$R$39)</f>
         <v/>
       </c>
     </row>
@@ -3707,7 +3730,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>MIN(資金明細!$X$2:$X$36)</f>
+        <f>MIN(資金明細!$X$2:$X$39)</f>
         <v/>
       </c>
     </row>
@@ -3726,7 +3749,7 @@
         </is>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$36,"進場",資金明細!$N$2:$N$36,"已下單")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$39,"進場",資金明細!$N$2:$N$39,"已下單")</f>
         <v/>
       </c>
     </row>
@@ -3745,7 +3768,7 @@
         </is>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$36,"進場",資金明細!$N$2:$N$36,"資金不足略過")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$39,"進場",資金明細!$N$2:$N$39,"資金不足略過")</f>
         <v/>
       </c>
     </row>
@@ -3756,7 +3779,7 @@
         </is>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$36,"出場",資金明細!$N$2:$N$36,"已下單",資金明細!$K$2:$K$36,"止盈")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$39,"出場",資金明細!$N$2:$N$39,"已下單",資金明細!$K$2:$K$39,"止盈")</f>
         <v/>
       </c>
     </row>
@@ -3767,7 +3790,7 @@
         </is>
       </c>
       <c r="B12" s="4">
-        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$18),參數!B6)</f>
+        <f>B5*B7*IFERROR(AVERAGE(交易明細!$AB$2:$AB$20),參數!B6)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3776,7 +3799,7 @@
         </is>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$36,"出場",資金明細!$N$2:$N$36,"已下單",資金明細!$K$2:$K$36,"止損")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$39,"出場",資金明細!$N$2:$N$39,"已下單",資金明細!$K$2:$K$39,"止損")</f>
         <v/>
       </c>
     </row>
@@ -3792,7 +3815,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$36,"出場",資金明細!$N$2:$N$36,"已下單"),0)</f>
+        <f>IFERROR(E11/COUNTIFS(資金明細!$C$2:$C$39,"出場",資金明細!$N$2:$N$39,"已下單"),0)</f>
         <v/>
       </c>
     </row>
@@ -3808,7 +3831,7 @@
         </is>
       </c>
       <c r="E14" s="15">
-        <f>MAX(資金明細!$U$2:$U$36)</f>
+        <f>MAX(資金明細!$U$2:$U$39)</f>
         <v/>
       </c>
     </row>
@@ -3824,7 +3847,7 @@
         </is>
       </c>
       <c r="E15" s="16">
-        <f>MAX(資金明細!$S$2:$S$36)</f>
+        <f>MAX(資金明細!$S$2:$S$39)</f>
         <v/>
       </c>
     </row>
@@ -3835,7 +3858,7 @@
         </is>
       </c>
       <c r="E16" s="16">
-        <f>B5*資金明細!V36</f>
+        <f>B5*資金明細!V39</f>
         <v/>
       </c>
     </row>
@@ -3846,7 +3869,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <f>0</f>
+        <f>IF(資金明細!N39="已下單",資金明細!O39*交易明細!L20,0)</f>
         <v/>
       </c>
     </row>
@@ -3857,7 +3880,7 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>MAX(資金明細!$Y$2:$Y$36)</f>
+        <f>MAX(資金明細!$Y$2:$Y$39)</f>
         <v/>
       </c>
     </row>
@@ -3879,7 +3902,7 @@
         </is>
       </c>
       <c r="E20" s="7">
-        <f>IFERROR(INDEX(資金明細!$B$2:$B$36,MATCH(1,資金明細!$Z$2:$Z$36,0)),"未觸發")</f>
+        <f>IFERROR(INDEX(資金明細!$B$2:$B$39,MATCH(1,資金明細!$Z$2:$Z$39,0)),"未觸發")</f>
         <v/>
       </c>
     </row>
@@ -3890,7 +3913,7 @@
         </is>
       </c>
       <c r="E21" s="15">
-        <f>COUNTIFS(資金明細!$C$2:$C$36,"進場",資金明細!$N$2:$N$36,"已停止")</f>
+        <f>COUNTIFS(資金明細!$C$2:$C$39,"進場",資金明細!$N$2:$N$39,"已停止")</f>
         <v/>
       </c>
     </row>
@@ -3955,7 +3978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7457,9 +7480,296 @@
         <v/>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>46291.59166666667</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2Z_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="n">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>0.06119729999999999</v>
+      </c>
+      <c r="I37" s="17" t="n">
+        <v>0.0662445</v>
+      </c>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="16">
+        <f>資金模擬!$B$5*V36</f>
+        <v/>
+      </c>
+      <c r="N37" s="2">
+        <f>IF(Z36=1,"已停止",IF(T36&gt;=M37,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O37" s="16">
+        <f>IF(N37="已下單",M37*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P37" s="4" t="n"/>
+      <c r="Q37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="10">
+        <f>R36+Q37</f>
+        <v/>
+      </c>
+      <c r="S37" s="16">
+        <f>S36+IF(N37="已下單",M37,0)</f>
+        <v/>
+      </c>
+      <c r="T37" s="16">
+        <f>R37-S37</f>
+        <v/>
+      </c>
+      <c r="U37" s="2">
+        <f>U36+IF(N37="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V37" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R37,0),MAX(V36,FLOOR(MAX(R37,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W37" s="10">
+        <f>MAX(W36,R37)</f>
+        <v/>
+      </c>
+      <c r="X37" s="4">
+        <f>IF(W37&gt;0,R37/W37-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y37" s="16">
+        <f>IF(R37&gt;0,S37*資金模擬!$B$7/R37,0)</f>
+        <v/>
+      </c>
+      <c r="Z37" s="2">
+        <f>IF(OR(Z36=1,R37&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>46291.59513888889</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>出場</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>2Z_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="H38" s="17" t="n">
+        <v>0.06119729999999999</v>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>0.0662445</v>
+      </c>
+      <c r="J38" s="17" t="n">
+        <v>0.0662445</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="L38" s="5">
+        <f>交易明細!K19</f>
+        <v/>
+      </c>
+      <c r="M38" s="16">
+        <f>M37</f>
+        <v/>
+      </c>
+      <c r="N38" s="2">
+        <f>N37</f>
+        <v/>
+      </c>
+      <c r="O38" s="16">
+        <f>O37</f>
+        <v/>
+      </c>
+      <c r="P38" s="4">
+        <f>交易明細!L19</f>
+        <v/>
+      </c>
+      <c r="Q38" s="10">
+        <f>IF(N38="已下單",O38*P38,0)</f>
+        <v/>
+      </c>
+      <c r="R38" s="10">
+        <f>R37+Q38</f>
+        <v/>
+      </c>
+      <c r="S38" s="16">
+        <f>S37-IF(N38="已下單",M38,0)</f>
+        <v/>
+      </c>
+      <c r="T38" s="16">
+        <f>R38-S38</f>
+        <v/>
+      </c>
+      <c r="U38" s="2">
+        <f>U37-IF(N38="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V38" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R38,0),MAX(V37,FLOOR(MAX(R38,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W38" s="10">
+        <f>MAX(W37,R38)</f>
+        <v/>
+      </c>
+      <c r="X38" s="4">
+        <f>IF(W38&gt;0,R38/W38-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y38" s="16">
+        <f>IF(R38&gt;0,S38*資金模擬!$B$7/R38,0)</f>
+        <v/>
+      </c>
+      <c r="Z38" s="2">
+        <f>IF(OR(Z37=1,R38&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>46291.62777777778</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Q_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="n">
+        <v>0.03002</v>
+      </c>
+      <c r="H39" s="17" t="n">
+        <v>0.0291194</v>
+      </c>
+      <c r="I39" s="17" t="n">
+        <v>0.031521</v>
+      </c>
+      <c r="J39" s="17" t="n"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="16">
+        <f>資金模擬!$B$5*V38</f>
+        <v/>
+      </c>
+      <c r="N39" s="2">
+        <f>IF(Z38=1,"已停止",IF(T38&gt;=M39,"已下單","資金不足略過"))</f>
+        <v/>
+      </c>
+      <c r="O39" s="16">
+        <f>IF(N39="已下單",M39*資金模擬!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="P39" s="4" t="n"/>
+      <c r="Q39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="10">
+        <f>R38+Q39</f>
+        <v/>
+      </c>
+      <c r="S39" s="16">
+        <f>S38+IF(N39="已下單",M39,0)</f>
+        <v/>
+      </c>
+      <c r="T39" s="16">
+        <f>R39-S39</f>
+        <v/>
+      </c>
+      <c r="U39" s="2">
+        <f>U38+IF(N39="已下單",1,0)</f>
+        <v/>
+      </c>
+      <c r="V39" s="16">
+        <f>IF(資金模擬!$B$9=2,MAX(R39,0),MAX(V38,FLOOR(MAX(R39,0),資金模擬!$B$6)))</f>
+        <v/>
+      </c>
+      <c r="W39" s="10">
+        <f>MAX(W38,R39)</f>
+        <v/>
+      </c>
+      <c r="X39" s="4">
+        <f>IF(W39&gt;0,R39/W39-1,-1)</f>
+        <v/>
+      </c>
+      <c r="Y39" s="16">
+        <f>IF(R39&gt;0,S39*資金模擬!$B$7/R39,0)</f>
+        <v/>
+      </c>
+      <c r="Z39" s="2">
+        <f>IF(OR(Z38=1,R39&lt;=資金模擬!$B$10),1,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z36"/>
-  <conditionalFormatting sqref="K2:K36">
+  <autoFilter ref="A1:Z39"/>
+  <conditionalFormatting sqref="K2:K39">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -7467,7 +7777,7 @@
       <formula>"止損"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N36">
+  <conditionalFormatting sqref="N2:N39">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"資金不足略過"</formula>
     </cfRule>
@@ -7475,7 +7785,7 @@
       <formula>"已停止"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q36">
+  <conditionalFormatting sqref="Q2:Q39">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -7540,7 +7850,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 00:00 ~ 2026-09-26 14:05（Dry Run）</t>
+          <t>2026-09-01 00:00 ~ 2026-09-26 15:09（Dry Run）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -7750,7 +8060,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$18),(B6+2*B7)/(B5+B6))</f>
+        <f>IFERROR(AVERAGE(交易明細!$AC$2:$AC$20),(B6+2*B7)/(B5+B6))</f>
         <v/>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7776,7 +8086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH18"/>
+  <dimension ref="A1:AH20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9534,9 +9844,195 @@
         <v>12</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2Z_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>46291.59166666667</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>0.06119729999999999</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>0.0662445</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>46291.59513888889</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>0.0662445</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>止損</t>
+        </is>
+      </c>
+      <c r="K19" s="5">
+        <f>(H19-D19)*24</f>
+        <v/>
+      </c>
+      <c r="L19" s="4">
+        <f>IF(C19="做多",I19/E19-1,1-I19/E19)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="19" t="n"/>
+      <c r="R19" s="19" t="n"/>
+      <c r="S19" s="4" t="n">
+        <v>0.005547630369313494</v>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U19" s="16" t="n"/>
+      <c r="V19" s="16" t="n"/>
+      <c r="W19" s="4" t="n"/>
+      <c r="X19" s="4" t="n"/>
+      <c r="Y19" s="4" t="n"/>
+      <c r="Z19" s="4" t="n"/>
+      <c r="AA19" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB19" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC19" s="4">
+        <f>(AB19+2*參數!$B$7)/(AA19+AB19)</f>
+        <v/>
+      </c>
+      <c r="AD19" s="2" t="n">
+        <v>0.06901974488904417</v>
+      </c>
+      <c r="AE19" s="2" t="n">
+        <v>0.5078436752773313</v>
+      </c>
+      <c r="AF19" s="2" t="inlineStr">
+        <is>
+          <t>15分0.5倍</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="n">
+        <v>0.03071393563143276</v>
+      </c>
+      <c r="AH19" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Q_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>做空</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>46291.62777777778</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0.03002</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>0.0291194</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>0.031521</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>46291.63125</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>0.03044</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>未平倉</t>
+        </is>
+      </c>
+      <c r="K20" s="5">
+        <f>(H20-D20)*24</f>
+        <v/>
+      </c>
+      <c r="L20" s="4">
+        <f>IF(C20="做多",I20/E20-1,1-I20/E20)-2*參數!$B$7</f>
+        <v/>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>持倉中（以最新收盤估值）</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="19" t="n"/>
+      <c r="R20" s="19" t="n"/>
+      <c r="S20" s="4" t="n">
+        <v>0.01395736175882756</v>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>0.01475682878081286</v>
+      </c>
+      <c r="U20" s="16" t="n"/>
+      <c r="V20" s="16" t="n"/>
+      <c r="W20" s="4" t="n"/>
+      <c r="X20" s="4" t="n"/>
+      <c r="Y20" s="4" t="n"/>
+      <c r="Z20" s="4" t="n"/>
+      <c r="AA20" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB20" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AC20" s="4">
+        <f>(AB20+2*參數!$B$7)/(AA20+AB20)</f>
+        <v/>
+      </c>
+      <c r="AD20" s="2" t="n">
+        <v>0.1789825630607753</v>
+      </c>
+      <c r="AE20" s="2" t="n">
+        <v>0.6712558597342427</v>
+      </c>
+      <c r="AF20" s="2" t="inlineStr">
+        <is>
+          <t>15分0.5倍</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="n">
+        <v>0.0553329114814034</v>
+      </c>
+      <c r="AH20" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AH18"/>
-  <conditionalFormatting sqref="J2:J18">
+  <autoFilter ref="A1:AH20"/>
+  <conditionalFormatting sqref="J2:J20">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"止盈"</formula>
     </cfRule>
@@ -9557,7 +10053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9643,27 +10139,27 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A2)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A2,交易明細!$C$2:$C$18,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A2,交易明細!$C$2:$C$20,"做多")</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A2,交易明細!$C$2:$C$18,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A2,交易明細!$C$2:$C$20,"做空")</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$18,$A2,交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>F2+G2+COUNTIFS(交易明細!$B$2:$B$20,$A2,交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="F2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A2,交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A2,交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="G2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A2,交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A2,交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="H2" s="4">
@@ -9671,19 +10167,19 @@
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A2,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A2,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A2,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A2,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K2" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A2,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A2,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L2" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A2,交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A2,交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -9694,27 +10190,27 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A3)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A3,交易明細!$C$2:$C$18,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A3,交易明細!$C$2:$C$20,"做多")</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A3,交易明細!$C$2:$C$18,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A3,交易明細!$C$2:$C$20,"做空")</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$18,$A3,交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>F3+G3+COUNTIFS(交易明細!$B$2:$B$20,$A3,交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="F3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A3,交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A3,交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="G3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A3,交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A3,交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="H3" s="4">
@@ -9722,19 +10218,19 @@
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A3,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A3,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A3,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A3,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K3" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A3,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A3,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L3" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A3,交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A3,交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -9745,27 +10241,27 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A4)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A4,交易明細!$C$2:$C$18,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A4,交易明細!$C$2:$C$20,"做多")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A4,交易明細!$C$2:$C$18,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A4,交易明細!$C$2:$C$20,"做空")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$18,$A4,交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>F4+G4+COUNTIFS(交易明細!$B$2:$B$20,$A4,交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A4,交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A4,交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A4,交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A4,交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="H4" s="4">
@@ -9773,19 +10269,19 @@
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A4,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A4,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A4,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A4,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K4" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A4,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A4,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A4,交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A4,交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -9796,27 +10292,27 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A5)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A5,交易明細!$C$2:$C$18,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A5,交易明細!$C$2:$C$20,"做多")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A5,交易明細!$C$2:$C$18,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A5,交易明細!$C$2:$C$20,"做空")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$18,$A5,交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>F5+G5+COUNTIFS(交易明細!$B$2:$B$20,$A5,交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A5,交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A5,交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A5,交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A5,交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -9824,19 +10320,19 @@
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A5,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A5,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A5,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A5,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A5,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A5,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A5,交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A5,交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -9847,27 +10343,27 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A6)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A6,交易明細!$C$2:$C$18,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A6,交易明細!$C$2:$C$20,"做多")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A6,交易明細!$C$2:$C$18,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A6,交易明細!$C$2:$C$20,"做空")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$18,$A6,交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>F6+G6+COUNTIFS(交易明細!$B$2:$B$20,$A6,交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A6,交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A6,交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A6,交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A6,交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -9875,19 +10371,19 @@
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A6,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A6,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A6,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A6,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A6,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A6,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A6,交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A6,交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -9898,27 +10394,27 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A7)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A7,交易明細!$C$2:$C$18,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A7,交易明細!$C$2:$C$20,"做多")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A7,交易明細!$C$2:$C$18,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A7,交易明細!$C$2:$C$20,"做空")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$18,$A7,交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>F7+G7+COUNTIFS(交易明細!$B$2:$B$20,$A7,交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A7,交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A7,交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A7,交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A7,交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -9926,19 +10422,19 @@
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A7,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A7,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A7,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A7,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A7,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A7,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A7,交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A7,交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -9949,27 +10445,27 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A8)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A8,交易明細!$C$2:$C$18,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A8,交易明細!$C$2:$C$20,"做多")</f>
         <v/>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A8,交易明細!$C$2:$C$18,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A8,交易明細!$C$2:$C$20,"做空")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$18,$A8,交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>F8+G8+COUNTIFS(交易明細!$B$2:$B$20,$A8,交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A8,交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A8,交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="G8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A8,交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A8,交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -9977,19 +10473,19 @@
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A8,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A8,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A8,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A8,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A8,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A8,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A8,交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A8,交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10000,27 +10496,27 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A9)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A9,交易明細!$C$2:$C$18,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A9,交易明細!$C$2:$C$20,"做多")</f>
         <v/>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A9,交易明細!$C$2:$C$18,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A9,交易明細!$C$2:$C$20,"做空")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$18,$A9,交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>F9+G9+COUNTIFS(交易明細!$B$2:$B$20,$A9,交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A9,交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A9,交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="G9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A9,交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A9,交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="H9" s="4">
@@ -10028,19 +10524,19 @@
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A9,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A9,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A9,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A9,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A9,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A9,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A9,交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A9,交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10051,27 +10547,27 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A10)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A10,交易明細!$C$2:$C$18,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A10,交易明細!$C$2:$C$20,"做多")</f>
         <v/>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A10,交易明細!$C$2:$C$18,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A10,交易明細!$C$2:$C$20,"做空")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$18,$A10,交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>F10+G10+COUNTIFS(交易明細!$B$2:$B$20,$A10,交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A10,交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A10,交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="G10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A10,交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A10,交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="H10" s="4">
@@ -10079,19 +10575,19 @@
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A10,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A10,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A10,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A10,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A10,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A10,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L10" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A10,交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A10,交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10102,27 +10598,27 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A11)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A11,交易明細!$C$2:$C$18,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A11,交易明細!$C$2:$C$20,"做多")</f>
         <v/>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A11,交易明細!$C$2:$C$18,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A11,交易明細!$C$2:$C$20,"做空")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$18,$A11,交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>F11+G11+COUNTIFS(交易明細!$B$2:$B$20,$A11,交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A11,交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A11,交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="G11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A11,交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A11,交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="H11" s="4">
@@ -10130,19 +10626,19 @@
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A11,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A11,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A11,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A11,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A11,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A11,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L11" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A11,交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A11,交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10153,27 +10649,27 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A12)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A12,交易明細!$C$2:$C$18,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A12,交易明細!$C$2:$C$20,"做多")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A12,交易明細!$C$2:$C$18,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A12,交易明細!$C$2:$C$20,"做空")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$18,$A12,交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>F12+G12+COUNTIFS(交易明細!$B$2:$B$20,$A12,交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A12,交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A12,交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A12,交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A12,交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="H12" s="4">
@@ -10181,19 +10677,19 @@
         <v/>
       </c>
       <c r="I12" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A12,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A12,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A12,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A12,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A12,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A12,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L12" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A12,交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A12,交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10204,27 +10700,27 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A13)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A13,交易明細!$C$2:$C$18,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A13,交易明細!$C$2:$C$20,"做多")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A13,交易明細!$C$2:$C$18,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A13,交易明細!$C$2:$C$20,"做空")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$18,$A13,交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>F13+G13+COUNTIFS(交易明細!$B$2:$B$20,$A13,交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A13,交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A13,交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A13,交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A13,交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="H13" s="4">
@@ -10232,19 +10728,19 @@
         <v/>
       </c>
       <c r="I13" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A13,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A13,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A13,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A13,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A13,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A13,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L13" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A13,交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A13,交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10255,27 +10751,27 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A14)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A14,交易明細!$C$2:$C$18,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A14,交易明細!$C$2:$C$20,"做多")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A14,交易明細!$C$2:$C$18,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A14,交易明細!$C$2:$C$20,"做空")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$18,$A14,交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>F14+G14+COUNTIFS(交易明細!$B$2:$B$20,$A14,交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A14,交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A14,交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A14,交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A14,交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="H14" s="4">
@@ -10283,19 +10779,19 @@
         <v/>
       </c>
       <c r="I14" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A14,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A14,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A14,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A14,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A14,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A14,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L14" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A14,交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A14,交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
     </row>
@@ -10306,27 +10802,27 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A15)</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A15,交易明細!$C$2:$C$18,"做多")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A15,交易明細!$C$2:$C$20,"做多")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A15,交易明細!$C$2:$C$18,"做空")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A15,交易明細!$C$2:$C$20,"做空")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$18,$A15,交易明細!$J$2:$J$18,"時間出場")</f>
+        <f>F15+G15+COUNTIFS(交易明細!$B$2:$B$20,$A15,交易明細!$J$2:$J$20,"時間出場")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A15,交易明細!$J$2:$J$18,"止盈")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A15,交易明細!$J$2:$J$20,"止盈")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A15,交易明細!$J$2:$J$18,"止損")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A15,交易明細!$J$2:$J$20,"止損")</f>
         <v/>
       </c>
       <c r="H15" s="4">
@@ -10334,24 +10830,126 @@
         <v/>
       </c>
       <c r="I15" s="4">
-        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A15,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A15,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="J15" s="4">
-        <f>SUMIFS(交易明細!$L$2:$L$18,交易明細!$B$2:$B$18,$A15,交易明細!$J$2:$J$18,"&lt;&gt;未平倉")</f>
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A15,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$18,交易明細!$B$2:$B$18,$A15,交易明細!$J$2:$J$18,"&lt;&gt;未平倉"),0)</f>
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A15,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
         <v/>
       </c>
       <c r="L15" s="2">
-        <f>COUNTIFS(交易明細!$B$2:$B$18,$A15,交易明細!$J$2:$J$18,"未平倉")</f>
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A15,交易明細!$J$2:$J$20,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2Z_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B16" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A16,交易明細!$C$2:$C$20,"做多")</f>
+        <v/>
+      </c>
+      <c r="D16" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A16,交易明細!$C$2:$C$20,"做空")</f>
+        <v/>
+      </c>
+      <c r="E16" s="2">
+        <f>F16+G16+COUNTIFS(交易明細!$B$2:$B$20,$A16,交易明細!$J$2:$J$20,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F16" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A16,交易明細!$J$2:$J$20,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G16" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A16,交易明細!$J$2:$J$20,"止損")</f>
+        <v/>
+      </c>
+      <c r="H16" s="4">
+        <f>IFERROR(F16/E16,0)</f>
+        <v/>
+      </c>
+      <c r="I16" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A16,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J16" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A16,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K16" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A16,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L16" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A16,交易明細!$J$2:$J$20,"未平倉")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Q_USDT_PERP</t>
+        </is>
+      </c>
+      <c r="B17" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A17)</f>
+        <v/>
+      </c>
+      <c r="C17" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A17,交易明細!$C$2:$C$20,"做多")</f>
+        <v/>
+      </c>
+      <c r="D17" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A17,交易明細!$C$2:$C$20,"做空")</f>
+        <v/>
+      </c>
+      <c r="E17" s="2">
+        <f>F17+G17+COUNTIFS(交易明細!$B$2:$B$20,$A17,交易明細!$J$2:$J$20,"時間出場")</f>
+        <v/>
+      </c>
+      <c r="F17" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A17,交易明細!$J$2:$J$20,"止盈")</f>
+        <v/>
+      </c>
+      <c r="G17" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A17,交易明細!$J$2:$J$20,"止損")</f>
+        <v/>
+      </c>
+      <c r="H17" s="4">
+        <f>IFERROR(F17/E17,0)</f>
+        <v/>
+      </c>
+      <c r="I17" s="4">
+        <f>IFERROR(AVERAGEIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A17,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="J17" s="4">
+        <f>SUMIFS(交易明細!$L$2:$L$20,交易明細!$B$2:$B$20,$A17,交易明細!$J$2:$J$20,"&lt;&gt;未平倉")</f>
+        <v/>
+      </c>
+      <c r="K17" s="5">
+        <f>IFERROR(AVERAGEIFS(交易明細!$K$2:$K$20,交易明細!$B$2:$B$20,$A17,交易明細!$J$2:$J$20,"&lt;&gt;未平倉"),0)</f>
+        <v/>
+      </c>
+      <c r="L17" s="2">
+        <f>COUNTIFS(交易明細!$B$2:$B$20,$A17,交易明細!$J$2:$J$20,"未平倉")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L15"/>
+  <autoFilter ref="A1:L17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15918,7 +16516,11 @@
           <t>已掃描</t>
         </is>
       </c>
-      <c r="C307" s="2" t="inlineStr"/>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>持倉中</t>
+        </is>
+      </c>
       <c r="D307" s="2" t="n"/>
       <c r="E307" s="17" t="n"/>
       <c r="F307" s="17" t="n"/>

--- a/output/dryrun_s5.xlsx
+++ b/output/dryrun_s5.xlsx
@@ -695,7 +695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 15:09（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
+          <t>回測區間：2026-09-01 00:00 ~ 2026-09-26 15:20（Dry Run）（台北時間）；市場：PERP；勝率 = 止盈筆數 ÷ 已平倉筆數；正報酬比例 = 報酬 &gt; 0 的筆數 ÷ 已平倉（含時間出場）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,56 +1086,56 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46291.63155474537</v>
+        <v>46291.63896155093</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>46291.63055555556</v>
+        <v>46291.63819444444</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>172.6</v>
+        <v>177.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
-        <v>46291.58748165509</v>
+        <v>46291.63155474537</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>46291.58611111111</v>
+        <v>46291.63055555556</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>148</v>
+        <v>172.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46291.52177836806</v>
+        <v>46291.58748165509</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>46291.52083333334</v>
+        <v>46291.58611111111</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>433</v>
@@ -1150,15 +1150,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>187.5</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
-        <v>46291.40186751157</v>
+        <v>46291.52177836806</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>46291.40069444444</v>
+        <v>46291.52083333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>433</v>
@@ -1173,15 +1173,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>188.1</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46291.36540915509</v>
+        <v>46291.40186751157</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>46291.36458333334</v>
+        <v>46291.40069444444</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>433</v>
@@ -1196,15 +1196,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>163.5</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>46291.26887001158</v>
+        <v>46291.36540915509</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>46291.26805555556</v>
+        <v>46291.36458333334</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>433</v>
@@ -1219,15 +1219,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>184.5</v>
+        <v>163.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46291.2560487963</v>
+        <v>46291.26887001158</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>46291.25486111111</v>
+        <v>46291.26805555556</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>433</v>
@@ -1242,84 +1242,84 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>191.6</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>46291.11246790509</v>
+        <v>46291.2560487963</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46291.11111111111</v>
+        <v>46291.25486111111</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>182.3</v>
+        <v>191.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46291.02308788194</v>
+        <v>46291.11246790509</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>46291.02222222222</v>
+        <v>46291.11111111111</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>140.5</v>
+        <v>182.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>46290.9990443287</v>
+        <v>46291.02308788194</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>46290.99791666667</v>
+        <v>46291.02222222222</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>433</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>197.5</v>
+        <v>140.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46290.91267655093</v>
+        <v>46290.9990443287</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>46290.91180555556</v>
+        <v>46290.99791666667</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>433</v>
@@ -1334,38 +1334,38 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>193.4</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>46290.82088560185</v>
+        <v>46290.91267655093</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>46290.8